--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217850</v>
+        <v>129217849</v>
       </c>
       <c r="B2" t="n">
         <v>79035</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527358</v>
+        <v>526979</v>
       </c>
       <c r="R2" t="n">
-        <v>7087435</v>
+        <v>7087143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217849</v>
+        <v>129217850</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526979</v>
+        <v>527358</v>
       </c>
       <c r="R3" t="n">
-        <v>7087143</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217798</v>
+        <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>92199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527408</v>
+        <v>527386</v>
       </c>
       <c r="R9" t="n">
-        <v>7087464</v>
+        <v>7087522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217856</v>
+        <v>129217813</v>
       </c>
       <c r="B11" t="n">
-        <v>92199</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527386</v>
+        <v>526901</v>
       </c>
       <c r="R11" t="n">
-        <v>7087522</v>
+        <v>7087135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,7 +1670,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217813</v>
+        <v>129217798</v>
       </c>
       <c r="B12" t="n">
         <v>57723</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526901</v>
+        <v>527408</v>
       </c>
       <c r="R12" t="n">
-        <v>7087135</v>
+        <v>7087464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,45 +1869,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217928</v>
+        <v>129217785</v>
       </c>
       <c r="B14" t="n">
-        <v>82898</v>
+        <v>91491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527359</v>
+        <v>527106</v>
       </c>
       <c r="R14" t="n">
-        <v>7087548</v>
+        <v>7087220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1948,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217842</v>
+        <v>129217780</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>83011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527385</v>
+        <v>527179</v>
       </c>
       <c r="R15" t="n">
-        <v>7087528</v>
+        <v>7087518</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,32 +2063,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217917</v>
+        <v>129217925</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527273</v>
+        <v>527089</v>
       </c>
       <c r="R16" t="n">
-        <v>7087581</v>
+        <v>7087260</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,11 +2134,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2166,10 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217852</v>
+        <v>129217795</v>
       </c>
       <c r="B17" t="n">
-        <v>82898</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,21 +2171,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2201,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527265</v>
+        <v>527123</v>
       </c>
       <c r="R17" t="n">
-        <v>7087520</v>
+        <v>7087425</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2263,10 +2257,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217840</v>
+        <v>129217855</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>82898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2268,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527386</v>
+        <v>527012</v>
       </c>
       <c r="R18" t="n">
-        <v>7087517</v>
+        <v>7087233</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217925</v>
+        <v>129217840</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>91540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,34 +2365,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527089</v>
+        <v>527386</v>
       </c>
       <c r="R19" t="n">
-        <v>7087260</v>
+        <v>7087517</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2457,7 +2451,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217855</v>
+        <v>129217928</v>
       </c>
       <c r="B20" t="n">
         <v>82898</v>
@@ -2488,14 +2482,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527012</v>
+        <v>527359</v>
       </c>
       <c r="R20" t="n">
-        <v>7087233</v>
+        <v>7087548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,6 +2530,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2554,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217785</v>
+        <v>129217842</v>
       </c>
       <c r="B21" t="n">
-        <v>91491</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527106</v>
+        <v>527385</v>
       </c>
       <c r="R21" t="n">
-        <v>7087220</v>
+        <v>7087528</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2651,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217780</v>
+        <v>129217852</v>
       </c>
       <c r="B22" t="n">
-        <v>83011</v>
+        <v>82898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2662,21 +2657,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2686,10 +2681,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527179</v>
+        <v>527265</v>
       </c>
       <c r="R22" t="n">
-        <v>7087518</v>
+        <v>7087520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2748,32 +2743,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217795</v>
+        <v>129217797</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>92226</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2783,10 +2778,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527123</v>
+        <v>527368</v>
       </c>
       <c r="R23" t="n">
-        <v>7087425</v>
+        <v>7087576</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2845,45 +2840,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217797</v>
+        <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>92226</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527368</v>
+        <v>527273</v>
       </c>
       <c r="R24" t="n">
-        <v>7087576</v>
+        <v>7087581</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2942,10 +2942,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129217779</v>
+        <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>83011</v>
+        <v>91526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527248</v>
+        <v>527167</v>
       </c>
       <c r="R25" t="n">
-        <v>7087513</v>
+        <v>7087461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129217793</v>
+        <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>91526</v>
+        <v>83011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527167</v>
+        <v>527248</v>
       </c>
       <c r="R26" t="n">
-        <v>7087461</v>
+        <v>7087513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217807</v>
+        <v>129217926</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>526921</v>
+        <v>527029</v>
       </c>
       <c r="R27" t="n">
-        <v>7087159</v>
+        <v>7087194</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,11 +3207,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217926</v>
+        <v>129217789</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,34 +3244,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527029</v>
+        <v>527376</v>
       </c>
       <c r="R28" t="n">
-        <v>7087194</v>
+        <v>7087516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217789</v>
+        <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3438,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527376</v>
+        <v>526921</v>
       </c>
       <c r="R30" t="n">
-        <v>7087516</v>
+        <v>7087159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217922</v>
+        <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>56904</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,34 +3540,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527122</v>
+        <v>527291</v>
       </c>
       <c r="R31" t="n">
-        <v>7087232</v>
+        <v>7087491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217836</v>
+        <v>129217820</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527091</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>7087273</v>
+        <v>7087201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,6 +3697,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3723,10 +3728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>56904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,16 +3739,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3754,14 +3759,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R33" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3799,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,32 +3825,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217787</v>
+        <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527291</v>
+        <v>527091</v>
       </c>
       <c r="R34" t="n">
-        <v>7087491</v>
+        <v>7087273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129217846</v>
+        <v>129217812</v>
       </c>
       <c r="B35" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527139</v>
+        <v>526904</v>
       </c>
       <c r="R35" t="n">
-        <v>7087468</v>
+        <v>7087132</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,6 +3993,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4019,10 +4024,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129217812</v>
+        <v>129217846</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,21 +4035,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4054,10 +4059,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>526904</v>
+        <v>527139</v>
       </c>
       <c r="R36" t="n">
-        <v>7087132</v>
+        <v>7087468</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,11 +4095,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4121,32 +4121,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R37" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,6 +4192,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4218,32 +4223,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217845</v>
+        <v>129217833</v>
       </c>
       <c r="B38" t="n">
-        <v>91544</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4253,10 +4258,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527173</v>
+        <v>527351</v>
       </c>
       <c r="R38" t="n">
-        <v>7087380</v>
+        <v>7087510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,6 +4294,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4315,32 +4325,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217821</v>
+        <v>129217835</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4350,10 +4360,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526924</v>
+        <v>527103</v>
       </c>
       <c r="R39" t="n">
-        <v>7087187</v>
+        <v>7087341</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4386,11 +4396,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4417,10 +4422,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217803</v>
+        <v>129217845</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4428,21 +4433,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4452,10 +4457,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526923</v>
+        <v>527173</v>
       </c>
       <c r="R40" t="n">
-        <v>7087199</v>
+        <v>7087380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4488,11 +4493,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4519,32 +4519,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4554,10 +4554,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R41" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4718,10 +4718,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129217778</v>
+        <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>83011</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4729,21 +4729,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>526957</v>
+        <v>527378</v>
       </c>
       <c r="R43" t="n">
-        <v>7087142</v>
+        <v>7087514</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4815,32 +4815,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217843</v>
+        <v>129217826</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>80044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527378</v>
+        <v>527090</v>
       </c>
       <c r="R44" t="n">
-        <v>7087514</v>
+        <v>7087261</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4912,32 +4912,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217826</v>
+        <v>129217778</v>
       </c>
       <c r="B45" t="n">
-        <v>80044</v>
+        <v>83011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527090</v>
+        <v>526957</v>
       </c>
       <c r="R45" t="n">
-        <v>7087261</v>
+        <v>7087142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5117,34 +5117,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R47" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5177,11 +5177,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5208,45 +5203,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217844</v>
+        <v>129217923</v>
       </c>
       <c r="B48" t="n">
-        <v>57715</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527355</v>
+        <v>527150</v>
       </c>
       <c r="R48" t="n">
-        <v>7087521</v>
+        <v>7087278</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,6 +5274,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5305,45 +5305,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217920</v>
+        <v>129217844</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>57715</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527064</v>
+        <v>527355</v>
       </c>
       <c r="R49" t="n">
-        <v>7087252</v>
+        <v>7087521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,11 +5376,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5509,45 +5504,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217790</v>
+        <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527357</v>
+        <v>527064</v>
       </c>
       <c r="R51" t="n">
-        <v>7087574</v>
+        <v>7087252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5580,6 +5575,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5703,7 +5703,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217800</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
         <v>57723</v>
@@ -5731,17 +5731,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527297</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087514</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5778,7 +5798,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5805,7 +5825,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217801</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
         <v>57723</v>
@@ -5840,10 +5860,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527106</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087348</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5880,7 +5900,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5907,7 +5927,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217819</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
         <v>57723</v>
@@ -5935,37 +5955,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527070</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087285</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6131,10 +6131,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217823</v>
+        <v>129217848</v>
       </c>
       <c r="B57" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6142,21 +6142,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527374</v>
+        <v>527106</v>
       </c>
       <c r="R57" t="n">
-        <v>7087508</v>
+        <v>7087367</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6233,32 +6233,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217832</v>
+        <v>129217784</v>
       </c>
       <c r="B58" t="n">
-        <v>98659</v>
+        <v>96905</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527149</v>
+        <v>527349</v>
       </c>
       <c r="R58" t="n">
-        <v>7087289</v>
+        <v>7087510</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6304,11 +6304,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6335,45 +6330,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217919</v>
+        <v>129217823</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527135</v>
+        <v>527374</v>
       </c>
       <c r="R59" t="n">
-        <v>7087449</v>
+        <v>7087508</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6410,7 +6405,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6437,7 +6432,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217834</v>
+        <v>129217832</v>
       </c>
       <c r="B60" t="n">
         <v>98659</v>
@@ -6472,10 +6467,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527268</v>
+        <v>527149</v>
       </c>
       <c r="R60" t="n">
-        <v>7087590</v>
+        <v>7087289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6512,7 +6507,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6539,45 +6534,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217848</v>
+        <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527106</v>
+        <v>527135</v>
       </c>
       <c r="R61" t="n">
-        <v>7087367</v>
+        <v>7087449</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6614,7 +6609,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6641,32 +6636,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217784</v>
+        <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>96905</v>
+        <v>98659</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6676,10 +6671,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527349</v>
+        <v>527268</v>
       </c>
       <c r="R62" t="n">
-        <v>7087510</v>
+        <v>7087590</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6712,6 +6707,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6738,45 +6738,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217913</v>
+        <v>129217854</v>
       </c>
       <c r="B63" t="n">
-        <v>98659</v>
+        <v>82898</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>526924</v>
+        <v>527015</v>
       </c>
       <c r="R63" t="n">
-        <v>7087085</v>
+        <v>7087228</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,11 +6809,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6840,32 +6835,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217829</v>
+        <v>129217827</v>
       </c>
       <c r="B64" t="n">
-        <v>91811</v>
+        <v>91981</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6875,10 +6870,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527138</v>
+        <v>527136</v>
       </c>
       <c r="R64" t="n">
-        <v>7087472</v>
+        <v>7087471</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6937,10 +6932,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217806</v>
+        <v>129217829</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6948,21 +6943,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6972,10 +6967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526925</v>
+        <v>527138</v>
       </c>
       <c r="R65" t="n">
-        <v>7087175</v>
+        <v>7087472</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7008,11 +7003,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7039,32 +7029,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217827</v>
+        <v>129217818</v>
       </c>
       <c r="B66" t="n">
-        <v>91981</v>
+        <v>57723</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7074,10 +7064,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527136</v>
+        <v>527359</v>
       </c>
       <c r="R66" t="n">
-        <v>7087471</v>
+        <v>7087452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7110,6 +7100,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7136,7 +7131,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217810</v>
+        <v>129217806</v>
       </c>
       <c r="B67" t="n">
         <v>57723</v>
@@ -7171,10 +7166,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526914</v>
+        <v>526925</v>
       </c>
       <c r="R67" t="n">
-        <v>7087139</v>
+        <v>7087175</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7211,7 +7206,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7238,7 +7233,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217818</v>
+        <v>129217810</v>
       </c>
       <c r="B68" t="n">
         <v>57723</v>
@@ -7273,10 +7268,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527359</v>
+        <v>526914</v>
       </c>
       <c r="R68" t="n">
-        <v>7087452</v>
+        <v>7087139</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7313,7 +7308,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7340,45 +7335,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217854</v>
+        <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>82898</v>
+        <v>98659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527015</v>
+        <v>526924</v>
       </c>
       <c r="R69" t="n">
-        <v>7087228</v>
+        <v>7087085</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,6 +7406,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7437,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217911</v>
+        <v>129217804</v>
       </c>
       <c r="B70" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,34 +7448,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527164</v>
+        <v>526927</v>
       </c>
       <c r="R70" t="n">
-        <v>7087462</v>
+        <v>7087193</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7508,6 +7508,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7534,10 +7539,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217853</v>
+        <v>129217808</v>
       </c>
       <c r="B71" t="n">
-        <v>82898</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,21 +7550,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7569,10 +7574,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527133</v>
+        <v>526917</v>
       </c>
       <c r="R71" t="n">
-        <v>7087390</v>
+        <v>7087144</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7605,6 +7610,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7631,10 +7641,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217804</v>
+        <v>129217911</v>
       </c>
       <c r="B72" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,34 +7652,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>526927</v>
+        <v>527164</v>
       </c>
       <c r="R72" t="n">
-        <v>7087193</v>
+        <v>7087462</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,11 +7712,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7733,10 +7738,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217808</v>
+        <v>129217786</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7744,21 +7749,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7768,10 +7773,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>526917</v>
+        <v>527238</v>
       </c>
       <c r="R73" t="n">
-        <v>7087144</v>
+        <v>7087520</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7804,11 +7809,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7835,10 +7835,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217786</v>
+        <v>129217853</v>
       </c>
       <c r="B74" t="n">
-        <v>91526</v>
+        <v>82898</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7846,21 +7846,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527238</v>
+        <v>527133</v>
       </c>
       <c r="R74" t="n">
-        <v>7087520</v>
+        <v>7087390</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217929</v>
+        <v>129217912</v>
       </c>
       <c r="B78" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8234,21 +8234,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8258,10 +8258,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527393</v>
+        <v>527089</v>
       </c>
       <c r="R78" t="n">
-        <v>7087440</v>
+        <v>7087260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8422,10 +8422,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217841</v>
+        <v>129217802</v>
       </c>
       <c r="B80" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8433,21 +8433,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8457,10 +8457,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527375</v>
+        <v>526934</v>
       </c>
       <c r="R80" t="n">
-        <v>7087521</v>
+        <v>7087213</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8493,6 +8493,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8519,10 +8524,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217912</v>
+        <v>129217929</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8530,21 +8535,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8554,10 +8559,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527089</v>
+        <v>527393</v>
       </c>
       <c r="R81" t="n">
-        <v>7087260</v>
+        <v>7087440</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8594,7 +8599,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8621,45 +8626,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217921</v>
+        <v>129217841</v>
       </c>
       <c r="B82" t="n">
-        <v>98659</v>
+        <v>91540</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526984</v>
+        <v>527375</v>
       </c>
       <c r="R82" t="n">
-        <v>7087226</v>
+        <v>7087521</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8692,11 +8697,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8723,45 +8723,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217914</v>
+        <v>129217830</v>
       </c>
       <c r="B83" t="n">
-        <v>98659</v>
+        <v>78048</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526928</v>
+        <v>526990</v>
       </c>
       <c r="R83" t="n">
-        <v>7087112</v>
+        <v>7087234</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8794,11 +8794,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8825,45 +8820,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217830</v>
+        <v>129217921</v>
       </c>
       <c r="B84" t="n">
-        <v>78048</v>
+        <v>98659</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526990</v>
+        <v>526984</v>
       </c>
       <c r="R84" t="n">
-        <v>7087234</v>
+        <v>7087226</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8896,6 +8891,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8922,45 +8922,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217802</v>
+        <v>129217914</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526934</v>
+        <v>526928</v>
       </c>
       <c r="R85" t="n">
-        <v>7087213</v>
+        <v>7087112</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9218,45 +9218,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217915</v>
+        <v>129217814</v>
       </c>
       <c r="B88" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527145</v>
+        <v>526905</v>
       </c>
       <c r="R88" t="n">
-        <v>7087306</v>
+        <v>7087117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217814</v>
+        <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526905</v>
+        <v>527094</v>
       </c>
       <c r="R89" t="n">
-        <v>7087117</v>
+        <v>7087264</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9422,45 +9422,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217851</v>
+        <v>129217915</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527094</v>
+        <v>527145</v>
       </c>
       <c r="R90" t="n">
-        <v>7087264</v>
+        <v>7087306</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217849</v>
+        <v>129217918</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526979</v>
+        <v>527262</v>
       </c>
       <c r="R2" t="n">
-        <v>7087143</v>
+        <v>7087588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217850</v>
+        <v>129217849</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527358</v>
+        <v>526979</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217815</v>
+        <v>129217850</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526883</v>
+        <v>527358</v>
       </c>
       <c r="R4" t="n">
-        <v>7087121</v>
+        <v>7087435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217918</v>
+        <v>129217815</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527262</v>
+        <v>526883</v>
       </c>
       <c r="R5" t="n">
-        <v>7087588</v>
+        <v>7087121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R6" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>80100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217831</v>
+        <v>129217791</v>
       </c>
       <c r="B8" t="n">
-        <v>80100</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527362</v>
+        <v>527219</v>
       </c>
       <c r="R8" t="n">
-        <v>7087507</v>
+        <v>7087542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217785</v>
+        <v>129217795</v>
       </c>
       <c r="B14" t="n">
-        <v>91491</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527106</v>
+        <v>527123</v>
       </c>
       <c r="R14" t="n">
-        <v>7087220</v>
+        <v>7087425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217780</v>
+        <v>129217855</v>
       </c>
       <c r="B15" t="n">
-        <v>83011</v>
+        <v>82898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527179</v>
+        <v>527012</v>
       </c>
       <c r="R15" t="n">
-        <v>7087518</v>
+        <v>7087233</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217925</v>
+        <v>129217840</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,34 +2074,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527089</v>
+        <v>527386</v>
       </c>
       <c r="R16" t="n">
-        <v>7087260</v>
+        <v>7087517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,10 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217795</v>
+        <v>129217928</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>82898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,34 +2171,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527123</v>
+        <v>527359</v>
       </c>
       <c r="R17" t="n">
-        <v>7087425</v>
+        <v>7087548</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,6 +2239,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2257,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217855</v>
+        <v>129217842</v>
       </c>
       <c r="B18" t="n">
-        <v>82898</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2292,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527012</v>
+        <v>527385</v>
       </c>
       <c r="R18" t="n">
-        <v>7087233</v>
+        <v>7087528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,10 +2355,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217840</v>
+        <v>129217852</v>
       </c>
       <c r="B19" t="n">
-        <v>91540</v>
+        <v>82898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2365,21 +2366,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2389,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527386</v>
+        <v>527265</v>
       </c>
       <c r="R19" t="n">
-        <v>7087517</v>
+        <v>7087520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,45 +2452,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217928</v>
+        <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>82898</v>
+        <v>92226</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527359</v>
+        <v>527368</v>
       </c>
       <c r="R20" t="n">
-        <v>7087548</v>
+        <v>7087576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2531,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2549,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217842</v>
+        <v>129217785</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>91491</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527385</v>
+        <v>527106</v>
       </c>
       <c r="R21" t="n">
-        <v>7087528</v>
+        <v>7087220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217852</v>
+        <v>129217780</v>
       </c>
       <c r="B22" t="n">
-        <v>82898</v>
+        <v>83011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527265</v>
+        <v>527179</v>
       </c>
       <c r="R22" t="n">
-        <v>7087520</v>
+        <v>7087518</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,45 +2743,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217797</v>
+        <v>129217925</v>
       </c>
       <c r="B23" t="n">
-        <v>92226</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527368</v>
+        <v>527089</v>
       </c>
       <c r="R23" t="n">
-        <v>7087576</v>
+        <v>7087260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217820</v>
+        <v>129217836</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527091</v>
       </c>
       <c r="R32" t="n">
-        <v>7087201</v>
+        <v>7087273</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,11 +3697,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3728,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217922</v>
+        <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>56904</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3739,16 +3734,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3759,14 +3754,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527122</v>
+        <v>527034</v>
       </c>
       <c r="R33" t="n">
-        <v>7087232</v>
+        <v>7087201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3799,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>56904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R34" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5203,32 +5203,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217923</v>
+        <v>129217920</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527150</v>
+        <v>527064</v>
       </c>
       <c r="R48" t="n">
-        <v>7087278</v>
+        <v>7087252</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5305,45 +5305,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217844</v>
+        <v>129217923</v>
       </c>
       <c r="B49" t="n">
-        <v>57715</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527355</v>
+        <v>527150</v>
       </c>
       <c r="R49" t="n">
-        <v>7087521</v>
+        <v>7087278</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,6 +5376,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5402,32 +5407,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217805</v>
+        <v>129217844</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>57715</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>526924</v>
+        <v>527355</v>
       </c>
       <c r="R50" t="n">
-        <v>7087183</v>
+        <v>7087521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,11 +5478,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5504,45 +5504,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217920</v>
+        <v>129217805</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527064</v>
+        <v>526924</v>
       </c>
       <c r="R51" t="n">
-        <v>7087252</v>
+        <v>7087183</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5606,10 +5606,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217794</v>
+        <v>129217819</v>
       </c>
       <c r="B52" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5617,34 +5617,54 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527134</v>
+        <v>527070</v>
       </c>
       <c r="R52" t="n">
-        <v>7087464</v>
+        <v>7087285</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5677,6 +5697,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5703,7 +5728,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B53" t="n">
         <v>57723</v>
@@ -5731,37 +5756,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5798,7 +5803,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5825,7 +5830,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B54" t="n">
         <v>57723</v>
@@ -5860,10 +5865,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5900,7 +5905,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5927,10 +5932,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217794</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5938,21 +5943,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5962,10 +5967,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>527134</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087464</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5998,11 +6003,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6131,10 +6131,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217848</v>
+        <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>96905</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6142,21 +6142,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527106</v>
+        <v>527349</v>
       </c>
       <c r="R57" t="n">
-        <v>7087367</v>
+        <v>7087510</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6202,11 +6202,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6233,10 +6228,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217784</v>
+        <v>129217823</v>
       </c>
       <c r="B58" t="n">
-        <v>96905</v>
+        <v>57883</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6244,21 +6239,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6268,10 +6263,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527349</v>
+        <v>527374</v>
       </c>
       <c r="R58" t="n">
-        <v>7087510</v>
+        <v>7087508</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6304,6 +6299,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6330,32 +6330,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217823</v>
+        <v>129217832</v>
       </c>
       <c r="B59" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527374</v>
+        <v>527149</v>
       </c>
       <c r="R59" t="n">
-        <v>7087508</v>
+        <v>7087289</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6432,7 +6432,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B60" t="n">
         <v>98659</v>
@@ -6463,14 +6463,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R60" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6534,7 +6534,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217919</v>
+        <v>129217834</v>
       </c>
       <c r="B61" t="n">
         <v>98659</v>
@@ -6565,14 +6565,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527135</v>
+        <v>527268</v>
       </c>
       <c r="R61" t="n">
-        <v>7087449</v>
+        <v>7087590</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6636,32 +6636,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217834</v>
+        <v>129217848</v>
       </c>
       <c r="B62" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527268</v>
+        <v>527106</v>
       </c>
       <c r="R62" t="n">
-        <v>7087590</v>
+        <v>7087367</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7437,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217804</v>
+        <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,21 +7448,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>526927</v>
+        <v>527238</v>
       </c>
       <c r="R70" t="n">
-        <v>7087193</v>
+        <v>7087520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7508,11 +7508,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7539,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217808</v>
+        <v>129217853</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>82898</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7550,21 +7545,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7574,10 +7569,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526917</v>
+        <v>527133</v>
       </c>
       <c r="R71" t="n">
-        <v>7087144</v>
+        <v>7087390</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7610,11 +7605,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7738,10 +7728,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217786</v>
+        <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>91526</v>
+        <v>83011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7749,21 +7739,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7773,10 +7763,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527238</v>
+        <v>527141</v>
       </c>
       <c r="R73" t="n">
-        <v>7087520</v>
+        <v>7087466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7835,10 +7825,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217853</v>
+        <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>82898</v>
+        <v>57723</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7846,21 +7836,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7870,10 +7860,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527133</v>
+        <v>526927</v>
       </c>
       <c r="R74" t="n">
-        <v>7087390</v>
+        <v>7087193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7906,6 +7896,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7932,10 +7927,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217781</v>
+        <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>83011</v>
+        <v>57723</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7943,21 +7938,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7967,10 +7962,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527141</v>
+        <v>526917</v>
       </c>
       <c r="R75" t="n">
-        <v>7087466</v>
+        <v>7087144</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8003,6 +7998,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9320,45 +9320,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217851</v>
+        <v>129217915</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527094</v>
+        <v>527145</v>
       </c>
       <c r="R89" t="n">
-        <v>7087264</v>
+        <v>7087306</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9422,45 +9422,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217915</v>
+        <v>129217851</v>
       </c>
       <c r="B90" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527145</v>
+        <v>527094</v>
       </c>
       <c r="R90" t="n">
-        <v>7087306</v>
+        <v>7087264</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217918</v>
+        <v>129217849</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527262</v>
+        <v>526979</v>
       </c>
       <c r="R2" t="n">
-        <v>7087588</v>
+        <v>7087143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217849</v>
+        <v>129217850</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526979</v>
+        <v>527358</v>
       </c>
       <c r="R3" t="n">
-        <v>7087143</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217850</v>
+        <v>129217815</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527358</v>
+        <v>526883</v>
       </c>
       <c r="R4" t="n">
-        <v>7087435</v>
+        <v>7087121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217815</v>
+        <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526883</v>
+        <v>527262</v>
       </c>
       <c r="R5" t="n">
-        <v>7087121</v>
+        <v>7087588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R6" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217831</v>
+        <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>80100</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527362</v>
+        <v>527399</v>
       </c>
       <c r="R7" t="n">
-        <v>7087507</v>
+        <v>7087454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217791</v>
+        <v>129217831</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>80104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527219</v>
+        <v>527362</v>
       </c>
       <c r="R8" t="n">
-        <v>7087542</v>
+        <v>7087507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217856</v>
+        <v>129217813</v>
       </c>
       <c r="B9" t="n">
-        <v>92199</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527386</v>
+        <v>526901</v>
       </c>
       <c r="R9" t="n">
-        <v>7087522</v>
+        <v>7087135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217782</v>
+        <v>129217798</v>
       </c>
       <c r="B10" t="n">
-        <v>96905</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527172</v>
+        <v>527408</v>
       </c>
       <c r="R10" t="n">
-        <v>7087341</v>
+        <v>7087464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,32 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217813</v>
+        <v>129217856</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>92206</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526901</v>
+        <v>527386</v>
       </c>
       <c r="R11" t="n">
-        <v>7087135</v>
+        <v>7087522</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1639,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217798</v>
+        <v>129217782</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>96915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527408</v>
+        <v>527172</v>
       </c>
       <c r="R12" t="n">
-        <v>7087464</v>
+        <v>7087341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,7 +1775,7 @@
         <v>129217927</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217795</v>
+        <v>129217928</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>82902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527123</v>
+        <v>527359</v>
       </c>
       <c r="R14" t="n">
-        <v>7087425</v>
+        <v>7087548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,6 +1948,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217855</v>
+        <v>129217842</v>
       </c>
       <c r="B15" t="n">
-        <v>82898</v>
+        <v>91547</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1978,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527012</v>
+        <v>527385</v>
       </c>
       <c r="R15" t="n">
-        <v>7087233</v>
+        <v>7087528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217840</v>
+        <v>129217852</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>82902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527386</v>
+        <v>527265</v>
       </c>
       <c r="R16" t="n">
-        <v>7087517</v>
+        <v>7087520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217928</v>
+        <v>129217840</v>
       </c>
       <c r="B17" t="n">
-        <v>82898</v>
+        <v>91547</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,34 +2172,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527359</v>
+        <v>527386</v>
       </c>
       <c r="R17" t="n">
-        <v>7087548</v>
+        <v>7087517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2240,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217842</v>
+        <v>129217795</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>91533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527385</v>
+        <v>527123</v>
       </c>
       <c r="R18" t="n">
-        <v>7087528</v>
+        <v>7087425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217852</v>
+        <v>129217855</v>
       </c>
       <c r="B19" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527265</v>
+        <v>527012</v>
       </c>
       <c r="R19" t="n">
-        <v>7087520</v>
+        <v>7087233</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217797</v>
+        <v>129217785</v>
       </c>
       <c r="B20" t="n">
-        <v>92226</v>
+        <v>91497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2463,21 +2463,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527368</v>
+        <v>527106</v>
       </c>
       <c r="R20" t="n">
-        <v>7087576</v>
+        <v>7087220</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217785</v>
+        <v>129217797</v>
       </c>
       <c r="B21" t="n">
-        <v>91491</v>
+        <v>92233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2560,21 +2560,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527106</v>
+        <v>527368</v>
       </c>
       <c r="R21" t="n">
-        <v>7087220</v>
+        <v>7087576</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,45 +2646,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217780</v>
+        <v>129217917</v>
       </c>
       <c r="B22" t="n">
-        <v>83011</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527179</v>
+        <v>527273</v>
       </c>
       <c r="R22" t="n">
-        <v>7087518</v>
+        <v>7087581</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,6 +2717,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2743,10 +2748,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217925</v>
+        <v>129217780</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>83015</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2754,34 +2759,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527089</v>
+        <v>527179</v>
       </c>
       <c r="R23" t="n">
-        <v>7087260</v>
+        <v>7087518</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2840,32 +2845,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217917</v>
+        <v>129217925</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2880,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527273</v>
+        <v>527089</v>
       </c>
       <c r="R24" t="n">
-        <v>7087581</v>
+        <v>7087260</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,11 +2916,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2945,7 +2945,7 @@
         <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217926</v>
+        <v>129217789</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527029</v>
+        <v>527376</v>
       </c>
       <c r="R27" t="n">
-        <v>7087194</v>
+        <v>7087516</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217789</v>
+        <v>129217910</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3264,14 +3264,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527376</v>
+        <v>527288</v>
       </c>
       <c r="R28" t="n">
-        <v>7087516</v>
+        <v>7087491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217910</v>
+        <v>129217926</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527288</v>
+        <v>527029</v>
       </c>
       <c r="R29" t="n">
-        <v>7087491</v>
+        <v>7087194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,45 +3626,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>56906</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R32" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3726,7 +3726,7 @@
         <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217922</v>
+        <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>56904</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527122</v>
+        <v>527091</v>
       </c>
       <c r="R34" t="n">
-        <v>7087232</v>
+        <v>7087273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129217812</v>
+        <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>91551</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>526904</v>
+        <v>527139</v>
       </c>
       <c r="R35" t="n">
-        <v>7087132</v>
+        <v>7087468</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,11 +3993,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4024,10 +4019,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129217846</v>
+        <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4035,21 +4030,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4059,10 +4054,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527139</v>
+        <v>526904</v>
       </c>
       <c r="R36" t="n">
-        <v>7087468</v>
+        <v>7087132</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4095,6 +4090,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4121,10 +4121,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217821</v>
+        <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>91551</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4132,21 +4132,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526924</v>
+        <v>527173</v>
       </c>
       <c r="R37" t="n">
-        <v>7087187</v>
+        <v>7087380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,11 +4192,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4223,32 +4218,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4258,10 +4253,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R38" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4298,7 +4293,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4325,32 +4320,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4360,10 +4355,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R39" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4396,6 +4391,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4422,32 +4422,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217845</v>
+        <v>129217833</v>
       </c>
       <c r="B40" t="n">
-        <v>91544</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527173</v>
+        <v>527351</v>
       </c>
       <c r="R40" t="n">
-        <v>7087380</v>
+        <v>7087510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4493,6 +4493,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4519,32 +4524,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217803</v>
+        <v>129217835</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4554,10 +4559,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526923</v>
+        <v>527103</v>
       </c>
       <c r="R41" t="n">
-        <v>7087199</v>
+        <v>7087341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4590,11 +4595,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4624,7 +4624,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>129217826</v>
       </c>
       <c r="B44" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>129217778</v>
       </c>
       <c r="B45" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>129217838</v>
       </c>
       <c r="B46" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5203,32 +5203,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217920</v>
+        <v>129217923</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527064</v>
+        <v>527150</v>
       </c>
       <c r="R48" t="n">
-        <v>7087252</v>
+        <v>7087278</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5305,45 +5305,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217923</v>
+        <v>129217844</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>57717</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527150</v>
+        <v>527355</v>
       </c>
       <c r="R49" t="n">
-        <v>7087278</v>
+        <v>7087521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,11 +5376,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5407,32 +5402,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217844</v>
+        <v>129217805</v>
       </c>
       <c r="B50" t="n">
-        <v>57715</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5442,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527355</v>
+        <v>526924</v>
       </c>
       <c r="R50" t="n">
-        <v>7087521</v>
+        <v>7087183</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5478,6 +5473,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5504,45 +5504,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217805</v>
+        <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>526924</v>
+        <v>527064</v>
       </c>
       <c r="R51" t="n">
-        <v>7087183</v>
+        <v>7087252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5606,10 +5606,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217819</v>
+        <v>129217794</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5617,54 +5617,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527070</v>
+        <v>527134</v>
       </c>
       <c r="R52" t="n">
-        <v>7087285</v>
+        <v>7087464</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5697,11 +5677,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5728,10 +5703,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217800</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5756,17 +5731,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527297</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087514</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5803,7 +5798,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5830,10 +5825,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217801</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5865,10 +5860,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527106</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087348</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5905,7 +5900,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5932,10 +5927,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217794</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
-        <v>91526</v>
+        <v>57725</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5943,21 +5938,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5967,10 +5962,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527134</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087464</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6003,6 +5998,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6032,7 +6032,7 @@
         <v>129217837</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217784</v>
+        <v>129217848</v>
       </c>
       <c r="B57" t="n">
-        <v>96905</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6142,21 +6142,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527349</v>
+        <v>527106</v>
       </c>
       <c r="R57" t="n">
-        <v>7087510</v>
+        <v>7087367</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6202,6 +6202,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6231,7 +6236,7 @@
         <v>129217823</v>
       </c>
       <c r="B58" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6330,32 +6335,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217832</v>
+        <v>129217784</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>96915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6365,10 +6370,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527149</v>
+        <v>527349</v>
       </c>
       <c r="R59" t="n">
-        <v>7087289</v>
+        <v>7087510</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6401,11 +6406,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6432,10 +6432,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217919</v>
+        <v>129217832</v>
       </c>
       <c r="B60" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6463,14 +6463,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527135</v>
+        <v>527149</v>
       </c>
       <c r="R60" t="n">
-        <v>7087449</v>
+        <v>7087289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6534,10 +6534,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217834</v>
+        <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6565,14 +6565,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527268</v>
+        <v>527135</v>
       </c>
       <c r="R61" t="n">
-        <v>7087590</v>
+        <v>7087449</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6636,32 +6636,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217848</v>
+        <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527106</v>
+        <v>527268</v>
       </c>
       <c r="R62" t="n">
-        <v>7087367</v>
+        <v>7087590</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217854</v>
+        <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>82898</v>
+        <v>91818</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527015</v>
+        <v>527138</v>
       </c>
       <c r="R63" t="n">
-        <v>7087228</v>
+        <v>7087472</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6838,7 +6838,7 @@
         <v>129217827</v>
       </c>
       <c r="B64" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217829</v>
+        <v>129217854</v>
       </c>
       <c r="B65" t="n">
-        <v>91811</v>
+        <v>82902</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6943,21 +6943,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527138</v>
+        <v>527015</v>
       </c>
       <c r="R65" t="n">
-        <v>7087472</v>
+        <v>7087228</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,45 +7029,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217818</v>
+        <v>129217913</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527359</v>
+        <v>526924</v>
       </c>
       <c r="R66" t="n">
-        <v>7087452</v>
+        <v>7087085</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7134,7 +7134,7 @@
         <v>129217806</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>129217810</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7335,45 +7335,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217913</v>
+        <v>129217818</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526924</v>
+        <v>527359</v>
       </c>
       <c r="R69" t="n">
-        <v>7087085</v>
+        <v>7087452</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7437,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217786</v>
+        <v>129217781</v>
       </c>
       <c r="B70" t="n">
-        <v>91526</v>
+        <v>83015</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,21 +7448,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527238</v>
+        <v>527141</v>
       </c>
       <c r="R70" t="n">
-        <v>7087520</v>
+        <v>7087466</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217853</v>
+        <v>129217804</v>
       </c>
       <c r="B71" t="n">
-        <v>82898</v>
+        <v>57725</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527133</v>
+        <v>526927</v>
       </c>
       <c r="R71" t="n">
-        <v>7087390</v>
+        <v>7087193</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7605,6 +7605,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7631,10 +7636,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217911</v>
+        <v>129217808</v>
       </c>
       <c r="B72" t="n">
-        <v>91526</v>
+        <v>57725</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,34 +7647,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527164</v>
+        <v>526917</v>
       </c>
       <c r="R72" t="n">
-        <v>7087462</v>
+        <v>7087144</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,6 +7707,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7728,10 +7738,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217781</v>
+        <v>129217786</v>
       </c>
       <c r="B73" t="n">
-        <v>83011</v>
+        <v>91533</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7739,21 +7749,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7763,10 +7773,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527141</v>
+        <v>527238</v>
       </c>
       <c r="R73" t="n">
-        <v>7087466</v>
+        <v>7087520</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7825,10 +7835,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217804</v>
+        <v>129217911</v>
       </c>
       <c r="B74" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7836,34 +7846,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526927</v>
+        <v>527164</v>
       </c>
       <c r="R74" t="n">
-        <v>7087193</v>
+        <v>7087462</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,11 +7906,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7927,10 +7932,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217808</v>
+        <v>129217853</v>
       </c>
       <c r="B75" t="n">
-        <v>57723</v>
+        <v>82902</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7938,21 +7943,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7962,10 +7967,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526917</v>
+        <v>527133</v>
       </c>
       <c r="R75" t="n">
-        <v>7087144</v>
+        <v>7087390</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,11 +8003,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8032,7 +8032,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>129217825</v>
       </c>
       <c r="B77" t="n">
-        <v>80044</v>
+        <v>80048</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8223,32 +8223,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217912</v>
+        <v>129217921</v>
       </c>
       <c r="B78" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8258,10 +8258,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527089</v>
+        <v>526984</v>
       </c>
       <c r="R78" t="n">
-        <v>7087260</v>
+        <v>7087226</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8325,32 +8325,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217924</v>
+        <v>129217914</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8360,10 +8360,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527289</v>
+        <v>526928</v>
       </c>
       <c r="R79" t="n">
-        <v>7087449</v>
+        <v>7087112</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8396,6 +8396,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8422,10 +8427,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217802</v>
+        <v>129217830</v>
       </c>
       <c r="B80" t="n">
-        <v>57723</v>
+        <v>78052</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8433,21 +8438,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8457,10 +8462,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526934</v>
+        <v>526990</v>
       </c>
       <c r="R80" t="n">
-        <v>7087213</v>
+        <v>7087234</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8493,11 +8498,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8524,10 +8524,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217929</v>
+        <v>129217802</v>
       </c>
       <c r="B81" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8555,14 +8555,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527393</v>
+        <v>526934</v>
       </c>
       <c r="R81" t="n">
-        <v>7087440</v>
+        <v>7087213</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8626,10 +8626,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217841</v>
+        <v>129217929</v>
       </c>
       <c r="B82" t="n">
-        <v>91540</v>
+        <v>57725</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8637,34 +8637,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527375</v>
+        <v>527393</v>
       </c>
       <c r="R82" t="n">
-        <v>7087521</v>
+        <v>7087440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8697,6 +8697,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8723,10 +8728,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217830</v>
+        <v>129217841</v>
       </c>
       <c r="B83" t="n">
-        <v>78048</v>
+        <v>91547</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8734,21 +8739,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228579</v>
+        <v>1204</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8758,10 +8763,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526990</v>
+        <v>527375</v>
       </c>
       <c r="R83" t="n">
-        <v>7087234</v>
+        <v>7087521</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8820,32 +8825,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217921</v>
+        <v>129217912</v>
       </c>
       <c r="B84" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8855,10 +8860,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526984</v>
+        <v>527089</v>
       </c>
       <c r="R84" t="n">
-        <v>7087226</v>
+        <v>7087260</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8895,7 +8900,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8922,32 +8927,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217914</v>
+        <v>129217924</v>
       </c>
       <c r="B85" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8957,10 +8962,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526928</v>
+        <v>527289</v>
       </c>
       <c r="R85" t="n">
-        <v>7087112</v>
+        <v>7087449</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8993,11 +8998,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9024,10 +9024,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217783</v>
+        <v>129217847</v>
       </c>
       <c r="B86" t="n">
-        <v>96905</v>
+        <v>91551</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9035,21 +9035,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527221</v>
+        <v>527069</v>
       </c>
       <c r="R86" t="n">
-        <v>7087348</v>
+        <v>7087323</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217847</v>
+        <v>129217783</v>
       </c>
       <c r="B87" t="n">
-        <v>91544</v>
+        <v>96915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9132,21 +9132,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527069</v>
+        <v>527221</v>
       </c>
       <c r="R87" t="n">
-        <v>7087323</v>
+        <v>7087348</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9218,10 +9218,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217814</v>
+        <v>129217851</v>
       </c>
       <c r="B88" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9229,21 +9229,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>526905</v>
+        <v>527094</v>
       </c>
       <c r="R88" t="n">
-        <v>7087117</v>
+        <v>7087264</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9320,45 +9320,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217915</v>
+        <v>129217814</v>
       </c>
       <c r="B89" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527145</v>
+        <v>526905</v>
       </c>
       <c r="R89" t="n">
-        <v>7087306</v>
+        <v>7087117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9422,45 +9422,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217851</v>
+        <v>129217915</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527094</v>
+        <v>527145</v>
       </c>
       <c r="R90" t="n">
-        <v>7087264</v>
+        <v>7087306</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>80104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217831</v>
+        <v>129217799</v>
       </c>
       <c r="B8" t="n">
-        <v>80104</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527362</v>
+        <v>527399</v>
       </c>
       <c r="R8" t="n">
-        <v>7087507</v>
+        <v>7087454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217813</v>
+        <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>92206</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526901</v>
+        <v>527386</v>
       </c>
       <c r="R9" t="n">
-        <v>7087135</v>
+        <v>7087522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217798</v>
+        <v>129217782</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>96915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527408</v>
+        <v>527172</v>
       </c>
       <c r="R10" t="n">
-        <v>7087464</v>
+        <v>7087341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217856</v>
+        <v>129217813</v>
       </c>
       <c r="B11" t="n">
-        <v>92206</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527386</v>
+        <v>526901</v>
       </c>
       <c r="R11" t="n">
-        <v>7087522</v>
+        <v>7087135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217782</v>
+        <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>96915</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527172</v>
+        <v>527408</v>
       </c>
       <c r="R12" t="n">
-        <v>7087341</v>
+        <v>7087464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2452,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217785</v>
+        <v>129217780</v>
       </c>
       <c r="B20" t="n">
-        <v>91497</v>
+        <v>83015</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527106</v>
+        <v>527179</v>
       </c>
       <c r="R20" t="n">
-        <v>7087220</v>
+        <v>7087518</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,45 +2549,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217797</v>
+        <v>129217925</v>
       </c>
       <c r="B21" t="n">
-        <v>92233</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527368</v>
+        <v>527089</v>
       </c>
       <c r="R21" t="n">
-        <v>7087576</v>
+        <v>7087260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,45 +2646,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217917</v>
+        <v>129217785</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>91497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527273</v>
+        <v>527106</v>
       </c>
       <c r="R22" t="n">
-        <v>7087581</v>
+        <v>7087220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,11 +2717,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2748,32 +2743,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217780</v>
+        <v>129217797</v>
       </c>
       <c r="B23" t="n">
-        <v>83015</v>
+        <v>92233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2783,10 +2778,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527179</v>
+        <v>527368</v>
       </c>
       <c r="R23" t="n">
-        <v>7087518</v>
+        <v>7087576</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2845,32 +2840,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217925</v>
+        <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2880,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527089</v>
+        <v>527273</v>
       </c>
       <c r="R24" t="n">
-        <v>7087260</v>
+        <v>7087581</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3626,45 +3626,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217922</v>
+        <v>129217836</v>
       </c>
       <c r="B32" t="n">
-        <v>56906</v>
+        <v>98669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527122</v>
+        <v>527091</v>
       </c>
       <c r="R32" t="n">
-        <v>7087232</v>
+        <v>7087273</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>56906</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R34" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217845</v>
+        <v>129217803</v>
       </c>
       <c r="B37" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4132,21 +4132,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527173</v>
+        <v>526923</v>
       </c>
       <c r="R37" t="n">
-        <v>7087380</v>
+        <v>7087199</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,6 +4192,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4218,7 +4223,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217803</v>
+        <v>129217821</v>
       </c>
       <c r="B38" t="n">
         <v>57725</v>
@@ -4253,10 +4258,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526923</v>
+        <v>526924</v>
       </c>
       <c r="R38" t="n">
-        <v>7087199</v>
+        <v>7087187</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4293,7 +4298,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4320,10 +4325,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217821</v>
+        <v>129217845</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4331,21 +4336,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4355,10 +4360,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526924</v>
+        <v>527173</v>
       </c>
       <c r="R39" t="n">
-        <v>7087187</v>
+        <v>7087380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,11 +4396,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -7437,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217781</v>
+        <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>83015</v>
+        <v>91533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,21 +7448,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527141</v>
+        <v>527238</v>
       </c>
       <c r="R70" t="n">
-        <v>7087466</v>
+        <v>7087520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217804</v>
+        <v>129217911</v>
       </c>
       <c r="B71" t="n">
-        <v>57725</v>
+        <v>91533</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,34 +7545,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526927</v>
+        <v>527164</v>
       </c>
       <c r="R71" t="n">
-        <v>7087193</v>
+        <v>7087462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7605,11 +7605,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7636,10 +7631,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217808</v>
+        <v>129217853</v>
       </c>
       <c r="B72" t="n">
-        <v>57725</v>
+        <v>82902</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7647,21 +7642,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7671,10 +7666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>526917</v>
+        <v>527133</v>
       </c>
       <c r="R72" t="n">
-        <v>7087144</v>
+        <v>7087390</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7707,11 +7702,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7738,10 +7728,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217786</v>
+        <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>91533</v>
+        <v>83015</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7749,21 +7739,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7773,10 +7763,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527238</v>
+        <v>527141</v>
       </c>
       <c r="R73" t="n">
-        <v>7087520</v>
+        <v>7087466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7835,10 +7825,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217911</v>
+        <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7846,34 +7836,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527164</v>
+        <v>526927</v>
       </c>
       <c r="R74" t="n">
-        <v>7087462</v>
+        <v>7087193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7906,6 +7896,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7932,10 +7927,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217853</v>
+        <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>82902</v>
+        <v>57725</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7943,21 +7938,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7967,10 +7962,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527133</v>
+        <v>526917</v>
       </c>
       <c r="R75" t="n">
-        <v>7087390</v>
+        <v>7087144</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8003,6 +7998,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8223,45 +8223,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217921</v>
+        <v>129217841</v>
       </c>
       <c r="B78" t="n">
-        <v>98669</v>
+        <v>91547</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>526984</v>
+        <v>527375</v>
       </c>
       <c r="R78" t="n">
-        <v>7087226</v>
+        <v>7087521</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8294,11 +8294,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8325,7 +8320,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217914</v>
+        <v>129217921</v>
       </c>
       <c r="B79" t="n">
         <v>98669</v>
@@ -8360,10 +8355,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526928</v>
+        <v>526984</v>
       </c>
       <c r="R79" t="n">
-        <v>7087112</v>
+        <v>7087226</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8400,7 +8395,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8427,45 +8422,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217830</v>
+        <v>129217914</v>
       </c>
       <c r="B80" t="n">
-        <v>78052</v>
+        <v>98669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526990</v>
+        <v>526928</v>
       </c>
       <c r="R80" t="n">
-        <v>7087234</v>
+        <v>7087112</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8498,6 +8493,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8524,10 +8524,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217802</v>
+        <v>129217912</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8535,34 +8535,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526934</v>
+        <v>527089</v>
       </c>
       <c r="R81" t="n">
-        <v>7087213</v>
+        <v>7087260</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8626,10 +8626,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217929</v>
+        <v>129217924</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8637,21 +8637,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8661,10 +8661,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527393</v>
+        <v>527289</v>
       </c>
       <c r="R82" t="n">
-        <v>7087440</v>
+        <v>7087449</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8697,11 +8697,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8728,10 +8723,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217841</v>
+        <v>129217802</v>
       </c>
       <c r="B83" t="n">
-        <v>91547</v>
+        <v>57725</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8739,21 +8734,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8763,10 +8758,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>527375</v>
+        <v>526934</v>
       </c>
       <c r="R83" t="n">
-        <v>7087521</v>
+        <v>7087213</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8799,6 +8794,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8825,10 +8825,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217912</v>
+        <v>129217929</v>
       </c>
       <c r="B84" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8836,21 +8836,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527089</v>
+        <v>527393</v>
       </c>
       <c r="R84" t="n">
-        <v>7087260</v>
+        <v>7087440</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8927,10 +8927,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217924</v>
+        <v>129217830</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>78052</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8938,34 +8938,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527289</v>
+        <v>526990</v>
       </c>
       <c r="R85" t="n">
-        <v>7087449</v>
+        <v>7087234</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217783</v>
+        <v>129217814</v>
       </c>
       <c r="B87" t="n">
-        <v>96915</v>
+        <v>57725</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9132,21 +9132,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527221</v>
+        <v>526905</v>
       </c>
       <c r="R87" t="n">
-        <v>7087348</v>
+        <v>7087117</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9192,6 +9192,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9218,10 +9223,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217851</v>
+        <v>129217783</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>96915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9229,21 +9234,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9253,10 +9258,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527094</v>
+        <v>527221</v>
       </c>
       <c r="R88" t="n">
-        <v>7087264</v>
+        <v>7087348</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9289,11 +9294,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217814</v>
+        <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526905</v>
+        <v>527094</v>
       </c>
       <c r="R89" t="n">
-        <v>7087117</v>
+        <v>7087264</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217849</v>
+        <v>129217918</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526979</v>
+        <v>527262</v>
       </c>
       <c r="R2" t="n">
-        <v>7087143</v>
+        <v>7087588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217850</v>
+        <v>129217849</v>
       </c>
       <c r="B3" t="n">
         <v>79039</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527358</v>
+        <v>526979</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217815</v>
+        <v>129217850</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526883</v>
+        <v>527358</v>
       </c>
       <c r="R4" t="n">
-        <v>7087121</v>
+        <v>7087435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217918</v>
+        <v>129217815</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527262</v>
+        <v>526883</v>
       </c>
       <c r="R5" t="n">
-        <v>7087588</v>
+        <v>7087121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R6" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R8" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,7 +1377,7 @@
         <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>92206</v>
+        <v>92213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129217782</v>
       </c>
       <c r="B10" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>129217928</v>
       </c>
       <c r="B14" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>129217842</v>
       </c>
       <c r="B15" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>129217852</v>
       </c>
       <c r="B16" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>129217840</v>
       </c>
       <c r="B17" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129217795</v>
       </c>
       <c r="B18" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>129217855</v>
       </c>
       <c r="B19" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217780</v>
+        <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>83015</v>
+        <v>92240</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527179</v>
+        <v>527368</v>
       </c>
       <c r="R20" t="n">
-        <v>7087518</v>
+        <v>7087576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,45 +2549,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217925</v>
+        <v>129217785</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527089</v>
+        <v>527106</v>
       </c>
       <c r="R21" t="n">
-        <v>7087260</v>
+        <v>7087220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,45 +2646,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217785</v>
+        <v>129217925</v>
       </c>
       <c r="B22" t="n">
-        <v>91497</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527106</v>
+        <v>527089</v>
       </c>
       <c r="R22" t="n">
-        <v>7087220</v>
+        <v>7087260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,32 +2743,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217797</v>
+        <v>129217780</v>
       </c>
       <c r="B23" t="n">
-        <v>92233</v>
+        <v>83005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527368</v>
+        <v>527179</v>
       </c>
       <c r="R23" t="n">
-        <v>7087576</v>
+        <v>7087518</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
         <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129217789</v>
       </c>
       <c r="B27" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>129217910</v>
       </c>
       <c r="B28" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217836</v>
+        <v>129217820</v>
       </c>
       <c r="B32" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527091</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>7087273</v>
+        <v>7087201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,6 +3697,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3723,10 +3728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>56906</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,16 +3739,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3754,14 +3759,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R33" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3799,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217922</v>
+        <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>56906</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527122</v>
+        <v>527091</v>
       </c>
       <c r="R34" t="n">
-        <v>7087232</v>
+        <v>7087273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3925,7 +3925,7 @@
         <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217803</v>
+        <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>91558</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4132,21 +4132,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526923</v>
+        <v>527173</v>
       </c>
       <c r="R37" t="n">
-        <v>7087199</v>
+        <v>7087380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,11 +4192,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4223,32 +4218,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217821</v>
+        <v>129217833</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4258,10 +4253,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526924</v>
+        <v>527351</v>
       </c>
       <c r="R38" t="n">
-        <v>7087187</v>
+        <v>7087510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4298,7 +4293,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4325,32 +4320,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217845</v>
+        <v>129217835</v>
       </c>
       <c r="B39" t="n">
-        <v>91551</v>
+        <v>98676</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4360,10 +4355,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527173</v>
+        <v>527103</v>
       </c>
       <c r="R39" t="n">
-        <v>7087380</v>
+        <v>7087341</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4422,32 +4417,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4457,10 +4452,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R40" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4497,7 +4492,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4524,32 +4519,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B41" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4559,10 +4554,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R41" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4595,6 +4590,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4624,7 +4624,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4815,32 +4815,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217826</v>
+        <v>129217838</v>
       </c>
       <c r="B44" t="n">
-        <v>80048</v>
+        <v>56906</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527090</v>
+        <v>527239</v>
       </c>
       <c r="R44" t="n">
-        <v>7087261</v>
+        <v>7087332</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4912,32 +4912,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217778</v>
+        <v>129217826</v>
       </c>
       <c r="B45" t="n">
-        <v>83015</v>
+        <v>80048</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>526957</v>
+        <v>527090</v>
       </c>
       <c r="R45" t="n">
-        <v>7087142</v>
+        <v>7087261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217838</v>
+        <v>129217778</v>
       </c>
       <c r="B46" t="n">
-        <v>56906</v>
+        <v>83005</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5020,21 +5020,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527239</v>
+        <v>526957</v>
       </c>
       <c r="R46" t="n">
-        <v>7087332</v>
+        <v>7087142</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5109,7 +5109,7 @@
         <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>129217794</v>
       </c>
       <c r="B52" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5703,65 +5703,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217837</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>526980</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087208</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5798,7 +5778,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5825,7 +5805,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217819</v>
       </c>
       <c r="B54" t="n">
         <v>57725</v>
@@ -5853,17 +5833,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>527070</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087285</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5927,7 +5927,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217800</v>
       </c>
       <c r="B55" t="n">
         <v>57725</v>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>527297</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6029,32 +6029,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217837</v>
+        <v>129217801</v>
       </c>
       <c r="B56" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526980</v>
+        <v>527106</v>
       </c>
       <c r="R56" t="n">
-        <v>7087208</v>
+        <v>7087348</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6233,10 +6233,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217823</v>
+        <v>129217784</v>
       </c>
       <c r="B58" t="n">
-        <v>57885</v>
+        <v>96922</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527374</v>
+        <v>527349</v>
       </c>
       <c r="R58" t="n">
-        <v>7087508</v>
+        <v>7087510</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6304,11 +6304,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>4st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6335,10 +6330,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217784</v>
+        <v>129217823</v>
       </c>
       <c r="B59" t="n">
-        <v>96915</v>
+        <v>57885</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6346,21 +6341,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6370,10 +6365,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527349</v>
+        <v>527374</v>
       </c>
       <c r="R59" t="n">
-        <v>7087510</v>
+        <v>7087508</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6406,6 +6401,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6435,7 +6435,7 @@
         <v>129217832</v>
       </c>
       <c r="B60" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6738,45 +6738,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217829</v>
+        <v>129217913</v>
       </c>
       <c r="B63" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527138</v>
+        <v>526924</v>
       </c>
       <c r="R63" t="n">
-        <v>7087472</v>
+        <v>7087085</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,6 +6809,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6835,32 +6840,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217827</v>
+        <v>129217829</v>
       </c>
       <c r="B64" t="n">
-        <v>91988</v>
+        <v>91825</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6870,10 +6875,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527136</v>
+        <v>527138</v>
       </c>
       <c r="R64" t="n">
-        <v>7087471</v>
+        <v>7087472</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6932,32 +6937,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217854</v>
+        <v>129217827</v>
       </c>
       <c r="B65" t="n">
-        <v>82902</v>
+        <v>91995</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6967,10 +6972,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527015</v>
+        <v>527136</v>
       </c>
       <c r="R65" t="n">
-        <v>7087228</v>
+        <v>7087471</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7029,45 +7034,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217913</v>
+        <v>129217854</v>
       </c>
       <c r="B66" t="n">
-        <v>98669</v>
+        <v>82871</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526924</v>
+        <v>527015</v>
       </c>
       <c r="R66" t="n">
-        <v>7087085</v>
+        <v>7087228</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7100,11 +7105,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7440,7 +7440,7 @@
         <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>129217911</v>
       </c>
       <c r="B71" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>129217853</v>
       </c>
       <c r="B72" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>83015</v>
+        <v>83005</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91529</v>
+        <v>91536</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>129217841</v>
       </c>
       <c r="B78" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8320,32 +8320,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217921</v>
+        <v>129217924</v>
       </c>
       <c r="B79" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8355,10 +8355,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526984</v>
+        <v>527289</v>
       </c>
       <c r="R79" t="n">
-        <v>7087226</v>
+        <v>7087449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8391,11 +8391,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8422,32 +8417,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217914</v>
+        <v>129217912</v>
       </c>
       <c r="B80" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8457,10 +8452,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526928</v>
+        <v>527089</v>
       </c>
       <c r="R80" t="n">
-        <v>7087112</v>
+        <v>7087260</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8497,7 +8492,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8524,10 +8519,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217912</v>
+        <v>129217802</v>
       </c>
       <c r="B81" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8535,34 +8530,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527089</v>
+        <v>526934</v>
       </c>
       <c r="R81" t="n">
-        <v>7087260</v>
+        <v>7087213</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8599,7 +8594,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8626,10 +8621,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217924</v>
+        <v>129217929</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8637,21 +8632,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8661,10 +8656,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527289</v>
+        <v>527393</v>
       </c>
       <c r="R82" t="n">
-        <v>7087449</v>
+        <v>7087440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8697,6 +8692,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8723,45 +8723,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217802</v>
+        <v>129217921</v>
       </c>
       <c r="B83" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526934</v>
+        <v>526984</v>
       </c>
       <c r="R83" t="n">
-        <v>7087213</v>
+        <v>7087226</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8825,32 +8825,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217929</v>
+        <v>129217914</v>
       </c>
       <c r="B84" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527393</v>
+        <v>526928</v>
       </c>
       <c r="R84" t="n">
-        <v>7087440</v>
+        <v>7087112</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9024,10 +9024,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217847</v>
+        <v>129217783</v>
       </c>
       <c r="B86" t="n">
-        <v>91551</v>
+        <v>96922</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9035,21 +9035,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527069</v>
+        <v>527221</v>
       </c>
       <c r="R86" t="n">
-        <v>7087323</v>
+        <v>7087348</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9223,45 +9223,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217783</v>
+        <v>129217915</v>
       </c>
       <c r="B88" t="n">
-        <v>96915</v>
+        <v>98676</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527221</v>
+        <v>527145</v>
       </c>
       <c r="R88" t="n">
-        <v>7087348</v>
+        <v>7087306</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9294,6 +9294,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9320,10 +9325,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217851</v>
+        <v>129217847</v>
       </c>
       <c r="B89" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9336,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9360,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527094</v>
+        <v>527069</v>
       </c>
       <c r="R89" t="n">
-        <v>7087264</v>
+        <v>7087323</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9391,11 +9396,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9422,45 +9422,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217915</v>
+        <v>129217851</v>
       </c>
       <c r="B90" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527145</v>
+        <v>527094</v>
       </c>
       <c r="R90" t="n">
-        <v>7087306</v>
+        <v>7087264</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217918</v>
+        <v>129217815</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527262</v>
+        <v>526883</v>
       </c>
       <c r="R2" t="n">
-        <v>7087588</v>
+        <v>7087121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +780,7 @@
         <v>129217849</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129217850</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217815</v>
+        <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526883</v>
+        <v>527262</v>
       </c>
       <c r="R5" t="n">
-        <v>7087121</v>
+        <v>7087588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R6" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,7 +1178,7 @@
         <v>129217831</v>
       </c>
       <c r="B7" t="n">
-        <v>80104</v>
+        <v>80106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R8" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,7 +1377,7 @@
         <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>92213</v>
+        <v>92215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217782</v>
+        <v>129217813</v>
       </c>
       <c r="B10" t="n">
-        <v>96922</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527172</v>
+        <v>526901</v>
       </c>
       <c r="R10" t="n">
-        <v>7087341</v>
+        <v>7087135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217813</v>
+        <v>129217798</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526901</v>
+        <v>527408</v>
       </c>
       <c r="R11" t="n">
-        <v>7087135</v>
+        <v>7087464</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1648,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217798</v>
+        <v>129217782</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>96924</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527408</v>
+        <v>527172</v>
       </c>
       <c r="R12" t="n">
-        <v>7087464</v>
+        <v>7087341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,7 +1775,7 @@
         <v>129217927</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217928</v>
+        <v>129217795</v>
       </c>
       <c r="B14" t="n">
-        <v>82871</v>
+        <v>91542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527359</v>
+        <v>527123</v>
       </c>
       <c r="R14" t="n">
-        <v>7087548</v>
+        <v>7087425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1948,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217842</v>
+        <v>129217855</v>
       </c>
       <c r="B15" t="n">
-        <v>91554</v>
+        <v>82873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527385</v>
+        <v>527012</v>
       </c>
       <c r="R15" t="n">
-        <v>7087528</v>
+        <v>7087233</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217852</v>
+        <v>129217840</v>
       </c>
       <c r="B16" t="n">
-        <v>82871</v>
+        <v>91556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527265</v>
+        <v>527386</v>
       </c>
       <c r="R16" t="n">
-        <v>7087520</v>
+        <v>7087517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,10 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217840</v>
+        <v>129217928</v>
       </c>
       <c r="B17" t="n">
-        <v>91554</v>
+        <v>82873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,34 +2171,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527386</v>
+        <v>527359</v>
       </c>
       <c r="R17" t="n">
-        <v>7087517</v>
+        <v>7087548</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,6 +2239,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217795</v>
+        <v>129217842</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>91556</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527123</v>
+        <v>527385</v>
       </c>
       <c r="R18" t="n">
-        <v>7087425</v>
+        <v>7087528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217855</v>
+        <v>129217852</v>
       </c>
       <c r="B19" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527012</v>
+        <v>527265</v>
       </c>
       <c r="R19" t="n">
-        <v>7087233</v>
+        <v>7087520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,7 +2455,7 @@
         <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129217785</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217925</v>
+        <v>129217780</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>83007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2657,34 +2657,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527089</v>
+        <v>527179</v>
       </c>
       <c r="R22" t="n">
-        <v>7087260</v>
+        <v>7087518</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217780</v>
+        <v>129217925</v>
       </c>
       <c r="B23" t="n">
-        <v>83005</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527179</v>
+        <v>527089</v>
       </c>
       <c r="R23" t="n">
-        <v>7087518</v>
+        <v>7087260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
         <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129217789</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>129217910</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>129217926</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>56908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3657,14 +3657,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R32" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,11 +3697,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3728,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217922</v>
+        <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>56906</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3739,16 +3734,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3759,14 +3754,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527122</v>
+        <v>527034</v>
       </c>
       <c r="R33" t="n">
-        <v>7087232</v>
+        <v>7087201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3799,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3828,7 +3828,7 @@
         <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>129217833</v>
       </c>
       <c r="B38" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>129217835</v>
       </c>
       <c r="B39" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>129217803</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>129217821</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4815,32 +4815,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217838</v>
+        <v>129217826</v>
       </c>
       <c r="B44" t="n">
-        <v>56906</v>
+        <v>80050</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527239</v>
+        <v>527090</v>
       </c>
       <c r="R44" t="n">
-        <v>7087332</v>
+        <v>7087261</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4912,32 +4912,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217826</v>
+        <v>129217778</v>
       </c>
       <c r="B45" t="n">
-        <v>80048</v>
+        <v>83007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527090</v>
+        <v>526957</v>
       </c>
       <c r="R45" t="n">
-        <v>7087261</v>
+        <v>7087142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217778</v>
+        <v>129217838</v>
       </c>
       <c r="B46" t="n">
-        <v>83005</v>
+        <v>56908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5020,21 +5020,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>526957</v>
+        <v>527239</v>
       </c>
       <c r="R46" t="n">
-        <v>7087142</v>
+        <v>7087332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217790</v>
+        <v>129217923</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5117,34 +5117,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527357</v>
+        <v>527150</v>
       </c>
       <c r="R47" t="n">
-        <v>7087574</v>
+        <v>7087278</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5177,6 +5177,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5203,10 +5208,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5214,34 +5219,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R48" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5274,11 +5279,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5308,7 +5308,7 @@
         <v>129217844</v>
       </c>
       <c r="B49" t="n">
-        <v>57717</v>
+        <v>57719</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>129217805</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>129217794</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>129217837</v>
       </c>
       <c r="B53" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>129217819</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>129217800</v>
       </c>
       <c r="B55" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>129217801</v>
       </c>
       <c r="B56" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6131,10 +6131,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217848</v>
+        <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>96924</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6142,21 +6142,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527106</v>
+        <v>527349</v>
       </c>
       <c r="R57" t="n">
-        <v>7087367</v>
+        <v>7087510</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6202,11 +6202,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6233,10 +6228,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217784</v>
+        <v>129217848</v>
       </c>
       <c r="B58" t="n">
-        <v>96922</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6244,21 +6239,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6268,10 +6263,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527349</v>
+        <v>527106</v>
       </c>
       <c r="R58" t="n">
-        <v>7087510</v>
+        <v>7087367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6304,6 +6299,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6333,7 +6333,7 @@
         <v>129217823</v>
       </c>
       <c r="B59" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>129217832</v>
       </c>
       <c r="B60" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6738,45 +6738,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217913</v>
+        <v>129217806</v>
       </c>
       <c r="B63" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>526924</v>
+        <v>526925</v>
       </c>
       <c r="R63" t="n">
-        <v>7087085</v>
+        <v>7087175</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6840,10 +6840,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217829</v>
+        <v>129217810</v>
       </c>
       <c r="B64" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6851,21 +6851,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527138</v>
+        <v>526914</v>
       </c>
       <c r="R64" t="n">
-        <v>7087472</v>
+        <v>7087139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6911,6 +6911,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6937,32 +6942,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217827</v>
+        <v>129217818</v>
       </c>
       <c r="B65" t="n">
-        <v>91995</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6972,10 +6977,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527136</v>
+        <v>527359</v>
       </c>
       <c r="R65" t="n">
-        <v>7087471</v>
+        <v>7087452</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7008,6 +7013,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7034,10 +7044,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217854</v>
+        <v>129217829</v>
       </c>
       <c r="B66" t="n">
-        <v>82871</v>
+        <v>91827</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7045,21 +7055,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7069,10 +7079,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527015</v>
+        <v>527138</v>
       </c>
       <c r="R66" t="n">
-        <v>7087228</v>
+        <v>7087472</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7131,10 +7141,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217806</v>
+        <v>129217854</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>82873</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7142,21 +7152,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7166,10 +7176,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526925</v>
+        <v>527015</v>
       </c>
       <c r="R67" t="n">
-        <v>7087175</v>
+        <v>7087228</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7202,11 +7212,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7233,32 +7238,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217810</v>
+        <v>129217827</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>91997</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7268,10 +7273,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>526914</v>
+        <v>527136</v>
       </c>
       <c r="R68" t="n">
-        <v>7087139</v>
+        <v>7087471</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7304,11 +7309,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7335,45 +7335,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217818</v>
+        <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527359</v>
+        <v>526924</v>
       </c>
       <c r="R69" t="n">
-        <v>7087452</v>
+        <v>7087085</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7440,7 +7440,7 @@
         <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217911</v>
+        <v>129217853</v>
       </c>
       <c r="B71" t="n">
-        <v>91540</v>
+        <v>82873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,34 +7545,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527164</v>
+        <v>527133</v>
       </c>
       <c r="R71" t="n">
-        <v>7087462</v>
+        <v>7087390</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217853</v>
+        <v>129217911</v>
       </c>
       <c r="B72" t="n">
-        <v>82871</v>
+        <v>91542</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,34 +7642,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527133</v>
+        <v>527164</v>
       </c>
       <c r="R72" t="n">
-        <v>7087390</v>
+        <v>7087462</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7731,7 +7731,7 @@
         <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>129217825</v>
       </c>
       <c r="B77" t="n">
-        <v>80048</v>
+        <v>80050</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217841</v>
+        <v>129217912</v>
       </c>
       <c r="B78" t="n">
-        <v>91554</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8234,34 +8234,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527375</v>
+        <v>527089</v>
       </c>
       <c r="R78" t="n">
-        <v>7087521</v>
+        <v>7087260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8294,6 +8294,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8323,7 +8328,7 @@
         <v>129217924</v>
       </c>
       <c r="B79" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8417,10 +8422,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217912</v>
+        <v>129217929</v>
       </c>
       <c r="B80" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8428,21 +8433,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8452,10 +8457,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527089</v>
+        <v>527393</v>
       </c>
       <c r="R80" t="n">
-        <v>7087260</v>
+        <v>7087440</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8492,7 +8497,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8519,10 +8524,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217802</v>
+        <v>129217830</v>
       </c>
       <c r="B81" t="n">
-        <v>57725</v>
+        <v>78054</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8530,21 +8535,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8554,10 +8559,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526934</v>
+        <v>526990</v>
       </c>
       <c r="R81" t="n">
-        <v>7087213</v>
+        <v>7087234</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8590,11 +8595,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8621,10 +8621,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217929</v>
+        <v>129217841</v>
       </c>
       <c r="B82" t="n">
-        <v>57725</v>
+        <v>91556</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8632,34 +8632,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527393</v>
+        <v>527375</v>
       </c>
       <c r="R82" t="n">
-        <v>7087440</v>
+        <v>7087521</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8692,11 +8692,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8723,45 +8718,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217921</v>
+        <v>129217802</v>
       </c>
       <c r="B83" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526984</v>
+        <v>526934</v>
       </c>
       <c r="R83" t="n">
-        <v>7087226</v>
+        <v>7087213</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8798,7 +8793,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8828,7 +8823,7 @@
         <v>129217914</v>
       </c>
       <c r="B84" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8927,45 +8922,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217830</v>
+        <v>129217921</v>
       </c>
       <c r="B85" t="n">
-        <v>78052</v>
+        <v>98678</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526990</v>
+        <v>526984</v>
       </c>
       <c r="R85" t="n">
-        <v>7087234</v>
+        <v>7087226</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8998,6 +8993,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9027,7 +9027,7 @@
         <v>129217783</v>
       </c>
       <c r="B86" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217814</v>
+        <v>129217847</v>
       </c>
       <c r="B87" t="n">
-        <v>57725</v>
+        <v>91560</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9132,21 +9132,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526905</v>
+        <v>527069</v>
       </c>
       <c r="R87" t="n">
-        <v>7087117</v>
+        <v>7087323</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9192,11 +9192,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9226,7 +9221,7 @@
         <v>129217915</v>
       </c>
       <c r="B88" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9325,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217847</v>
+        <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9336,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9360,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527069</v>
+        <v>527094</v>
       </c>
       <c r="R89" t="n">
-        <v>7087323</v>
+        <v>7087264</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9396,6 +9391,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9422,10 +9422,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217851</v>
+        <v>129217814</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9433,21 +9433,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527094</v>
+        <v>526905</v>
       </c>
       <c r="R90" t="n">
-        <v>7087264</v>
+        <v>7087117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217815</v>
+        <v>129217849</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526883</v>
+        <v>526979</v>
       </c>
       <c r="R2" t="n">
-        <v>7087121</v>
+        <v>7087143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217849</v>
+        <v>129217850</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526979</v>
+        <v>527358</v>
       </c>
       <c r="R3" t="n">
-        <v>7087143</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217850</v>
+        <v>129217815</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527358</v>
+        <v>526883</v>
       </c>
       <c r="R4" t="n">
-        <v>7087435</v>
+        <v>7087121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217831</v>
+        <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>80106</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527362</v>
+        <v>527399</v>
       </c>
       <c r="R7" t="n">
-        <v>7087507</v>
+        <v>7087454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R8" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217813</v>
+        <v>129217782</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>96924</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526901</v>
+        <v>527172</v>
       </c>
       <c r="R10" t="n">
-        <v>7087135</v>
+        <v>7087341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,7 +1568,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217798</v>
+        <v>129217813</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1608,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527408</v>
+        <v>526901</v>
       </c>
       <c r="R11" t="n">
-        <v>7087464</v>
+        <v>7087135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1643,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217782</v>
+        <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>96924</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527172</v>
+        <v>527408</v>
       </c>
       <c r="R12" t="n">
-        <v>7087341</v>
+        <v>7087464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217795</v>
+        <v>129217842</v>
       </c>
       <c r="B14" t="n">
-        <v>91542</v>
+        <v>91556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527123</v>
+        <v>527385</v>
       </c>
       <c r="R14" t="n">
-        <v>7087425</v>
+        <v>7087528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217855</v>
+        <v>129217840</v>
       </c>
       <c r="B15" t="n">
-        <v>82873</v>
+        <v>91556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527012</v>
+        <v>527386</v>
       </c>
       <c r="R15" t="n">
-        <v>7087233</v>
+        <v>7087517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217840</v>
+        <v>129217795</v>
       </c>
       <c r="B16" t="n">
-        <v>91556</v>
+        <v>91542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527386</v>
+        <v>527123</v>
       </c>
       <c r="R16" t="n">
-        <v>7087517</v>
+        <v>7087425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217842</v>
+        <v>129217852</v>
       </c>
       <c r="B18" t="n">
-        <v>91556</v>
+        <v>82873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527385</v>
+        <v>527265</v>
       </c>
       <c r="R18" t="n">
-        <v>7087528</v>
+        <v>7087520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217852</v>
+        <v>129217855</v>
       </c>
       <c r="B19" t="n">
         <v>82873</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527265</v>
+        <v>527012</v>
       </c>
       <c r="R19" t="n">
-        <v>7087520</v>
+        <v>7087233</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,45 +2549,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217785</v>
+        <v>129217925</v>
       </c>
       <c r="B21" t="n">
-        <v>91506</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527106</v>
+        <v>527089</v>
       </c>
       <c r="R21" t="n">
-        <v>7087220</v>
+        <v>7087260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2743,45 +2743,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217925</v>
+        <v>129217785</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>91506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527089</v>
+        <v>527106</v>
       </c>
       <c r="R23" t="n">
-        <v>7087260</v>
+        <v>7087220</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217922</v>
+        <v>129217820</v>
       </c>
       <c r="B32" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3657,14 +3657,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527122</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>7087232</v>
+        <v>7087201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,6 +3697,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3723,32 +3728,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217820</v>
+        <v>129217836</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3763,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527034</v>
+        <v>527091</v>
       </c>
       <c r="R33" t="n">
-        <v>7087201</v>
+        <v>7087273</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3799,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>56908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R34" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4121,32 +4121,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217845</v>
+        <v>129217833</v>
       </c>
       <c r="B37" t="n">
-        <v>91560</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527173</v>
+        <v>527351</v>
       </c>
       <c r="R37" t="n">
-        <v>7087380</v>
+        <v>7087510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,6 +4192,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4218,7 +4223,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217833</v>
+        <v>129217835</v>
       </c>
       <c r="B38" t="n">
         <v>98678</v>
@@ -4253,10 +4258,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527351</v>
+        <v>527103</v>
       </c>
       <c r="R38" t="n">
-        <v>7087510</v>
+        <v>7087341</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4289,11 +4294,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4320,32 +4320,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217835</v>
+        <v>129217803</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527103</v>
+        <v>526923</v>
       </c>
       <c r="R39" t="n">
-        <v>7087341</v>
+        <v>7087199</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,6 +4391,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4417,7 +4422,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217803</v>
+        <v>129217821</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4452,10 +4457,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526923</v>
+        <v>526924</v>
       </c>
       <c r="R40" t="n">
-        <v>7087199</v>
+        <v>7087187</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,7 +4497,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4519,10 +4524,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217821</v>
+        <v>129217845</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4530,21 +4535,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4554,10 +4559,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526924</v>
+        <v>527173</v>
       </c>
       <c r="R41" t="n">
-        <v>7087187</v>
+        <v>7087380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4590,11 +4595,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,10 +5106,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5117,34 +5117,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R47" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5177,11 +5177,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5208,45 +5203,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217790</v>
+        <v>129217920</v>
       </c>
       <c r="B48" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527357</v>
+        <v>527064</v>
       </c>
       <c r="R48" t="n">
-        <v>7087574</v>
+        <v>7087252</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,6 +5274,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5305,45 +5305,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217844</v>
+        <v>129217923</v>
       </c>
       <c r="B49" t="n">
-        <v>57719</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527355</v>
+        <v>527150</v>
       </c>
       <c r="R49" t="n">
-        <v>7087521</v>
+        <v>7087278</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,6 +5376,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5402,32 +5407,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217805</v>
+        <v>129217844</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57719</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>526924</v>
+        <v>527355</v>
       </c>
       <c r="R50" t="n">
-        <v>7087183</v>
+        <v>7087521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,11 +5478,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5504,45 +5504,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217920</v>
+        <v>129217805</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527064</v>
+        <v>526924</v>
       </c>
       <c r="R51" t="n">
-        <v>7087252</v>
+        <v>7087183</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5703,45 +5703,65 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217837</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>526980</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087208</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5778,7 +5798,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5805,7 +5825,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5833,37 +5853,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5927,7 +5927,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6029,32 +6029,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217801</v>
+        <v>129217837</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527106</v>
+        <v>526980</v>
       </c>
       <c r="R56" t="n">
-        <v>7087348</v>
+        <v>7087208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6131,10 +6131,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217784</v>
+        <v>129217848</v>
       </c>
       <c r="B57" t="n">
-        <v>96924</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6142,21 +6142,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527349</v>
+        <v>527106</v>
       </c>
       <c r="R57" t="n">
-        <v>7087510</v>
+        <v>7087367</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6202,6 +6202,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6228,32 +6233,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217848</v>
+        <v>129217832</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6263,10 +6268,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527106</v>
+        <v>527149</v>
       </c>
       <c r="R58" t="n">
-        <v>7087367</v>
+        <v>7087289</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6303,7 +6308,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6330,45 +6335,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217823</v>
+        <v>129217919</v>
       </c>
       <c r="B59" t="n">
-        <v>57887</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527374</v>
+        <v>527135</v>
       </c>
       <c r="R59" t="n">
-        <v>7087508</v>
+        <v>7087449</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6405,7 +6410,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6432,7 +6437,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217832</v>
+        <v>129217834</v>
       </c>
       <c r="B60" t="n">
         <v>98678</v>
@@ -6467,10 +6472,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527149</v>
+        <v>527268</v>
       </c>
       <c r="R60" t="n">
-        <v>7087289</v>
+        <v>7087590</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6507,7 +6512,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6534,45 +6539,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217919</v>
+        <v>129217784</v>
       </c>
       <c r="B61" t="n">
-        <v>98678</v>
+        <v>96924</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527135</v>
+        <v>527349</v>
       </c>
       <c r="R61" t="n">
-        <v>7087449</v>
+        <v>7087510</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,11 +6610,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6636,32 +6636,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217834</v>
+        <v>129217823</v>
       </c>
       <c r="B62" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527268</v>
+        <v>527374</v>
       </c>
       <c r="R62" t="n">
-        <v>7087590</v>
+        <v>7087508</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217806</v>
+        <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>526925</v>
+        <v>527138</v>
       </c>
       <c r="R63" t="n">
-        <v>7087175</v>
+        <v>7087472</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,11 +6809,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6840,7 +6835,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217810</v>
+        <v>129217806</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -6875,10 +6870,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526914</v>
+        <v>526925</v>
       </c>
       <c r="R64" t="n">
-        <v>7087139</v>
+        <v>7087175</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6915,7 +6910,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6942,7 +6937,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217818</v>
+        <v>129217810</v>
       </c>
       <c r="B65" t="n">
         <v>57727</v>
@@ -6977,10 +6972,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527359</v>
+        <v>526914</v>
       </c>
       <c r="R65" t="n">
-        <v>7087452</v>
+        <v>7087139</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7017,7 +7012,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7044,10 +7039,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217829</v>
+        <v>129217818</v>
       </c>
       <c r="B66" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7055,21 +7050,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7079,10 +7074,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527138</v>
+        <v>527359</v>
       </c>
       <c r="R66" t="n">
-        <v>7087472</v>
+        <v>7087452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7115,6 +7110,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7141,45 +7141,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217854</v>
+        <v>129217913</v>
       </c>
       <c r="B67" t="n">
-        <v>82873</v>
+        <v>98678</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527015</v>
+        <v>526924</v>
       </c>
       <c r="R67" t="n">
-        <v>7087228</v>
+        <v>7087085</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7212,6 +7212,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7335,45 +7340,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217913</v>
+        <v>129217854</v>
       </c>
       <c r="B69" t="n">
-        <v>98678</v>
+        <v>82873</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526924</v>
+        <v>527015</v>
       </c>
       <c r="R69" t="n">
-        <v>7087085</v>
+        <v>7087228</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7406,11 +7411,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7437,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217786</v>
+        <v>129217781</v>
       </c>
       <c r="B70" t="n">
-        <v>91542</v>
+        <v>83007</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,21 +7448,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527238</v>
+        <v>527141</v>
       </c>
       <c r="R70" t="n">
-        <v>7087520</v>
+        <v>7087466</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217911</v>
+        <v>129217804</v>
       </c>
       <c r="B72" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,34 +7642,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527164</v>
+        <v>526927</v>
       </c>
       <c r="R72" t="n">
-        <v>7087462</v>
+        <v>7087193</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,6 +7702,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7728,10 +7733,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217781</v>
+        <v>129217808</v>
       </c>
       <c r="B73" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7739,21 +7744,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7763,10 +7768,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527141</v>
+        <v>526917</v>
       </c>
       <c r="R73" t="n">
-        <v>7087466</v>
+        <v>7087144</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7799,6 +7804,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7825,10 +7835,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217804</v>
+        <v>129217786</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7836,21 +7846,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7860,10 +7870,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526927</v>
+        <v>527238</v>
       </c>
       <c r="R74" t="n">
-        <v>7087193</v>
+        <v>7087520</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,11 +7906,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7927,10 +7932,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217808</v>
+        <v>129217911</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7938,34 +7943,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526917</v>
+        <v>527164</v>
       </c>
       <c r="R75" t="n">
-        <v>7087144</v>
+        <v>7087462</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,11 +8003,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8223,10 +8223,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217912</v>
+        <v>129217924</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8234,21 +8234,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8258,10 +8258,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527089</v>
+        <v>527289</v>
       </c>
       <c r="R78" t="n">
-        <v>7087260</v>
+        <v>7087449</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8294,11 +8294,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8325,10 +8320,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217924</v>
+        <v>129217912</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8336,21 +8331,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8360,10 +8355,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527289</v>
+        <v>527089</v>
       </c>
       <c r="R79" t="n">
-        <v>7087449</v>
+        <v>7087260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8396,6 +8391,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8422,7 +8422,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217929</v>
+        <v>129217802</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8453,14 +8453,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527393</v>
+        <v>526934</v>
       </c>
       <c r="R80" t="n">
-        <v>7087440</v>
+        <v>7087213</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8524,10 +8524,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217830</v>
+        <v>129217929</v>
       </c>
       <c r="B81" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8535,34 +8535,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526990</v>
+        <v>527393</v>
       </c>
       <c r="R81" t="n">
-        <v>7087234</v>
+        <v>7087440</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8595,6 +8595,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8718,45 +8723,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217802</v>
+        <v>129217921</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526934</v>
+        <v>526984</v>
       </c>
       <c r="R83" t="n">
-        <v>7087213</v>
+        <v>7087226</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8793,7 +8798,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8922,45 +8927,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217921</v>
+        <v>129217830</v>
       </c>
       <c r="B85" t="n">
-        <v>98678</v>
+        <v>78054</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526984</v>
+        <v>526990</v>
       </c>
       <c r="R85" t="n">
-        <v>7087226</v>
+        <v>7087234</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8993,11 +8998,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9218,45 +9218,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217915</v>
+        <v>129217851</v>
       </c>
       <c r="B88" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527145</v>
+        <v>527094</v>
       </c>
       <c r="R88" t="n">
-        <v>7087306</v>
+        <v>7087264</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9320,10 +9320,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217851</v>
+        <v>129217814</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9331,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527094</v>
+        <v>526905</v>
       </c>
       <c r="R89" t="n">
-        <v>7087264</v>
+        <v>7087117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9422,45 +9422,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217814</v>
+        <v>129217915</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>526905</v>
+        <v>527145</v>
       </c>
       <c r="R90" t="n">
-        <v>7087117</v>
+        <v>7087306</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217849</v>
+        <v>129217815</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526979</v>
+        <v>526883</v>
       </c>
       <c r="R2" t="n">
-        <v>7087143</v>
+        <v>7087121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,45 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217850</v>
+        <v>129217918</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527358</v>
+        <v>527262</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217815</v>
+        <v>129217849</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526883</v>
+        <v>526979</v>
       </c>
       <c r="R4" t="n">
-        <v>7087121</v>
+        <v>7087143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217918</v>
+        <v>129217850</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527262</v>
+        <v>527358</v>
       </c>
       <c r="R5" t="n">
-        <v>7087588</v>
+        <v>7087435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217856</v>
+        <v>129217813</v>
       </c>
       <c r="B9" t="n">
-        <v>92215</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527386</v>
+        <v>526901</v>
       </c>
       <c r="R9" t="n">
-        <v>7087522</v>
+        <v>7087135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217782</v>
+        <v>129217798</v>
       </c>
       <c r="B10" t="n">
-        <v>96924</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527172</v>
+        <v>527408</v>
       </c>
       <c r="R10" t="n">
-        <v>7087341</v>
+        <v>7087464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,32 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217813</v>
+        <v>129217856</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526901</v>
+        <v>527386</v>
       </c>
       <c r="R11" t="n">
-        <v>7087135</v>
+        <v>7087522</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1639,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217798</v>
+        <v>129217782</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>96924</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527408</v>
+        <v>527172</v>
       </c>
       <c r="R12" t="n">
-        <v>7087464</v>
+        <v>7087341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217789</v>
+        <v>129217926</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527376</v>
+        <v>527029</v>
       </c>
       <c r="R27" t="n">
-        <v>7087516</v>
+        <v>7087194</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217910</v>
+        <v>129217807</v>
       </c>
       <c r="B28" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,34 +3244,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527288</v>
+        <v>526921</v>
       </c>
       <c r="R28" t="n">
-        <v>7087491</v>
+        <v>7087159</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,6 +3304,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217926</v>
+        <v>129217789</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,34 +3346,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527029</v>
+        <v>527376</v>
       </c>
       <c r="R29" t="n">
-        <v>7087194</v>
+        <v>7087516</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217807</v>
+        <v>129217910</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3438,34 +3443,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>526921</v>
+        <v>527288</v>
       </c>
       <c r="R30" t="n">
-        <v>7087159</v>
+        <v>7087491</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3657,14 +3657,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R32" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,11 +3697,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3728,32 +3723,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217836</v>
+        <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3763,10 +3758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527091</v>
+        <v>527034</v>
       </c>
       <c r="R33" t="n">
-        <v>7087273</v>
+        <v>7087201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3799,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217922</v>
+        <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>56908</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527122</v>
+        <v>527091</v>
       </c>
       <c r="R34" t="n">
-        <v>7087232</v>
+        <v>7087273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4320,10 +4320,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217803</v>
+        <v>129217845</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4331,21 +4331,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4355,10 +4355,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526923</v>
+        <v>527173</v>
       </c>
       <c r="R39" t="n">
-        <v>7087199</v>
+        <v>7087380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,11 +4391,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4422,7 +4417,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217821</v>
+        <v>129217803</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4457,10 +4452,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526924</v>
+        <v>526923</v>
       </c>
       <c r="R40" t="n">
-        <v>7087187</v>
+        <v>7087199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4497,7 +4492,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4524,10 +4519,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217845</v>
+        <v>129217821</v>
       </c>
       <c r="B41" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4535,21 +4530,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4559,10 +4554,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527173</v>
+        <v>526924</v>
       </c>
       <c r="R41" t="n">
-        <v>7087380</v>
+        <v>7087187</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4595,6 +4590,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5203,45 +5203,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217920</v>
+        <v>129217844</v>
       </c>
       <c r="B48" t="n">
-        <v>98678</v>
+        <v>57719</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527064</v>
+        <v>527355</v>
       </c>
       <c r="R48" t="n">
-        <v>7087252</v>
+        <v>7087521</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5274,11 +5274,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5305,10 +5300,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217923</v>
+        <v>129217805</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5316,34 +5311,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527150</v>
+        <v>526924</v>
       </c>
       <c r="R49" t="n">
-        <v>7087278</v>
+        <v>7087183</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5380,7 +5375,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5407,45 +5402,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217844</v>
+        <v>129217923</v>
       </c>
       <c r="B50" t="n">
-        <v>57719</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527355</v>
+        <v>527150</v>
       </c>
       <c r="R50" t="n">
-        <v>7087521</v>
+        <v>7087278</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5478,6 +5473,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5504,45 +5504,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217805</v>
+        <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>526924</v>
+        <v>527064</v>
       </c>
       <c r="R51" t="n">
-        <v>7087183</v>
+        <v>7087252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6233,32 +6233,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217832</v>
+        <v>129217823</v>
       </c>
       <c r="B58" t="n">
-        <v>98678</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527149</v>
+        <v>527374</v>
       </c>
       <c r="R58" t="n">
-        <v>7087289</v>
+        <v>7087508</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6335,45 +6335,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217919</v>
+        <v>129217784</v>
       </c>
       <c r="B59" t="n">
-        <v>98678</v>
+        <v>96924</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527135</v>
+        <v>527349</v>
       </c>
       <c r="R59" t="n">
-        <v>7087449</v>
+        <v>7087510</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6406,11 +6406,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6437,7 +6432,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217834</v>
+        <v>129217832</v>
       </c>
       <c r="B60" t="n">
         <v>98678</v>
@@ -6472,10 +6467,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527268</v>
+        <v>527149</v>
       </c>
       <c r="R60" t="n">
-        <v>7087590</v>
+        <v>7087289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6512,7 +6507,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6539,45 +6534,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217784</v>
+        <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>96924</v>
+        <v>98678</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527349</v>
+        <v>527135</v>
       </c>
       <c r="R61" t="n">
-        <v>7087510</v>
+        <v>7087449</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6610,6 +6605,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6636,32 +6636,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217823</v>
+        <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>57887</v>
+        <v>98678</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6671,10 +6671,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527374</v>
+        <v>527268</v>
       </c>
       <c r="R62" t="n">
-        <v>7087508</v>
+        <v>7087590</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6738,10 +6738,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217829</v>
+        <v>129217806</v>
       </c>
       <c r="B63" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527138</v>
+        <v>526925</v>
       </c>
       <c r="R63" t="n">
-        <v>7087472</v>
+        <v>7087175</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,6 +6809,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6835,7 +6840,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217806</v>
+        <v>129217810</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -6870,10 +6875,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526925</v>
+        <v>526914</v>
       </c>
       <c r="R64" t="n">
-        <v>7087175</v>
+        <v>7087139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6910,7 +6915,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6937,7 +6942,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217810</v>
+        <v>129217818</v>
       </c>
       <c r="B65" t="n">
         <v>57727</v>
@@ -6972,10 +6977,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526914</v>
+        <v>527359</v>
       </c>
       <c r="R65" t="n">
-        <v>7087139</v>
+        <v>7087452</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7012,7 +7017,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7039,10 +7044,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217818</v>
+        <v>129217829</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7050,21 +7055,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7074,10 +7079,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527359</v>
+        <v>527138</v>
       </c>
       <c r="R66" t="n">
-        <v>7087452</v>
+        <v>7087472</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7110,11 +7115,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7141,10 +7141,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217913</v>
+        <v>129217827</v>
       </c>
       <c r="B67" t="n">
-        <v>98678</v>
+        <v>91997</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7152,34 +7152,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526924</v>
+        <v>527136</v>
       </c>
       <c r="R67" t="n">
-        <v>7087085</v>
+        <v>7087471</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7212,11 +7212,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7243,32 +7238,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217827</v>
+        <v>129217854</v>
       </c>
       <c r="B68" t="n">
-        <v>91997</v>
+        <v>82873</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7278,10 +7273,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527136</v>
+        <v>527015</v>
       </c>
       <c r="R68" t="n">
-        <v>7087471</v>
+        <v>7087228</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7340,45 +7335,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217854</v>
+        <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>82873</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527015</v>
+        <v>526924</v>
       </c>
       <c r="R69" t="n">
-        <v>7087228</v>
+        <v>7087085</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7411,6 +7406,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7437,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217781</v>
+        <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>83007</v>
+        <v>91542</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,21 +7448,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527141</v>
+        <v>527238</v>
       </c>
       <c r="R70" t="n">
-        <v>7087466</v>
+        <v>7087520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217853</v>
+        <v>129217911</v>
       </c>
       <c r="B71" t="n">
-        <v>82873</v>
+        <v>91542</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,34 +7545,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527133</v>
+        <v>527164</v>
       </c>
       <c r="R71" t="n">
-        <v>7087390</v>
+        <v>7087462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217804</v>
+        <v>129217853</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,21 +7642,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>526927</v>
+        <v>527133</v>
       </c>
       <c r="R72" t="n">
-        <v>7087193</v>
+        <v>7087390</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7702,11 +7702,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7733,10 +7728,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217808</v>
+        <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>83007</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7744,21 +7739,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7768,10 +7763,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>526917</v>
+        <v>527141</v>
       </c>
       <c r="R73" t="n">
-        <v>7087144</v>
+        <v>7087466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7804,11 +7799,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7835,10 +7825,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217786</v>
+        <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7846,21 +7836,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7870,10 +7860,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527238</v>
+        <v>526927</v>
       </c>
       <c r="R74" t="n">
-        <v>7087520</v>
+        <v>7087193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7906,6 +7896,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7932,10 +7927,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217911</v>
+        <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7943,34 +7938,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527164</v>
+        <v>526917</v>
       </c>
       <c r="R75" t="n">
-        <v>7087462</v>
+        <v>7087144</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8003,6 +7998,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9024,10 +9024,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217783</v>
+        <v>129217851</v>
       </c>
       <c r="B86" t="n">
-        <v>96924</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9035,21 +9035,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527221</v>
+        <v>527094</v>
       </c>
       <c r="R86" t="n">
-        <v>7087348</v>
+        <v>7087264</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9095,6 +9095,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9121,10 +9126,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217847</v>
+        <v>129217814</v>
       </c>
       <c r="B87" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9132,21 +9137,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9156,10 +9161,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527069</v>
+        <v>526905</v>
       </c>
       <c r="R87" t="n">
-        <v>7087323</v>
+        <v>7087117</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9192,6 +9197,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9218,45 +9228,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217851</v>
+        <v>129217915</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527094</v>
+        <v>527145</v>
       </c>
       <c r="R88" t="n">
-        <v>7087264</v>
+        <v>7087306</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9293,7 +9303,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9320,10 +9330,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217814</v>
+        <v>129217783</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>96924</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9331,21 +9341,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9355,10 +9365,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526905</v>
+        <v>527221</v>
       </c>
       <c r="R89" t="n">
-        <v>7087117</v>
+        <v>7087348</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9391,11 +9401,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9422,45 +9427,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217915</v>
+        <v>129217847</v>
       </c>
       <c r="B90" t="n">
-        <v>98678</v>
+        <v>91560</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527145</v>
+        <v>527069</v>
       </c>
       <c r="R90" t="n">
-        <v>7087306</v>
+        <v>7087323</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9493,11 +9498,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217815</v>
+        <v>129217849</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526883</v>
+        <v>526979</v>
       </c>
       <c r="R2" t="n">
-        <v>7087121</v>
+        <v>7087143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217918</v>
+        <v>129217850</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527262</v>
+        <v>527358</v>
       </c>
       <c r="R3" t="n">
-        <v>7087588</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217849</v>
+        <v>129217815</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526979</v>
+        <v>526883</v>
       </c>
       <c r="R4" t="n">
-        <v>7087143</v>
+        <v>7087121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217850</v>
+        <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527358</v>
+        <v>527262</v>
       </c>
       <c r="R5" t="n">
-        <v>7087435</v>
+        <v>7087588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
         <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217813</v>
+        <v>129217782</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>96950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526901</v>
+        <v>527172</v>
       </c>
       <c r="R9" t="n">
-        <v>7087135</v>
+        <v>7087341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217798</v>
+        <v>129217856</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>92230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527408</v>
+        <v>527386</v>
       </c>
       <c r="R10" t="n">
-        <v>7087464</v>
+        <v>7087522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217856</v>
+        <v>129217813</v>
       </c>
       <c r="B11" t="n">
-        <v>92215</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527386</v>
+        <v>526901</v>
       </c>
       <c r="R11" t="n">
-        <v>7087522</v>
+        <v>7087135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217782</v>
+        <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>96924</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527172</v>
+        <v>527408</v>
       </c>
       <c r="R12" t="n">
-        <v>7087341</v>
+        <v>7087464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217842</v>
+        <v>129217928</v>
       </c>
       <c r="B14" t="n">
-        <v>91556</v>
+        <v>82873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527385</v>
+        <v>527359</v>
       </c>
       <c r="R14" t="n">
-        <v>7087528</v>
+        <v>7087548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,6 +1948,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217840</v>
+        <v>129217842</v>
       </c>
       <c r="B15" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2001,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527386</v>
+        <v>527385</v>
       </c>
       <c r="R15" t="n">
-        <v>7087517</v>
+        <v>7087528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217795</v>
+        <v>129217852</v>
       </c>
       <c r="B16" t="n">
-        <v>91542</v>
+        <v>82873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527123</v>
+        <v>527265</v>
       </c>
       <c r="R16" t="n">
-        <v>7087425</v>
+        <v>7087520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217928</v>
+        <v>129217840</v>
       </c>
       <c r="B17" t="n">
-        <v>82873</v>
+        <v>91554</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,34 +2172,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527359</v>
+        <v>527386</v>
       </c>
       <c r="R17" t="n">
-        <v>7087548</v>
+        <v>7087517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2240,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217852</v>
+        <v>129217795</v>
       </c>
       <c r="B18" t="n">
-        <v>82873</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527265</v>
+        <v>527123</v>
       </c>
       <c r="R18" t="n">
-        <v>7087520</v>
+        <v>7087425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,7 +2455,7 @@
         <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217925</v>
+        <v>129217780</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2560,34 +2560,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527089</v>
+        <v>527179</v>
       </c>
       <c r="R21" t="n">
-        <v>7087260</v>
+        <v>7087518</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217780</v>
+        <v>129217925</v>
       </c>
       <c r="B22" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2657,34 +2657,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527179</v>
+        <v>527089</v>
       </c>
       <c r="R22" t="n">
-        <v>7087518</v>
+        <v>7087260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
         <v>129217785</v>
       </c>
       <c r="B23" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129217793</v>
+        <v>129217779</v>
       </c>
       <c r="B25" t="n">
-        <v>91542</v>
+        <v>83007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527167</v>
+        <v>527248</v>
       </c>
       <c r="R25" t="n">
-        <v>7087461</v>
+        <v>7087513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129217779</v>
+        <v>129217793</v>
       </c>
       <c r="B26" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527248</v>
+        <v>527167</v>
       </c>
       <c r="R26" t="n">
-        <v>7087513</v>
+        <v>7087461</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3338,7 +3338,7 @@
         <v>129217789</v>
       </c>
       <c r="B29" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>129217910</v>
       </c>
       <c r="B30" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217922</v>
+        <v>129217820</v>
       </c>
       <c r="B32" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3657,14 +3657,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527122</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>7087232</v>
+        <v>7087201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,6 +3697,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3723,10 +3728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,16 +3739,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3754,14 +3759,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R33" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3799,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3828,7 +3828,7 @@
         <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>129217833</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>129217835</v>
       </c>
       <c r="B38" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>129217845</v>
       </c>
       <c r="B39" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4621,32 +4621,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129217792</v>
+        <v>129217826</v>
       </c>
       <c r="B42" t="n">
-        <v>91542</v>
+        <v>80050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4656,10 +4656,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527192</v>
+        <v>527090</v>
       </c>
       <c r="R42" t="n">
-        <v>7087529</v>
+        <v>7087261</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4718,10 +4718,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129217843</v>
+        <v>129217778</v>
       </c>
       <c r="B43" t="n">
-        <v>91556</v>
+        <v>83007</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4729,21 +4729,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527378</v>
+        <v>526957</v>
       </c>
       <c r="R43" t="n">
-        <v>7087514</v>
+        <v>7087142</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4815,32 +4815,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217826</v>
+        <v>129217838</v>
       </c>
       <c r="B44" t="n">
-        <v>80050</v>
+        <v>56908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527090</v>
+        <v>527239</v>
       </c>
       <c r="R44" t="n">
-        <v>7087261</v>
+        <v>7087332</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217778</v>
+        <v>129217792</v>
       </c>
       <c r="B45" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4923,21 +4923,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>526957</v>
+        <v>527192</v>
       </c>
       <c r="R45" t="n">
-        <v>7087142</v>
+        <v>7087529</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217838</v>
+        <v>129217843</v>
       </c>
       <c r="B46" t="n">
-        <v>56908</v>
+        <v>91554</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5020,21 +5020,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527239</v>
+        <v>527378</v>
       </c>
       <c r="R46" t="n">
-        <v>7087332</v>
+        <v>7087514</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5106,10 +5106,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217790</v>
+        <v>129217923</v>
       </c>
       <c r="B47" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5117,34 +5117,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527357</v>
+        <v>527150</v>
       </c>
       <c r="R47" t="n">
-        <v>7087574</v>
+        <v>7087278</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5177,6 +5177,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5402,32 +5407,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217923</v>
+        <v>129217920</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527150</v>
+        <v>527064</v>
       </c>
       <c r="R50" t="n">
-        <v>7087278</v>
+        <v>7087252</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5477,7 +5482,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5504,45 +5509,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217920</v>
+        <v>129217790</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527064</v>
+        <v>527357</v>
       </c>
       <c r="R51" t="n">
-        <v>7087252</v>
+        <v>7087574</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5575,11 +5580,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5606,10 +5606,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217794</v>
+        <v>129217819</v>
       </c>
       <c r="B52" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5617,34 +5617,54 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527134</v>
+        <v>527070</v>
       </c>
       <c r="R52" t="n">
-        <v>7087464</v>
+        <v>7087285</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5677,6 +5697,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5703,7 +5728,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -5731,37 +5756,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5798,7 +5803,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5825,7 +5830,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5860,10 +5865,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5900,7 +5905,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5927,32 +5932,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217837</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5962,10 +5967,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>526980</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087208</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6002,7 +6007,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6029,32 +6034,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217837</v>
+        <v>129217794</v>
       </c>
       <c r="B56" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6064,10 +6069,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526980</v>
+        <v>527134</v>
       </c>
       <c r="R56" t="n">
-        <v>7087208</v>
+        <v>7087464</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6100,11 +6105,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6131,10 +6131,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217848</v>
+        <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>96950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6142,21 +6142,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527106</v>
+        <v>527349</v>
       </c>
       <c r="R57" t="n">
-        <v>7087367</v>
+        <v>7087510</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6202,11 +6202,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6233,10 +6228,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217823</v>
+        <v>129217848</v>
       </c>
       <c r="B58" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6244,21 +6239,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6268,10 +6263,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527374</v>
+        <v>527106</v>
       </c>
       <c r="R58" t="n">
-        <v>7087508</v>
+        <v>7087367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6308,7 +6303,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6335,10 +6330,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217784</v>
+        <v>129217823</v>
       </c>
       <c r="B59" t="n">
-        <v>96924</v>
+        <v>57887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6346,21 +6341,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6370,10 +6365,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527349</v>
+        <v>527374</v>
       </c>
       <c r="R59" t="n">
-        <v>7087510</v>
+        <v>7087508</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6406,6 +6401,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6435,7 +6435,7 @@
         <v>129217832</v>
       </c>
       <c r="B60" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6738,32 +6738,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217806</v>
+        <v>129217827</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>526925</v>
+        <v>527136</v>
       </c>
       <c r="R63" t="n">
-        <v>7087175</v>
+        <v>7087471</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6809,11 +6809,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6840,10 +6835,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217810</v>
+        <v>129217854</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6851,21 +6846,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6875,10 +6870,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526914</v>
+        <v>527015</v>
       </c>
       <c r="R64" t="n">
-        <v>7087139</v>
+        <v>7087228</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6911,11 +6906,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6942,10 +6932,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217818</v>
+        <v>129217829</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91837</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6953,21 +6943,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6977,10 +6967,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527359</v>
+        <v>527138</v>
       </c>
       <c r="R65" t="n">
-        <v>7087452</v>
+        <v>7087472</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7013,11 +7003,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7044,10 +7029,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217829</v>
+        <v>129217806</v>
       </c>
       <c r="B66" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7055,21 +7040,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7079,10 +7064,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527138</v>
+        <v>526925</v>
       </c>
       <c r="R66" t="n">
-        <v>7087472</v>
+        <v>7087175</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7115,6 +7100,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7141,32 +7131,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217827</v>
+        <v>129217810</v>
       </c>
       <c r="B67" t="n">
-        <v>91997</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7176,10 +7166,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527136</v>
+        <v>526914</v>
       </c>
       <c r="R67" t="n">
-        <v>7087471</v>
+        <v>7087139</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7212,6 +7202,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7238,10 +7233,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217854</v>
+        <v>129217818</v>
       </c>
       <c r="B68" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7249,21 +7244,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7273,10 +7268,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527015</v>
+        <v>527359</v>
       </c>
       <c r="R68" t="n">
-        <v>7087228</v>
+        <v>7087452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7309,6 +7304,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7338,7 +7338,7 @@
         <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7437,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217786</v>
+        <v>129217804</v>
       </c>
       <c r="B70" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,21 +7448,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527238</v>
+        <v>526927</v>
       </c>
       <c r="R70" t="n">
-        <v>7087520</v>
+        <v>7087193</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7508,6 +7508,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7534,10 +7539,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217911</v>
+        <v>129217808</v>
       </c>
       <c r="B71" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,34 +7550,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527164</v>
+        <v>526917</v>
       </c>
       <c r="R71" t="n">
-        <v>7087462</v>
+        <v>7087144</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7605,6 +7610,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7631,10 +7641,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217853</v>
+        <v>129217786</v>
       </c>
       <c r="B72" t="n">
-        <v>82873</v>
+        <v>91540</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,21 +7652,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7666,10 +7676,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527133</v>
+        <v>527238</v>
       </c>
       <c r="R72" t="n">
-        <v>7087390</v>
+        <v>7087520</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7728,10 +7738,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217781</v>
+        <v>129217911</v>
       </c>
       <c r="B73" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7739,34 +7749,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527141</v>
+        <v>527164</v>
       </c>
       <c r="R73" t="n">
-        <v>7087466</v>
+        <v>7087462</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7825,10 +7835,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217804</v>
+        <v>129217853</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7836,21 +7846,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7860,10 +7870,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526927</v>
+        <v>527133</v>
       </c>
       <c r="R74" t="n">
-        <v>7087193</v>
+        <v>7087390</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7896,11 +7906,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7927,10 +7932,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217808</v>
+        <v>129217781</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>83007</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7938,21 +7943,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7962,10 +7967,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526917</v>
+        <v>527141</v>
       </c>
       <c r="R75" t="n">
-        <v>7087144</v>
+        <v>7087466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7998,11 +8003,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8032,7 +8032,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217924</v>
+        <v>129217912</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8234,21 +8234,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8258,10 +8258,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527289</v>
+        <v>527089</v>
       </c>
       <c r="R78" t="n">
-        <v>7087449</v>
+        <v>7087260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8294,6 +8294,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8320,10 +8325,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217912</v>
+        <v>129217924</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8331,21 +8336,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8355,10 +8360,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527089</v>
+        <v>527289</v>
       </c>
       <c r="R79" t="n">
-        <v>7087260</v>
+        <v>7087449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8391,11 +8396,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8422,10 +8422,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217802</v>
+        <v>129217841</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>91554</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8433,21 +8433,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8457,10 +8457,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526934</v>
+        <v>527375</v>
       </c>
       <c r="R80" t="n">
-        <v>7087213</v>
+        <v>7087521</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8493,11 +8493,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8524,7 +8519,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217929</v>
+        <v>129217802</v>
       </c>
       <c r="B81" t="n">
         <v>57727</v>
@@ -8555,14 +8550,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527393</v>
+        <v>526934</v>
       </c>
       <c r="R81" t="n">
-        <v>7087440</v>
+        <v>7087213</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8626,10 +8621,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217841</v>
+        <v>129217929</v>
       </c>
       <c r="B82" t="n">
-        <v>91556</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8637,34 +8632,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527375</v>
+        <v>527393</v>
       </c>
       <c r="R82" t="n">
-        <v>7087521</v>
+        <v>7087440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8697,6 +8692,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8723,10 +8723,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217921</v>
+        <v>129217914</v>
       </c>
       <c r="B83" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526984</v>
+        <v>526928</v>
       </c>
       <c r="R83" t="n">
-        <v>7087226</v>
+        <v>7087112</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8825,45 +8825,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217914</v>
+        <v>129217830</v>
       </c>
       <c r="B84" t="n">
-        <v>98678</v>
+        <v>78054</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526928</v>
+        <v>526990</v>
       </c>
       <c r="R84" t="n">
-        <v>7087112</v>
+        <v>7087234</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8896,11 +8896,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8927,45 +8922,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217830</v>
+        <v>129217921</v>
       </c>
       <c r="B85" t="n">
-        <v>78054</v>
+        <v>98704</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526990</v>
+        <v>526984</v>
       </c>
       <c r="R85" t="n">
-        <v>7087234</v>
+        <v>7087226</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8998,6 +8993,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9024,45 +9024,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217851</v>
+        <v>129217915</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527094</v>
+        <v>527145</v>
       </c>
       <c r="R86" t="n">
-        <v>7087264</v>
+        <v>7087306</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9228,45 +9228,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217915</v>
+        <v>129217783</v>
       </c>
       <c r="B88" t="n">
-        <v>98678</v>
+        <v>96950</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527145</v>
+        <v>527221</v>
       </c>
       <c r="R88" t="n">
-        <v>7087306</v>
+        <v>7087348</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9299,11 +9299,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9330,10 +9325,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217783</v>
+        <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>96924</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9341,21 +9336,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9365,10 +9360,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527221</v>
+        <v>527094</v>
       </c>
       <c r="R89" t="n">
-        <v>7087348</v>
+        <v>7087264</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9401,6 +9396,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9430,7 +9430,7 @@
         <v>129217847</v>
       </c>
       <c r="B90" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217849</v>
+        <v>129217918</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526979</v>
+        <v>527262</v>
       </c>
       <c r="R2" t="n">
-        <v>7087143</v>
+        <v>7087588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217850</v>
+        <v>129217849</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527358</v>
+        <v>526979</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217815</v>
+        <v>129217850</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526883</v>
+        <v>527358</v>
       </c>
       <c r="R4" t="n">
-        <v>7087121</v>
+        <v>7087435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217918</v>
+        <v>129217815</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527262</v>
+        <v>526883</v>
       </c>
       <c r="R5" t="n">
-        <v>7087588</v>
+        <v>7087121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R6" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217831</v>
+        <v>129217791</v>
       </c>
       <c r="B8" t="n">
-        <v>80106</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527362</v>
+        <v>527219</v>
       </c>
       <c r="R8" t="n">
-        <v>7087507</v>
+        <v>7087542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217782</v>
+        <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>96950</v>
+        <v>92231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527172</v>
+        <v>527386</v>
       </c>
       <c r="R9" t="n">
-        <v>7087341</v>
+        <v>7087522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217856</v>
+        <v>129217782</v>
       </c>
       <c r="B10" t="n">
-        <v>92230</v>
+        <v>96951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527386</v>
+        <v>527172</v>
       </c>
       <c r="R10" t="n">
-        <v>7087522</v>
+        <v>7087341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217928</v>
+        <v>129217795</v>
       </c>
       <c r="B14" t="n">
-        <v>82873</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527359</v>
+        <v>527123</v>
       </c>
       <c r="R14" t="n">
-        <v>7087548</v>
+        <v>7087425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1948,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217842</v>
+        <v>129217855</v>
       </c>
       <c r="B15" t="n">
-        <v>91554</v>
+        <v>82873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527385</v>
+        <v>527012</v>
       </c>
       <c r="R15" t="n">
-        <v>7087528</v>
+        <v>7087233</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217852</v>
+        <v>129217840</v>
       </c>
       <c r="B16" t="n">
-        <v>82873</v>
+        <v>91554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527265</v>
+        <v>527386</v>
       </c>
       <c r="R16" t="n">
-        <v>7087520</v>
+        <v>7087517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,10 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217840</v>
+        <v>129217928</v>
       </c>
       <c r="B17" t="n">
-        <v>91554</v>
+        <v>82873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,34 +2171,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527386</v>
+        <v>527359</v>
       </c>
       <c r="R17" t="n">
-        <v>7087517</v>
+        <v>7087548</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,6 +2239,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217795</v>
+        <v>129217842</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>91554</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527123</v>
+        <v>527385</v>
       </c>
       <c r="R18" t="n">
-        <v>7087425</v>
+        <v>7087528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217855</v>
+        <v>129217852</v>
       </c>
       <c r="B19" t="n">
         <v>82873</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527012</v>
+        <v>527265</v>
       </c>
       <c r="R19" t="n">
-        <v>7087233</v>
+        <v>7087520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,7 +2455,7 @@
         <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217807</v>
+        <v>129217789</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>526921</v>
+        <v>527376</v>
       </c>
       <c r="R28" t="n">
-        <v>7087159</v>
+        <v>7087516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,11 +3304,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3335,7 +3330,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217789</v>
+        <v>129217910</v>
       </c>
       <c r="B29" t="n">
         <v>91540</v>
@@ -3366,14 +3361,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527376</v>
+        <v>527288</v>
       </c>
       <c r="R29" t="n">
-        <v>7087516</v>
+        <v>7087491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217910</v>
+        <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,34 +3438,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527288</v>
+        <v>526921</v>
       </c>
       <c r="R30" t="n">
-        <v>7087491</v>
+        <v>7087159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3657,14 +3657,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R32" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,11 +3697,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3728,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217922</v>
+        <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3739,16 +3734,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3759,14 +3754,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527122</v>
+        <v>527034</v>
       </c>
       <c r="R33" t="n">
-        <v>7087232</v>
+        <v>7087201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3799,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3828,7 +3828,7 @@
         <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129217846</v>
+        <v>129217812</v>
       </c>
       <c r="B35" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527139</v>
+        <v>526904</v>
       </c>
       <c r="R35" t="n">
-        <v>7087468</v>
+        <v>7087132</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,6 +3993,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4019,10 +4024,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129217812</v>
+        <v>129217846</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,23 +4035,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4054,10 +4055,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>526904</v>
+        <v>527139</v>
       </c>
       <c r="R36" t="n">
-        <v>7087132</v>
+        <v>7087468</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,11 +4091,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4121,32 +4117,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B37" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4156,10 +4152,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R37" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4196,7 +4192,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4223,32 +4219,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B38" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4258,10 +4254,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R38" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4294,6 +4290,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4320,32 +4321,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217845</v>
+        <v>129217833</v>
       </c>
       <c r="B39" t="n">
-        <v>91558</v>
+        <v>98705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4355,10 +4356,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527173</v>
+        <v>527351</v>
       </c>
       <c r="R39" t="n">
-        <v>7087380</v>
+        <v>7087510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,6 +4392,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4417,10 +4423,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217803</v>
+        <v>129217845</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4428,23 +4434,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4452,10 +4454,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526923</v>
+        <v>527173</v>
       </c>
       <c r="R40" t="n">
-        <v>7087199</v>
+        <v>7087380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4488,11 +4490,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4519,32 +4516,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217821</v>
+        <v>129217835</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4554,10 +4551,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526924</v>
+        <v>527103</v>
       </c>
       <c r="R41" t="n">
-        <v>7087187</v>
+        <v>7087341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4590,11 +4587,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4621,32 +4613,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129217826</v>
+        <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>80050</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4656,10 +4648,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527090</v>
+        <v>527192</v>
       </c>
       <c r="R42" t="n">
-        <v>7087261</v>
+        <v>7087529</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4718,10 +4710,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129217778</v>
+        <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>83007</v>
+        <v>91554</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4729,21 +4721,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4753,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>526957</v>
+        <v>527378</v>
       </c>
       <c r="R43" t="n">
-        <v>7087142</v>
+        <v>7087514</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4815,32 +4807,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217838</v>
+        <v>129217826</v>
       </c>
       <c r="B44" t="n">
-        <v>56908</v>
+        <v>80050</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4850,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527239</v>
+        <v>527090</v>
       </c>
       <c r="R44" t="n">
-        <v>7087332</v>
+        <v>7087261</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4912,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217792</v>
+        <v>129217778</v>
       </c>
       <c r="B45" t="n">
-        <v>91540</v>
+        <v>83007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4923,21 +4915,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4947,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527192</v>
+        <v>526957</v>
       </c>
       <c r="R45" t="n">
-        <v>7087529</v>
+        <v>7087142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5009,10 +5001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217843</v>
+        <v>129217838</v>
       </c>
       <c r="B46" t="n">
-        <v>91554</v>
+        <v>56908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5020,21 +5012,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5044,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527378</v>
+        <v>527239</v>
       </c>
       <c r="R46" t="n">
-        <v>7087514</v>
+        <v>7087332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5106,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5117,34 +5109,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R47" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5177,11 +5169,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5208,45 +5195,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217844</v>
+        <v>129217923</v>
       </c>
       <c r="B48" t="n">
-        <v>57719</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527355</v>
+        <v>527150</v>
       </c>
       <c r="R48" t="n">
-        <v>7087521</v>
+        <v>7087278</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,6 +5266,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5305,45 +5297,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217805</v>
+        <v>129217920</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>526924</v>
+        <v>527064</v>
       </c>
       <c r="R49" t="n">
-        <v>7087183</v>
+        <v>7087252</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5380,7 +5372,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5407,45 +5399,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217920</v>
+        <v>129217844</v>
       </c>
       <c r="B50" t="n">
-        <v>98704</v>
+        <v>57719</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527064</v>
+        <v>527355</v>
       </c>
       <c r="R50" t="n">
-        <v>7087252</v>
+        <v>7087521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5478,11 +5470,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5509,10 +5496,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217790</v>
+        <v>129217805</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5520,21 +5507,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5544,10 +5531,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527357</v>
+        <v>526924</v>
       </c>
       <c r="R51" t="n">
-        <v>7087574</v>
+        <v>7087183</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5580,6 +5567,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5606,10 +5598,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217819</v>
+        <v>129217794</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5617,54 +5609,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527070</v>
+        <v>527134</v>
       </c>
       <c r="R52" t="n">
-        <v>7087285</v>
+        <v>7087464</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5697,11 +5669,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5728,7 +5695,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217800</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -5756,17 +5723,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527297</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087514</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5803,7 +5790,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5830,7 +5817,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217801</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5865,10 +5852,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527106</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087348</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5905,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5932,32 +5919,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217837</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5967,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>526980</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087208</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6007,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6034,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217794</v>
+        <v>129217837</v>
       </c>
       <c r="B56" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6069,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527134</v>
+        <v>526980</v>
       </c>
       <c r="R56" t="n">
-        <v>7087464</v>
+        <v>7087208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6105,6 +6092,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6134,7 +6126,7 @@
         <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6228,10 +6220,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217848</v>
+        <v>129217823</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6239,21 +6231,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6263,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527106</v>
+        <v>527374</v>
       </c>
       <c r="R58" t="n">
-        <v>7087367</v>
+        <v>7087508</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6303,7 +6295,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6330,32 +6322,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217823</v>
+        <v>129217832</v>
       </c>
       <c r="B59" t="n">
-        <v>57887</v>
+        <v>98705</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6365,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527374</v>
+        <v>527149</v>
       </c>
       <c r="R59" t="n">
-        <v>7087508</v>
+        <v>7087289</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6405,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6432,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B60" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6463,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R60" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6507,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6534,10 +6526,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217919</v>
+        <v>129217834</v>
       </c>
       <c r="B61" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6565,14 +6557,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527135</v>
+        <v>527268</v>
       </c>
       <c r="R61" t="n">
-        <v>7087449</v>
+        <v>7087590</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6609,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6636,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217834</v>
+        <v>129217848</v>
       </c>
       <c r="B62" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6671,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527268</v>
+        <v>527106</v>
       </c>
       <c r="R62" t="n">
-        <v>7087590</v>
+        <v>7087367</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6711,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6738,32 +6730,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217827</v>
+        <v>129217854</v>
       </c>
       <c r="B63" t="n">
-        <v>91992</v>
+        <v>82873</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6773,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527136</v>
+        <v>527015</v>
       </c>
       <c r="R63" t="n">
-        <v>7087471</v>
+        <v>7087228</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6835,32 +6827,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217854</v>
+        <v>129217827</v>
       </c>
       <c r="B64" t="n">
-        <v>82873</v>
+        <v>91993</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6870,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527015</v>
+        <v>527136</v>
       </c>
       <c r="R64" t="n">
-        <v>7087228</v>
+        <v>7087471</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6932,10 +6924,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217829</v>
+        <v>129217806</v>
       </c>
       <c r="B65" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6943,21 +6935,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6967,10 +6959,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527138</v>
+        <v>526925</v>
       </c>
       <c r="R65" t="n">
-        <v>7087472</v>
+        <v>7087175</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7003,6 +6995,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7029,7 +7026,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217806</v>
+        <v>129217810</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -7064,10 +7061,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526925</v>
+        <v>526914</v>
       </c>
       <c r="R66" t="n">
-        <v>7087175</v>
+        <v>7087139</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7104,7 +7101,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7131,7 +7128,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217810</v>
+        <v>129217818</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7166,10 +7163,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526914</v>
+        <v>527359</v>
       </c>
       <c r="R67" t="n">
-        <v>7087139</v>
+        <v>7087452</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7206,7 +7203,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7233,10 +7230,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217818</v>
+        <v>129217829</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7244,21 +7241,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7268,10 +7265,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527359</v>
+        <v>527138</v>
       </c>
       <c r="R68" t="n">
-        <v>7087452</v>
+        <v>7087472</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7304,11 +7301,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7338,7 +7330,7 @@
         <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7437,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217804</v>
+        <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7472,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>526927</v>
+        <v>527238</v>
       </c>
       <c r="R70" t="n">
-        <v>7087193</v>
+        <v>7087520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7508,11 +7500,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7539,10 +7526,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217808</v>
+        <v>129217853</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7550,21 +7537,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7574,10 +7561,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526917</v>
+        <v>527133</v>
       </c>
       <c r="R71" t="n">
-        <v>7087144</v>
+        <v>7087390</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7610,11 +7597,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7641,7 +7623,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217786</v>
+        <v>129217911</v>
       </c>
       <c r="B72" t="n">
         <v>91540</v>
@@ -7672,14 +7654,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527238</v>
+        <v>527164</v>
       </c>
       <c r="R72" t="n">
-        <v>7087520</v>
+        <v>7087462</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7738,10 +7720,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217911</v>
+        <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>91540</v>
+        <v>83007</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7749,34 +7731,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527164</v>
+        <v>527141</v>
       </c>
       <c r="R73" t="n">
-        <v>7087462</v>
+        <v>7087466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7835,10 +7817,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217853</v>
+        <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7846,21 +7828,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7870,10 +7852,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527133</v>
+        <v>526927</v>
       </c>
       <c r="R74" t="n">
-        <v>7087390</v>
+        <v>7087193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7906,6 +7888,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7932,10 +7919,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217781</v>
+        <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>83007</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7943,21 +7930,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7967,10 +7954,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527141</v>
+        <v>526917</v>
       </c>
       <c r="R75" t="n">
-        <v>7087466</v>
+        <v>7087144</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8003,6 +7990,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8223,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217912</v>
+        <v>129217841</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>91554</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8234,34 +8226,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527089</v>
+        <v>527375</v>
       </c>
       <c r="R78" t="n">
-        <v>7087260</v>
+        <v>7087521</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8294,11 +8286,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8325,10 +8312,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217924</v>
+        <v>129217830</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>78054</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8336,34 +8323,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527289</v>
+        <v>526990</v>
       </c>
       <c r="R79" t="n">
-        <v>7087449</v>
+        <v>7087234</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8422,10 +8409,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217841</v>
+        <v>129217912</v>
       </c>
       <c r="B80" t="n">
-        <v>91554</v>
+        <v>80146</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8433,34 +8420,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527375</v>
+        <v>527089</v>
       </c>
       <c r="R80" t="n">
-        <v>7087521</v>
+        <v>7087260</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8493,6 +8480,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8519,10 +8511,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217802</v>
+        <v>129217924</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8530,34 +8522,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526934</v>
+        <v>527289</v>
       </c>
       <c r="R81" t="n">
-        <v>7087213</v>
+        <v>7087449</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8590,11 +8582,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8621,32 +8608,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217929</v>
+        <v>129217921</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8656,10 +8643,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527393</v>
+        <v>526984</v>
       </c>
       <c r="R82" t="n">
-        <v>7087440</v>
+        <v>7087226</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8696,7 +8683,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8726,7 +8713,7 @@
         <v>129217914</v>
       </c>
       <c r="B83" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8825,10 +8812,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217830</v>
+        <v>129217802</v>
       </c>
       <c r="B84" t="n">
-        <v>78054</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8836,21 +8823,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8860,10 +8847,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526990</v>
+        <v>526934</v>
       </c>
       <c r="R84" t="n">
-        <v>7087234</v>
+        <v>7087213</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8896,6 +8883,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8922,32 +8914,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217921</v>
+        <v>129217929</v>
       </c>
       <c r="B85" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8957,10 +8949,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526984</v>
+        <v>527393</v>
       </c>
       <c r="R85" t="n">
-        <v>7087226</v>
+        <v>7087440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8997,7 +8989,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9024,45 +9016,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217915</v>
+        <v>129217783</v>
       </c>
       <c r="B86" t="n">
-        <v>98704</v>
+        <v>96951</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527145</v>
+        <v>527221</v>
       </c>
       <c r="R86" t="n">
-        <v>7087306</v>
+        <v>7087348</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9095,11 +9087,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9228,45 +9215,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217783</v>
+        <v>129217915</v>
       </c>
       <c r="B88" t="n">
-        <v>96950</v>
+        <v>98705</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527221</v>
+        <v>527145</v>
       </c>
       <c r="R88" t="n">
-        <v>7087348</v>
+        <v>7087306</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9299,6 +9286,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9430,7 +9422,7 @@
         <v>129217847</v>
       </c>
       <c r="B90" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9447,14 +9439,10 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217918</v>
+        <v>129217815</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527262</v>
+        <v>526883</v>
       </c>
       <c r="R2" t="n">
-        <v>7087588</v>
+        <v>7087121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,57 +765,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217849</v>
+        <v>129217918</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526979</v>
+        <v>527262</v>
       </c>
       <c r="R3" t="n">
-        <v>7087143</v>
+        <v>7087588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,6 +850,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -862,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217850</v>
+        <v>129217849</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527358</v>
+        <v>526979</v>
       </c>
       <c r="R4" t="n">
-        <v>7087435</v>
+        <v>7087143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,11 +952,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200 bålar</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -964,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217815</v>
+        <v>129217850</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526883</v>
+        <v>527358</v>
       </c>
       <c r="R5" t="n">
-        <v>7087121</v>
+        <v>7087435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1066,22 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R6" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,11 +1151,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1168,44 +1163,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217831</v>
+        <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>80106</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527362</v>
+        <v>527399</v>
       </c>
       <c r="R7" t="n">
-        <v>7087507</v>
+        <v>7087454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,6 +1248,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1265,44 +1265,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217791</v>
+        <v>129217831</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>80106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527219</v>
+        <v>527362</v>
       </c>
       <c r="R8" t="n">
-        <v>7087542</v>
+        <v>7087507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,44 +1362,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217856</v>
+        <v>129217813</v>
       </c>
       <c r="B9" t="n">
-        <v>92231</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527386</v>
+        <v>526901</v>
       </c>
       <c r="R9" t="n">
-        <v>7087522</v>
+        <v>7087135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1447,6 +1447,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1459,22 +1464,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217782</v>
+        <v>129217798</v>
       </c>
       <c r="B10" t="n">
-        <v>96951</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527172</v>
+        <v>527408</v>
       </c>
       <c r="R10" t="n">
-        <v>7087341</v>
+        <v>7087464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1544,6 +1549,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1556,44 +1566,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217813</v>
+        <v>129217856</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526901</v>
+        <v>527386</v>
       </c>
       <c r="R11" t="n">
-        <v>7087135</v>
+        <v>7087522</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,11 +1651,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1658,22 +1663,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217798</v>
+        <v>129217782</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>96952</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527408</v>
+        <v>527172</v>
       </c>
       <c r="R12" t="n">
-        <v>7087464</v>
+        <v>7087341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,11 +1748,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1760,12 +1760,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1857,44 +1857,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217795</v>
+        <v>129217785</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527123</v>
+        <v>527106</v>
       </c>
       <c r="R14" t="n">
-        <v>7087425</v>
+        <v>7087220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,22 +1954,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217855</v>
+        <v>129217780</v>
       </c>
       <c r="B15" t="n">
-        <v>82873</v>
+        <v>83007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527012</v>
+        <v>527179</v>
       </c>
       <c r="R15" t="n">
-        <v>7087233</v>
+        <v>7087518</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,22 +2051,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217840</v>
+        <v>129217925</v>
       </c>
       <c r="B16" t="n">
-        <v>91554</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,34 +2074,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527386</v>
+        <v>527089</v>
       </c>
       <c r="R16" t="n">
-        <v>7087517</v>
+        <v>7087260</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,44 +2148,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217928</v>
+        <v>129217917</v>
       </c>
       <c r="B17" t="n">
-        <v>82873</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527359</v>
+        <v>527273</v>
       </c>
       <c r="R17" t="n">
-        <v>7087548</v>
+        <v>7087581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,35 +2233,39 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217842</v>
+        <v>129217928</v>
       </c>
       <c r="B18" t="n">
-        <v>91554</v>
+        <v>82873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,34 +2273,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527385</v>
+        <v>527359</v>
       </c>
       <c r="R18" t="n">
-        <v>7087528</v>
+        <v>7087548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,28 +2341,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217852</v>
+        <v>129217842</v>
       </c>
       <c r="B19" t="n">
-        <v>82873</v>
+        <v>91554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2366,21 +2371,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2390,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527265</v>
+        <v>527385</v>
       </c>
       <c r="R19" t="n">
-        <v>7087520</v>
+        <v>7087528</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2440,44 +2445,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217797</v>
+        <v>129217852</v>
       </c>
       <c r="B20" t="n">
-        <v>92258</v>
+        <v>82873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527368</v>
+        <v>527265</v>
       </c>
       <c r="R20" t="n">
-        <v>7087576</v>
+        <v>7087520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2537,22 +2542,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217780</v>
+        <v>129217840</v>
       </c>
       <c r="B21" t="n">
-        <v>83007</v>
+        <v>91554</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2560,21 +2565,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527179</v>
+        <v>527386</v>
       </c>
       <c r="R21" t="n">
-        <v>7087518</v>
+        <v>7087517</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2634,22 +2639,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217925</v>
+        <v>129217795</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2657,34 +2662,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527089</v>
+        <v>527123</v>
       </c>
       <c r="R22" t="n">
-        <v>7087260</v>
+        <v>7087425</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,44 +2736,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217785</v>
+        <v>129217855</v>
       </c>
       <c r="B23" t="n">
-        <v>91504</v>
+        <v>82873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2778,10 +2783,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527106</v>
+        <v>527012</v>
       </c>
       <c r="R23" t="n">
-        <v>7087220</v>
+        <v>7087233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,57 +2833,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217917</v>
+        <v>129217797</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>92258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527273</v>
+        <v>527368</v>
       </c>
       <c r="R24" t="n">
-        <v>7087581</v>
+        <v>7087576</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2913,11 +2918,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2930,22 +2930,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129217779</v>
+        <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527248</v>
+        <v>527167</v>
       </c>
       <c r="R25" t="n">
-        <v>7087513</v>
+        <v>7087461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,22 +3027,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129217793</v>
+        <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>83007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527167</v>
+        <v>527248</v>
       </c>
       <c r="R26" t="n">
-        <v>7087461</v>
+        <v>7087513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3124,22 +3124,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217926</v>
+        <v>129217789</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527029</v>
+        <v>527376</v>
       </c>
       <c r="R27" t="n">
-        <v>7087194</v>
+        <v>7087516</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,19 +3221,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217789</v>
+        <v>129217910</v>
       </c>
       <c r="B28" t="n">
         <v>91540</v>
@@ -3264,14 +3264,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527376</v>
+        <v>527288</v>
       </c>
       <c r="R28" t="n">
-        <v>7087516</v>
+        <v>7087491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3318,22 +3318,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217910</v>
+        <v>129217926</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527288</v>
+        <v>527029</v>
       </c>
       <c r="R29" t="n">
-        <v>7087491</v>
+        <v>7087194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3415,12 +3415,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3517,44 +3517,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217787</v>
+        <v>129217836</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527291</v>
+        <v>527091</v>
       </c>
       <c r="R31" t="n">
-        <v>7087491</v>
+        <v>7087273</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3614,22 +3614,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217922</v>
+        <v>129217787</v>
       </c>
       <c r="B32" t="n">
-        <v>56908</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,34 +3637,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527122</v>
+        <v>527291</v>
       </c>
       <c r="R32" t="n">
-        <v>7087232</v>
+        <v>7087491</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,12 +3711,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3813,57 +3813,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B34" t="n">
-        <v>98705</v>
+        <v>56908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R34" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3910,22 +3910,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129217812</v>
+        <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,23 +3933,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3957,10 +3953,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>526904</v>
+        <v>527139</v>
       </c>
       <c r="R35" t="n">
-        <v>7087132</v>
+        <v>7087468</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3995,11 +3991,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4012,22 +4003,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129217846</v>
+        <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4035,19 +4026,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4055,10 +4050,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527139</v>
+        <v>526904</v>
       </c>
       <c r="R36" t="n">
-        <v>7087468</v>
+        <v>7087132</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4093,6 +4088,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4105,22 +4105,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217803</v>
+        <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4128,23 +4128,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4152,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526923</v>
+        <v>527173</v>
       </c>
       <c r="R37" t="n">
-        <v>7087199</v>
+        <v>7087380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4190,11 +4186,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4207,19 +4198,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217821</v>
+        <v>129217803</v>
       </c>
       <c r="B38" t="n">
         <v>57727</v>
@@ -4254,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526924</v>
+        <v>526923</v>
       </c>
       <c r="R38" t="n">
-        <v>7087187</v>
+        <v>7087199</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4294,7 +4285,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4309,44 +4300,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217833</v>
+        <v>129217821</v>
       </c>
       <c r="B39" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4356,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527351</v>
+        <v>526924</v>
       </c>
       <c r="R39" t="n">
-        <v>7087510</v>
+        <v>7087187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4396,7 +4387,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4411,42 +4402,46 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217845</v>
+        <v>129217833</v>
       </c>
       <c r="B40" t="n">
-        <v>91560</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4454,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527173</v>
+        <v>527351</v>
       </c>
       <c r="R40" t="n">
-        <v>7087380</v>
+        <v>7087510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,6 +4487,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4504,12 +4504,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4519,7 +4519,7 @@
         <v>129217835</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4601,12 +4601,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4698,12 +4698,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4795,12 +4795,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4892,12 +4892,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -4989,12 +4989,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5086,12 +5086,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5183,57 +5183,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217923</v>
+        <v>129217844</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>57719</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527150</v>
+        <v>527355</v>
       </c>
       <c r="R48" t="n">
-        <v>7087278</v>
+        <v>7087521</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5268,11 +5268,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5285,57 +5280,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217920</v>
+        <v>129217805</v>
       </c>
       <c r="B49" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527064</v>
+        <v>526924</v>
       </c>
       <c r="R49" t="n">
-        <v>7087252</v>
+        <v>7087183</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5372,7 +5367,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5387,57 +5382,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217844</v>
+        <v>129217923</v>
       </c>
       <c r="B50" t="n">
-        <v>57719</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527355</v>
+        <v>527150</v>
       </c>
       <c r="R50" t="n">
-        <v>7087521</v>
+        <v>7087278</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5472,6 +5467,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5484,57 +5484,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217805</v>
+        <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>526924</v>
+        <v>527064</v>
       </c>
       <c r="R51" t="n">
-        <v>7087183</v>
+        <v>7087252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5586,12 +5586,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5683,77 +5683,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217837</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>526980</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087208</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5790,7 +5770,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5805,19 +5785,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217819</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5845,17 +5825,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>527070</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087285</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5907,19 +5907,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217800</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>527297</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6009,44 +6009,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217837</v>
+        <v>129217801</v>
       </c>
       <c r="B56" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526980</v>
+        <v>527106</v>
       </c>
       <c r="R56" t="n">
-        <v>7087208</v>
+        <v>7087348</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6111,22 +6111,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217784</v>
+        <v>129217823</v>
       </c>
       <c r="B57" t="n">
-        <v>96951</v>
+        <v>57887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527349</v>
+        <v>527374</v>
       </c>
       <c r="R57" t="n">
-        <v>7087510</v>
+        <v>7087508</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6196,6 +6196,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4st</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6208,44 +6213,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217823</v>
+        <v>129217832</v>
       </c>
       <c r="B58" t="n">
-        <v>57887</v>
+        <v>98706</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527374</v>
+        <v>527149</v>
       </c>
       <c r="R58" t="n">
-        <v>7087508</v>
+        <v>7087289</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6295,7 +6300,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6310,22 +6315,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B59" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6353,14 +6358,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R59" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6402,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6412,22 +6417,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217919</v>
+        <v>129217834</v>
       </c>
       <c r="B60" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6455,14 +6460,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527135</v>
+        <v>527268</v>
       </c>
       <c r="R60" t="n">
-        <v>7087449</v>
+        <v>7087590</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6504,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6514,44 +6519,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217834</v>
+        <v>129217784</v>
       </c>
       <c r="B61" t="n">
-        <v>98705</v>
+        <v>96952</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6566,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527268</v>
+        <v>527349</v>
       </c>
       <c r="R61" t="n">
-        <v>7087590</v>
+        <v>7087510</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6599,11 +6604,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Flera 100 plantor</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6616,12 +6616,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6718,22 +6718,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217854</v>
+        <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>82873</v>
+        <v>91838</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527015</v>
+        <v>527138</v>
       </c>
       <c r="R63" t="n">
-        <v>7087228</v>
+        <v>7087472</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6815,22 +6815,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217827</v>
+        <v>129217913</v>
       </c>
       <c r="B64" t="n">
-        <v>91993</v>
+        <v>98706</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6838,34 +6838,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527136</v>
+        <v>526924</v>
       </c>
       <c r="R64" t="n">
-        <v>7087471</v>
+        <v>7087085</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6900,6 +6900,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -6912,44 +6917,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217806</v>
+        <v>129217827</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91993</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6959,10 +6964,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526925</v>
+        <v>527136</v>
       </c>
       <c r="R65" t="n">
-        <v>7087175</v>
+        <v>7087471</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6997,11 +7002,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7014,22 +7014,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217810</v>
+        <v>129217854</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>82873</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7037,21 +7037,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526914</v>
+        <v>527015</v>
       </c>
       <c r="R66" t="n">
-        <v>7087139</v>
+        <v>7087228</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7099,11 +7099,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7116,19 +7111,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217818</v>
+        <v>129217806</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7163,10 +7158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527359</v>
+        <v>526925</v>
       </c>
       <c r="R67" t="n">
-        <v>7087452</v>
+        <v>7087175</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7218,22 +7213,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217829</v>
+        <v>129217810</v>
       </c>
       <c r="B68" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7241,21 +7236,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7265,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527138</v>
+        <v>526914</v>
       </c>
       <c r="R68" t="n">
-        <v>7087472</v>
+        <v>7087139</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7303,6 +7298,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7315,57 +7315,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217913</v>
+        <v>129217818</v>
       </c>
       <c r="B69" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526924</v>
+        <v>527359</v>
       </c>
       <c r="R69" t="n">
-        <v>7087085</v>
+        <v>7087452</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7417,12 +7417,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7514,22 +7514,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217853</v>
+        <v>129217911</v>
       </c>
       <c r="B71" t="n">
-        <v>82873</v>
+        <v>91540</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7537,34 +7537,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527133</v>
+        <v>527164</v>
       </c>
       <c r="R71" t="n">
-        <v>7087390</v>
+        <v>7087462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7611,22 +7611,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217911</v>
+        <v>129217853</v>
       </c>
       <c r="B72" t="n">
-        <v>91540</v>
+        <v>82873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7634,34 +7634,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527164</v>
+        <v>527133</v>
       </c>
       <c r="R72" t="n">
-        <v>7087462</v>
+        <v>7087390</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7708,12 +7708,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7805,12 +7805,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7907,12 +7907,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8009,12 +8009,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8106,12 +8106,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8203,22 +8203,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217841</v>
+        <v>129217912</v>
       </c>
       <c r="B78" t="n">
-        <v>91554</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,34 +8226,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527375</v>
+        <v>527089</v>
       </c>
       <c r="R78" t="n">
-        <v>7087521</v>
+        <v>7087260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8288,6 +8288,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8300,22 +8305,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217830</v>
+        <v>129217924</v>
       </c>
       <c r="B79" t="n">
-        <v>78054</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8323,34 +8328,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526990</v>
+        <v>527289</v>
       </c>
       <c r="R79" t="n">
-        <v>7087234</v>
+        <v>7087449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8397,22 +8402,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217912</v>
+        <v>129217841</v>
       </c>
       <c r="B80" t="n">
-        <v>80146</v>
+        <v>91554</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8420,34 +8425,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527089</v>
+        <v>527375</v>
       </c>
       <c r="R80" t="n">
-        <v>7087260</v>
+        <v>7087521</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8482,11 +8487,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8499,22 +8499,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217924</v>
+        <v>129217802</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8522,34 +8522,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527289</v>
+        <v>526934</v>
       </c>
       <c r="R81" t="n">
-        <v>7087449</v>
+        <v>7087213</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8584,6 +8584,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8596,44 +8601,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217921</v>
+        <v>129217929</v>
       </c>
       <c r="B82" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8643,10 +8648,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526984</v>
+        <v>527393</v>
       </c>
       <c r="R82" t="n">
-        <v>7087226</v>
+        <v>7087440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8683,7 +8688,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8698,22 +8703,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217914</v>
+        <v>129217921</v>
       </c>
       <c r="B83" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8745,10 +8750,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526928</v>
+        <v>526984</v>
       </c>
       <c r="R83" t="n">
-        <v>7087112</v>
+        <v>7087226</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8785,7 +8790,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8800,57 +8805,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217802</v>
+        <v>129217914</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526934</v>
+        <v>526928</v>
       </c>
       <c r="R84" t="n">
-        <v>7087213</v>
+        <v>7087112</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8887,7 +8892,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8902,22 +8907,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217929</v>
+        <v>129217830</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>78054</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8925,34 +8930,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527393</v>
+        <v>526990</v>
       </c>
       <c r="R85" t="n">
-        <v>7087440</v>
+        <v>7087234</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8987,11 +8992,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9004,12 +9004,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9019,7 +9019,7 @@
         <v>129217783</v>
       </c>
       <c r="B86" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9101,22 +9101,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217814</v>
+        <v>129217851</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9124,21 +9124,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526905</v>
+        <v>527094</v>
       </c>
       <c r="R87" t="n">
-        <v>7087117</v>
+        <v>7087264</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9203,57 +9203,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217915</v>
+        <v>129217814</v>
       </c>
       <c r="B88" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527145</v>
+        <v>526905</v>
       </c>
       <c r="R88" t="n">
-        <v>7087306</v>
+        <v>7087117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9305,22 +9305,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217851</v>
+        <v>129217847</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9328,23 +9328,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9352,10 +9348,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527094</v>
+        <v>527069</v>
       </c>
       <c r="R89" t="n">
-        <v>7087264</v>
+        <v>7087323</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9390,11 +9386,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -9407,53 +9398,57 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217847</v>
+        <v>129217915</v>
       </c>
       <c r="B90" t="n">
-        <v>91560</v>
+        <v>98706</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527069</v>
+        <v>527145</v>
       </c>
       <c r="R90" t="n">
-        <v>7087323</v>
+        <v>7087306</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9488,6 +9483,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -9500,12 +9500,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217815</v>
+        <v>129217849</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526883</v>
+        <v>526979</v>
       </c>
       <c r="R2" t="n">
-        <v>7087121</v>
+        <v>7087143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217918</v>
+        <v>129217850</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527262</v>
+        <v>527358</v>
       </c>
       <c r="R3" t="n">
-        <v>7087588</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217849</v>
+        <v>129217815</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526979</v>
+        <v>526883</v>
       </c>
       <c r="R4" t="n">
-        <v>7087143</v>
+        <v>7087121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217850</v>
+        <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527358</v>
+        <v>527262</v>
       </c>
       <c r="R5" t="n">
-        <v>7087435</v>
+        <v>7087588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
         <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129217831</v>
       </c>
       <c r="B8" t="n">
-        <v>80106</v>
+        <v>80108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217813</v>
+        <v>129217782</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>96956</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526901</v>
+        <v>527172</v>
       </c>
       <c r="R9" t="n">
-        <v>7087135</v>
+        <v>7087341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217798</v>
+        <v>129217856</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>92234</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527408</v>
+        <v>527386</v>
       </c>
       <c r="R10" t="n">
-        <v>7087464</v>
+        <v>7087522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,32 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217856</v>
+        <v>129217813</v>
       </c>
       <c r="B11" t="n">
-        <v>92231</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527386</v>
+        <v>526901</v>
       </c>
       <c r="R11" t="n">
-        <v>7087522</v>
+        <v>7087135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217782</v>
+        <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>96952</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1681,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527172</v>
+        <v>527408</v>
       </c>
       <c r="R12" t="n">
-        <v>7087341</v>
+        <v>7087464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,7 +1775,7 @@
         <v>129217927</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217785</v>
+        <v>129217795</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527106</v>
+        <v>527123</v>
       </c>
       <c r="R14" t="n">
-        <v>7087220</v>
+        <v>7087425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217780</v>
+        <v>129217855</v>
       </c>
       <c r="B15" t="n">
-        <v>83007</v>
+        <v>82877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1977,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527179</v>
+        <v>527012</v>
       </c>
       <c r="R15" t="n">
-        <v>7087518</v>
+        <v>7087233</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217925</v>
+        <v>129217840</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>91557</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,34 +2074,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527089</v>
+        <v>527386</v>
       </c>
       <c r="R16" t="n">
-        <v>7087260</v>
+        <v>7087517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217917</v>
+        <v>129217928</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>82877</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527273</v>
+        <v>527359</v>
       </c>
       <c r="R17" t="n">
-        <v>7087581</v>
+        <v>7087548</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,17 +2233,13 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2262,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217928</v>
+        <v>129217842</v>
       </c>
       <c r="B18" t="n">
-        <v>82873</v>
+        <v>91557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2273,34 +2269,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527359</v>
+        <v>527385</v>
       </c>
       <c r="R18" t="n">
-        <v>7087548</v>
+        <v>7087528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,7 +2337,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2360,10 +2355,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217842</v>
+        <v>129217852</v>
       </c>
       <c r="B19" t="n">
-        <v>91554</v>
+        <v>82877</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2371,21 +2366,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2395,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527385</v>
+        <v>527265</v>
       </c>
       <c r="R19" t="n">
-        <v>7087528</v>
+        <v>7087520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2457,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217852</v>
+        <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>82873</v>
+        <v>92261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2492,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527265</v>
+        <v>527368</v>
       </c>
       <c r="R20" t="n">
-        <v>7087520</v>
+        <v>7087576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2554,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217840</v>
+        <v>129217785</v>
       </c>
       <c r="B21" t="n">
-        <v>91554</v>
+        <v>91507</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527386</v>
+        <v>527106</v>
       </c>
       <c r="R21" t="n">
-        <v>7087517</v>
+        <v>7087220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2651,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217795</v>
+        <v>129217780</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>83011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2662,21 +2657,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2686,10 +2681,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527123</v>
+        <v>527179</v>
       </c>
       <c r="R22" t="n">
-        <v>7087425</v>
+        <v>7087518</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2748,10 +2743,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217855</v>
+        <v>129217925</v>
       </c>
       <c r="B23" t="n">
-        <v>82873</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2759,34 +2754,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527012</v>
+        <v>527089</v>
       </c>
       <c r="R23" t="n">
-        <v>7087233</v>
+        <v>7087260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2845,45 +2840,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217797</v>
+        <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>92258</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527368</v>
+        <v>527273</v>
       </c>
       <c r="R24" t="n">
-        <v>7087576</v>
+        <v>7087581</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2945,7 +2945,7 @@
         <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129217789</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>129217910</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>129217926</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,32 +3529,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217836</v>
+        <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527091</v>
+        <v>527291</v>
       </c>
       <c r="R31" t="n">
-        <v>7087273</v>
+        <v>7087491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217787</v>
+        <v>129217820</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,21 +3637,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527291</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>7087491</v>
+        <v>7087201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,6 +3697,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3723,10 +3728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,16 +3739,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3754,14 +3759,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R33" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3799,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217922</v>
+        <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>56908</v>
+        <v>98710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527122</v>
+        <v>527091</v>
       </c>
       <c r="R34" t="n">
-        <v>7087232</v>
+        <v>7087273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3925,7 +3925,7 @@
         <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217803</v>
+        <v>129217833</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526923</v>
+        <v>527351</v>
       </c>
       <c r="R38" t="n">
-        <v>7087199</v>
+        <v>7087510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4312,32 +4312,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217821</v>
+        <v>129217835</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526924</v>
+        <v>527103</v>
       </c>
       <c r="R39" t="n">
-        <v>7087187</v>
+        <v>7087341</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,11 +4383,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4414,32 +4409,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R40" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,7 +4484,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4516,32 +4511,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B41" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4551,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R41" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,6 +4582,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4616,7 +4616,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217826</v>
+        <v>129217838</v>
       </c>
       <c r="B44" t="n">
-        <v>80050</v>
+        <v>56908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527090</v>
+        <v>527239</v>
       </c>
       <c r="R44" t="n">
-        <v>7087261</v>
+        <v>7087332</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4907,7 +4907,7 @@
         <v>129217778</v>
       </c>
       <c r="B45" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5001,32 +5001,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217838</v>
+        <v>129217826</v>
       </c>
       <c r="B46" t="n">
-        <v>56908</v>
+        <v>80052</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527239</v>
+        <v>527090</v>
       </c>
       <c r="R46" t="n">
-        <v>7087332</v>
+        <v>7087261</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5101,7 +5101,7 @@
         <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5195,45 +5195,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217844</v>
+        <v>129217923</v>
       </c>
       <c r="B48" t="n">
-        <v>57719</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527355</v>
+        <v>527150</v>
       </c>
       <c r="R48" t="n">
-        <v>7087521</v>
+        <v>7087278</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5266,6 +5266,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5292,32 +5297,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217805</v>
+        <v>129217844</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57719</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5327,10 +5332,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>526924</v>
+        <v>527355</v>
       </c>
       <c r="R49" t="n">
-        <v>7087183</v>
+        <v>7087521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5363,11 +5368,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5394,10 +5394,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217923</v>
+        <v>129217805</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5405,34 +5405,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527150</v>
+        <v>526924</v>
       </c>
       <c r="R50" t="n">
-        <v>7087278</v>
+        <v>7087183</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5499,7 +5499,7 @@
         <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>129217794</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,45 +5695,65 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217837</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>526980</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087208</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5770,7 +5790,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5797,7 +5817,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5825,37 +5845,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,7 +5919,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217801</v>
+        <v>129217837</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527106</v>
+        <v>526980</v>
       </c>
       <c r="R56" t="n">
-        <v>7087348</v>
+        <v>7087208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217823</v>
+        <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>96956</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527374</v>
+        <v>527349</v>
       </c>
       <c r="R57" t="n">
-        <v>7087508</v>
+        <v>7087510</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,11 +6194,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4st</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6225,32 +6220,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217832</v>
+        <v>129217823</v>
       </c>
       <c r="B58" t="n">
-        <v>98706</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6260,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527149</v>
+        <v>527374</v>
       </c>
       <c r="R58" t="n">
-        <v>7087289</v>
+        <v>7087508</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6300,7 +6295,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6327,45 +6322,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217919</v>
+        <v>129217848</v>
       </c>
       <c r="B59" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527135</v>
+        <v>527106</v>
       </c>
       <c r="R59" t="n">
-        <v>7087449</v>
+        <v>7087367</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6402,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6429,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217834</v>
+        <v>129217832</v>
       </c>
       <c r="B60" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6464,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527268</v>
+        <v>527149</v>
       </c>
       <c r="R60" t="n">
-        <v>7087590</v>
+        <v>7087289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6504,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6531,45 +6526,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217784</v>
+        <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>96952</v>
+        <v>98710</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527349</v>
+        <v>527135</v>
       </c>
       <c r="R61" t="n">
-        <v>7087510</v>
+        <v>7087449</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6602,6 +6597,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6628,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217848</v>
+        <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527106</v>
+        <v>527268</v>
       </c>
       <c r="R62" t="n">
-        <v>7087367</v>
+        <v>7087590</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217829</v>
+        <v>129217854</v>
       </c>
       <c r="B63" t="n">
-        <v>91838</v>
+        <v>82877</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527138</v>
+        <v>527015</v>
       </c>
       <c r="R63" t="n">
-        <v>7087472</v>
+        <v>7087228</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6827,10 +6827,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217913</v>
+        <v>129217827</v>
       </c>
       <c r="B64" t="n">
-        <v>98706</v>
+        <v>91996</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6838,34 +6838,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526924</v>
+        <v>527136</v>
       </c>
       <c r="R64" t="n">
-        <v>7087085</v>
+        <v>7087471</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6898,11 +6898,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6929,32 +6924,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217827</v>
+        <v>129217829</v>
       </c>
       <c r="B65" t="n">
-        <v>91993</v>
+        <v>91841</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6964,10 +6959,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527136</v>
+        <v>527138</v>
       </c>
       <c r="R65" t="n">
-        <v>7087471</v>
+        <v>7087472</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7026,10 +7021,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217854</v>
+        <v>129217806</v>
       </c>
       <c r="B66" t="n">
-        <v>82873</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7037,21 +7032,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7061,10 +7056,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527015</v>
+        <v>526925</v>
       </c>
       <c r="R66" t="n">
-        <v>7087228</v>
+        <v>7087175</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7097,6 +7092,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7123,7 +7123,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217806</v>
+        <v>129217810</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526925</v>
+        <v>526914</v>
       </c>
       <c r="R67" t="n">
-        <v>7087175</v>
+        <v>7087139</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7225,7 +7225,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217810</v>
+        <v>129217818</v>
       </c>
       <c r="B68" t="n">
         <v>57727</v>
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>526914</v>
+        <v>527359</v>
       </c>
       <c r="R68" t="n">
-        <v>7087139</v>
+        <v>7087452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7327,45 +7327,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217818</v>
+        <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527359</v>
+        <v>526924</v>
       </c>
       <c r="R69" t="n">
-        <v>7087452</v>
+        <v>7087085</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7432,7 +7432,7 @@
         <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7526,10 +7526,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217911</v>
+        <v>129217853</v>
       </c>
       <c r="B71" t="n">
-        <v>91540</v>
+        <v>82877</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7537,34 +7537,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527164</v>
+        <v>527133</v>
       </c>
       <c r="R71" t="n">
-        <v>7087462</v>
+        <v>7087390</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7623,10 +7623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217853</v>
+        <v>129217911</v>
       </c>
       <c r="B72" t="n">
-        <v>82873</v>
+        <v>91543</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7634,34 +7634,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527133</v>
+        <v>527164</v>
       </c>
       <c r="R72" t="n">
-        <v>7087390</v>
+        <v>7087462</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7723,7 +7723,7 @@
         <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>129217825</v>
       </c>
       <c r="B77" t="n">
-        <v>80050</v>
+        <v>80052</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217912</v>
+        <v>129217841</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>91557</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,34 +8226,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527089</v>
+        <v>527375</v>
       </c>
       <c r="R78" t="n">
-        <v>7087260</v>
+        <v>7087521</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,11 +8286,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8317,10 +8312,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217924</v>
+        <v>129217802</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8328,34 +8323,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527289</v>
+        <v>526934</v>
       </c>
       <c r="R79" t="n">
-        <v>7087449</v>
+        <v>7087213</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8388,6 +8383,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8414,10 +8414,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217841</v>
+        <v>129217929</v>
       </c>
       <c r="B80" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8425,34 +8425,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527375</v>
+        <v>527393</v>
       </c>
       <c r="R80" t="n">
-        <v>7087521</v>
+        <v>7087440</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8485,6 +8485,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8511,45 +8516,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217802</v>
+        <v>129217921</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526934</v>
+        <v>526984</v>
       </c>
       <c r="R81" t="n">
-        <v>7087213</v>
+        <v>7087226</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8586,7 +8591,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8613,32 +8618,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217929</v>
+        <v>129217914</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8648,10 +8653,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527393</v>
+        <v>526928</v>
       </c>
       <c r="R82" t="n">
-        <v>7087440</v>
+        <v>7087112</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8688,7 +8693,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8715,45 +8720,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217921</v>
+        <v>129217830</v>
       </c>
       <c r="B83" t="n">
-        <v>98706</v>
+        <v>78056</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526984</v>
+        <v>526990</v>
       </c>
       <c r="R83" t="n">
-        <v>7087226</v>
+        <v>7087234</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8786,11 +8791,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8817,32 +8817,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217914</v>
+        <v>129217924</v>
       </c>
       <c r="B84" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526928</v>
+        <v>527289</v>
       </c>
       <c r="R84" t="n">
-        <v>7087112</v>
+        <v>7087449</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8888,11 +8888,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8919,10 +8914,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217830</v>
+        <v>129217912</v>
       </c>
       <c r="B85" t="n">
-        <v>78054</v>
+        <v>80148</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8930,34 +8925,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526990</v>
+        <v>527089</v>
       </c>
       <c r="R85" t="n">
-        <v>7087234</v>
+        <v>7087260</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8990,6 +8985,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9016,10 +9016,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217783</v>
+        <v>129217851</v>
       </c>
       <c r="B86" t="n">
-        <v>96952</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9027,21 +9027,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527221</v>
+        <v>527094</v>
       </c>
       <c r="R86" t="n">
-        <v>7087348</v>
+        <v>7087264</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9087,6 +9087,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9113,10 +9118,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217851</v>
+        <v>129217814</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9124,21 +9129,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9148,10 +9153,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527094</v>
+        <v>526905</v>
       </c>
       <c r="R87" t="n">
-        <v>7087264</v>
+        <v>7087117</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9188,7 +9193,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9215,10 +9220,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217814</v>
+        <v>129217783</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>96956</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9226,21 +9231,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9250,10 +9255,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>526905</v>
+        <v>527221</v>
       </c>
       <c r="R88" t="n">
-        <v>7087117</v>
+        <v>7087348</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9286,11 +9291,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9320,7 +9320,7 @@
         <v>129217847</v>
       </c>
       <c r="B89" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>129217915</v>
       </c>
       <c r="B90" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217795</v>
+        <v>129217797</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>92261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527123</v>
+        <v>527368</v>
       </c>
       <c r="R14" t="n">
-        <v>7087425</v>
+        <v>7087576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217855</v>
+        <v>129217785</v>
       </c>
       <c r="B15" t="n">
-        <v>82877</v>
+        <v>91507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527012</v>
+        <v>527106</v>
       </c>
       <c r="R15" t="n">
-        <v>7087233</v>
+        <v>7087220</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217840</v>
+        <v>129217780</v>
       </c>
       <c r="B16" t="n">
-        <v>91557</v>
+        <v>83011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527386</v>
+        <v>527179</v>
       </c>
       <c r="R16" t="n">
-        <v>7087517</v>
+        <v>7087518</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,10 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217928</v>
+        <v>129217925</v>
       </c>
       <c r="B17" t="n">
-        <v>82877</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527359</v>
+        <v>527089</v>
       </c>
       <c r="R17" t="n">
-        <v>7087548</v>
+        <v>7087260</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2239,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2258,45 +2257,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217842</v>
+        <v>129217917</v>
       </c>
       <c r="B18" t="n">
-        <v>91557</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527385</v>
+        <v>527273</v>
       </c>
       <c r="R18" t="n">
-        <v>7087528</v>
+        <v>7087581</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,6 +2328,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2355,10 +2359,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217852</v>
+        <v>129217795</v>
       </c>
       <c r="B19" t="n">
-        <v>82877</v>
+        <v>91543</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2366,21 +2370,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2390,10 +2394,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527265</v>
+        <v>527123</v>
       </c>
       <c r="R19" t="n">
-        <v>7087520</v>
+        <v>7087425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,32 +2456,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217797</v>
+        <v>129217855</v>
       </c>
       <c r="B20" t="n">
-        <v>92261</v>
+        <v>82877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2491,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527368</v>
+        <v>527012</v>
       </c>
       <c r="R20" t="n">
-        <v>7087576</v>
+        <v>7087233</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,32 +2553,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217785</v>
+        <v>129217840</v>
       </c>
       <c r="B21" t="n">
-        <v>91507</v>
+        <v>91557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527106</v>
+        <v>527386</v>
       </c>
       <c r="R21" t="n">
-        <v>7087220</v>
+        <v>7087517</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,10 +2650,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217780</v>
+        <v>129217928</v>
       </c>
       <c r="B22" t="n">
-        <v>83011</v>
+        <v>82877</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2657,34 +2661,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527179</v>
+        <v>527359</v>
       </c>
       <c r="R22" t="n">
-        <v>7087518</v>
+        <v>7087548</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,6 +2729,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2743,10 +2748,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217925</v>
+        <v>129217842</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>91557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2754,34 +2759,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527089</v>
+        <v>527385</v>
       </c>
       <c r="R23" t="n">
-        <v>7087260</v>
+        <v>7087528</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2840,45 +2845,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217917</v>
+        <v>129217852</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>82877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527273</v>
+        <v>527265</v>
       </c>
       <c r="R24" t="n">
-        <v>7087581</v>
+        <v>7087520</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,11 +2916,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6220,10 +6220,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217823</v>
+        <v>129217848</v>
       </c>
       <c r="B58" t="n">
-        <v>57887</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6231,21 +6231,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527374</v>
+        <v>527106</v>
       </c>
       <c r="R58" t="n">
-        <v>7087508</v>
+        <v>7087367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,32 +6322,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217848</v>
+        <v>129217832</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527106</v>
+        <v>527149</v>
       </c>
       <c r="R59" t="n">
-        <v>7087367</v>
+        <v>7087289</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,7 +6424,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B60" t="n">
         <v>98710</v>
@@ -6455,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R60" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,7 +6526,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217919</v>
+        <v>129217834</v>
       </c>
       <c r="B61" t="n">
         <v>98710</v>
@@ -6557,14 +6557,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527135</v>
+        <v>527268</v>
       </c>
       <c r="R61" t="n">
-        <v>7087449</v>
+        <v>7087590</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6628,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217834</v>
+        <v>129217823</v>
       </c>
       <c r="B62" t="n">
-        <v>98710</v>
+        <v>57887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527268</v>
+        <v>527374</v>
       </c>
       <c r="R62" t="n">
-        <v>7087590</v>
+        <v>7087508</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217854</v>
+        <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>82877</v>
+        <v>91841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527015</v>
+        <v>527138</v>
       </c>
       <c r="R63" t="n">
-        <v>7087228</v>
+        <v>7087472</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6827,32 +6827,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217827</v>
+        <v>129217854</v>
       </c>
       <c r="B64" t="n">
-        <v>91996</v>
+        <v>82877</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527136</v>
+        <v>527015</v>
       </c>
       <c r="R64" t="n">
-        <v>7087471</v>
+        <v>7087228</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6924,32 +6924,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217829</v>
+        <v>129217827</v>
       </c>
       <c r="B65" t="n">
-        <v>91841</v>
+        <v>91996</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527138</v>
+        <v>527136</v>
       </c>
       <c r="R65" t="n">
-        <v>7087472</v>
+        <v>7087471</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217841</v>
+        <v>129217802</v>
       </c>
       <c r="B78" t="n">
-        <v>91557</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,21 +8226,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527375</v>
+        <v>526934</v>
       </c>
       <c r="R78" t="n">
-        <v>7087521</v>
+        <v>7087213</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,6 +8286,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8312,7 +8317,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217802</v>
+        <v>129217929</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8343,14 +8348,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526934</v>
+        <v>527393</v>
       </c>
       <c r="R79" t="n">
-        <v>7087213</v>
+        <v>7087440</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8414,10 +8419,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217929</v>
+        <v>129217912</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8425,21 +8430,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8449,10 +8454,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527393</v>
+        <v>527089</v>
       </c>
       <c r="R80" t="n">
-        <v>7087440</v>
+        <v>7087260</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8489,7 +8494,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8516,45 +8521,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217921</v>
+        <v>129217830</v>
       </c>
       <c r="B81" t="n">
-        <v>98710</v>
+        <v>78056</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526984</v>
+        <v>526990</v>
       </c>
       <c r="R81" t="n">
-        <v>7087226</v>
+        <v>7087234</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8587,11 +8592,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8618,45 +8618,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217914</v>
+        <v>129217841</v>
       </c>
       <c r="B82" t="n">
-        <v>98710</v>
+        <v>91557</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526928</v>
+        <v>527375</v>
       </c>
       <c r="R82" t="n">
-        <v>7087112</v>
+        <v>7087521</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8689,11 +8689,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8720,10 +8715,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217830</v>
+        <v>129217924</v>
       </c>
       <c r="B83" t="n">
-        <v>78056</v>
+        <v>79043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8731,34 +8726,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526990</v>
+        <v>527289</v>
       </c>
       <c r="R83" t="n">
-        <v>7087234</v>
+        <v>7087449</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8817,32 +8812,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217924</v>
+        <v>129217921</v>
       </c>
       <c r="B84" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8852,10 +8847,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527289</v>
+        <v>526984</v>
       </c>
       <c r="R84" t="n">
-        <v>7087449</v>
+        <v>7087226</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8888,6 +8883,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8914,32 +8914,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217912</v>
+        <v>129217914</v>
       </c>
       <c r="B85" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527089</v>
+        <v>526928</v>
       </c>
       <c r="R85" t="n">
-        <v>7087260</v>
+        <v>7087112</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129217849</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129217850</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217791</v>
+        <v>129217831</v>
       </c>
       <c r="B6" t="n">
-        <v>91543</v>
+        <v>80109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527219</v>
+        <v>527362</v>
       </c>
       <c r="R6" t="n">
-        <v>7087542</v>
+        <v>7087507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217831</v>
+        <v>129217799</v>
       </c>
       <c r="B8" t="n">
-        <v>80108</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527362</v>
+        <v>527399</v>
       </c>
       <c r="R8" t="n">
-        <v>7087507</v>
+        <v>7087454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217782</v>
+        <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>96956</v>
+        <v>92236</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527172</v>
+        <v>527386</v>
       </c>
       <c r="R9" t="n">
-        <v>7087341</v>
+        <v>7087522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217856</v>
+        <v>129217782</v>
       </c>
       <c r="B10" t="n">
-        <v>92234</v>
+        <v>96958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527386</v>
+        <v>527172</v>
       </c>
       <c r="R10" t="n">
-        <v>7087522</v>
+        <v>7087341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1775,7 +1775,7 @@
         <v>129217927</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217797</v>
+        <v>129217795</v>
       </c>
       <c r="B14" t="n">
-        <v>92261</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527368</v>
+        <v>527123</v>
       </c>
       <c r="R14" t="n">
-        <v>7087576</v>
+        <v>7087425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217785</v>
+        <v>129217855</v>
       </c>
       <c r="B15" t="n">
-        <v>91507</v>
+        <v>82878</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527106</v>
+        <v>527012</v>
       </c>
       <c r="R15" t="n">
-        <v>7087220</v>
+        <v>7087233</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217780</v>
+        <v>129217840</v>
       </c>
       <c r="B16" t="n">
-        <v>83011</v>
+        <v>91559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527179</v>
+        <v>527386</v>
       </c>
       <c r="R16" t="n">
-        <v>7087518</v>
+        <v>7087517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,10 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217925</v>
+        <v>129217928</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>82878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527089</v>
+        <v>527359</v>
       </c>
       <c r="R17" t="n">
-        <v>7087260</v>
+        <v>7087548</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,6 +2239,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2257,45 +2258,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217917</v>
+        <v>129217842</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>91559</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527273</v>
+        <v>527385</v>
       </c>
       <c r="R18" t="n">
-        <v>7087581</v>
+        <v>7087528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,11 +2329,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2359,10 +2355,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217795</v>
+        <v>129217852</v>
       </c>
       <c r="B19" t="n">
-        <v>91543</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2370,21 +2366,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2394,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527123</v>
+        <v>527265</v>
       </c>
       <c r="R19" t="n">
-        <v>7087425</v>
+        <v>7087520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,10 +2452,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217855</v>
+        <v>129217780</v>
       </c>
       <c r="B20" t="n">
-        <v>82877</v>
+        <v>83012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2467,21 +2463,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2491,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527012</v>
+        <v>527179</v>
       </c>
       <c r="R20" t="n">
-        <v>7087233</v>
+        <v>7087518</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2553,10 +2549,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217840</v>
+        <v>129217925</v>
       </c>
       <c r="B21" t="n">
-        <v>91557</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,34 +2560,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527386</v>
+        <v>527089</v>
       </c>
       <c r="R21" t="n">
-        <v>7087517</v>
+        <v>7087260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2650,32 +2646,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217928</v>
+        <v>129217917</v>
       </c>
       <c r="B22" t="n">
-        <v>82877</v>
+        <v>98712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2685,10 +2681,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527359</v>
+        <v>527273</v>
       </c>
       <c r="R22" t="n">
-        <v>7087548</v>
+        <v>7087581</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,13 +2719,17 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2748,32 +2748,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217842</v>
+        <v>129217797</v>
       </c>
       <c r="B23" t="n">
-        <v>91557</v>
+        <v>92263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527385</v>
+        <v>527368</v>
       </c>
       <c r="R23" t="n">
-        <v>7087528</v>
+        <v>7087576</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2845,32 +2845,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217852</v>
+        <v>129217785</v>
       </c>
       <c r="B24" t="n">
-        <v>82877</v>
+        <v>91509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527265</v>
+        <v>527106</v>
       </c>
       <c r="R24" t="n">
-        <v>7087520</v>
+        <v>7087220</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2945,7 +2945,7 @@
         <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217789</v>
+        <v>129217926</v>
       </c>
       <c r="B27" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527376</v>
+        <v>527029</v>
       </c>
       <c r="R27" t="n">
-        <v>7087516</v>
+        <v>7087194</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217910</v>
+        <v>129217807</v>
       </c>
       <c r="B28" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,34 +3244,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527288</v>
+        <v>526921</v>
       </c>
       <c r="R28" t="n">
-        <v>7087491</v>
+        <v>7087159</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,6 +3304,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217926</v>
+        <v>129217789</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,34 +3346,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527029</v>
+        <v>527376</v>
       </c>
       <c r="R29" t="n">
-        <v>7087194</v>
+        <v>7087516</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217807</v>
+        <v>129217910</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3438,34 +3443,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>526921</v>
+        <v>527288</v>
       </c>
       <c r="R30" t="n">
-        <v>7087159</v>
+        <v>7087491</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217787</v>
+        <v>129217820</v>
       </c>
       <c r="B31" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527291</v>
+        <v>527034</v>
       </c>
       <c r="R31" t="n">
-        <v>7087491</v>
+        <v>7087201</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,6 +3600,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3626,10 +3631,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217820</v>
+        <v>129217787</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,21 +3642,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3666,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527291</v>
       </c>
       <c r="R32" t="n">
-        <v>7087201</v>
+        <v>7087491</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,11 +3702,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3828,7 +3828,7 @@
         <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,10 +4117,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217845</v>
+        <v>129217803</v>
       </c>
       <c r="B37" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4128,19 +4128,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4148,10 +4152,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527173</v>
+        <v>526923</v>
       </c>
       <c r="R37" t="n">
-        <v>7087380</v>
+        <v>7087199</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,6 +4188,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4210,32 +4219,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217833</v>
+        <v>129217821</v>
       </c>
       <c r="B38" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4254,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527351</v>
+        <v>526924</v>
       </c>
       <c r="R38" t="n">
-        <v>7087510</v>
+        <v>7087187</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4285,7 +4294,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4312,34 +4321,30 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217835</v>
+        <v>129217845</v>
       </c>
       <c r="B39" t="n">
-        <v>98710</v>
+        <v>91565</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4347,10 +4352,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527103</v>
+        <v>527173</v>
       </c>
       <c r="R39" t="n">
-        <v>7087341</v>
+        <v>7087380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4409,32 +4414,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217803</v>
+        <v>129217833</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526923</v>
+        <v>527351</v>
       </c>
       <c r="R40" t="n">
-        <v>7087199</v>
+        <v>7087510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,7 +4489,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4511,32 +4516,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217821</v>
+        <v>129217835</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4551,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526924</v>
+        <v>527103</v>
       </c>
       <c r="R41" t="n">
-        <v>7087187</v>
+        <v>7087341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4582,11 +4587,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4616,7 +4616,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217838</v>
+        <v>129217826</v>
       </c>
       <c r="B44" t="n">
-        <v>56908</v>
+        <v>80053</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527239</v>
+        <v>527090</v>
       </c>
       <c r="R44" t="n">
-        <v>7087332</v>
+        <v>7087261</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4907,7 +4907,7 @@
         <v>129217778</v>
       </c>
       <c r="B45" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5001,32 +5001,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217826</v>
+        <v>129217838</v>
       </c>
       <c r="B46" t="n">
-        <v>80052</v>
+        <v>56908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527090</v>
+        <v>527239</v>
       </c>
       <c r="R46" t="n">
-        <v>7087261</v>
+        <v>7087332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5101,7 +5101,7 @@
         <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>129217923</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217794</v>
+        <v>129217819</v>
       </c>
       <c r="B52" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5609,34 +5609,54 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527134</v>
+        <v>527070</v>
       </c>
       <c r="R52" t="n">
-        <v>7087464</v>
+        <v>7087285</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5669,6 +5689,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5695,7 +5720,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -5723,37 +5748,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5790,7 +5795,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5817,7 +5822,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5852,10 +5857,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5897,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,32 +5924,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217837</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5954,10 +5959,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>526980</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087208</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5999,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,32 +6026,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217837</v>
+        <v>129217794</v>
       </c>
       <c r="B56" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6061,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526980</v>
+        <v>527134</v>
       </c>
       <c r="R56" t="n">
-        <v>7087208</v>
+        <v>7087464</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6092,11 +6097,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6126,7 +6126,7 @@
         <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217848</v>
+        <v>129217832</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527106</v>
+        <v>527149</v>
       </c>
       <c r="R58" t="n">
-        <v>7087367</v>
+        <v>7087289</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B59" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6353,14 +6353,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R59" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217919</v>
+        <v>129217834</v>
       </c>
       <c r="B60" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6455,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527135</v>
+        <v>527268</v>
       </c>
       <c r="R60" t="n">
-        <v>7087449</v>
+        <v>7087590</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,32 +6526,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217834</v>
+        <v>129217848</v>
       </c>
       <c r="B61" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527268</v>
+        <v>527106</v>
       </c>
       <c r="R61" t="n">
-        <v>7087590</v>
+        <v>7087367</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6730,45 +6730,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217829</v>
+        <v>129217913</v>
       </c>
       <c r="B63" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527138</v>
+        <v>526924</v>
       </c>
       <c r="R63" t="n">
-        <v>7087472</v>
+        <v>7087085</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6801,6 +6801,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6827,10 +6832,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217854</v>
+        <v>129217829</v>
       </c>
       <c r="B64" t="n">
-        <v>82877</v>
+        <v>91843</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6838,21 +6843,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6862,10 +6867,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527015</v>
+        <v>527138</v>
       </c>
       <c r="R64" t="n">
-        <v>7087228</v>
+        <v>7087472</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6924,32 +6929,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217827</v>
+        <v>129217854</v>
       </c>
       <c r="B65" t="n">
-        <v>91996</v>
+        <v>82878</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6959,10 +6964,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527136</v>
+        <v>527015</v>
       </c>
       <c r="R65" t="n">
-        <v>7087471</v>
+        <v>7087228</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7021,32 +7026,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217806</v>
+        <v>129217827</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91998</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7056,10 +7061,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526925</v>
+        <v>527136</v>
       </c>
       <c r="R66" t="n">
-        <v>7087175</v>
+        <v>7087471</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7092,11 +7097,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7123,7 +7123,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217810</v>
+        <v>129217806</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526914</v>
+        <v>526925</v>
       </c>
       <c r="R67" t="n">
-        <v>7087139</v>
+        <v>7087175</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7225,7 +7225,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217818</v>
+        <v>129217810</v>
       </c>
       <c r="B68" t="n">
         <v>57727</v>
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527359</v>
+        <v>526914</v>
       </c>
       <c r="R68" t="n">
-        <v>7087452</v>
+        <v>7087139</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7327,45 +7327,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217913</v>
+        <v>129217818</v>
       </c>
       <c r="B69" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526924</v>
+        <v>527359</v>
       </c>
       <c r="R69" t="n">
-        <v>7087085</v>
+        <v>7087452</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7432,7 +7432,7 @@
         <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>129217853</v>
       </c>
       <c r="B71" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>129217911</v>
       </c>
       <c r="B72" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>129217825</v>
       </c>
       <c r="B77" t="n">
-        <v>80052</v>
+        <v>80053</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217802</v>
+        <v>129217924</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,34 +8226,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>526934</v>
+        <v>527289</v>
       </c>
       <c r="R78" t="n">
-        <v>7087213</v>
+        <v>7087449</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,11 +8286,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8317,10 +8312,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217929</v>
+        <v>129217912</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8328,21 +8323,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8352,10 +8347,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527393</v>
+        <v>527089</v>
       </c>
       <c r="R79" t="n">
-        <v>7087440</v>
+        <v>7087260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8392,7 +8387,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8419,32 +8414,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217912</v>
+        <v>129217921</v>
       </c>
       <c r="B80" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8454,10 +8449,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527089</v>
+        <v>526984</v>
       </c>
       <c r="R80" t="n">
-        <v>7087260</v>
+        <v>7087226</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8494,7 +8489,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8521,45 +8516,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217830</v>
+        <v>129217914</v>
       </c>
       <c r="B81" t="n">
-        <v>78056</v>
+        <v>98712</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526990</v>
+        <v>526928</v>
       </c>
       <c r="R81" t="n">
-        <v>7087234</v>
+        <v>7087112</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8592,6 +8587,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8618,10 +8618,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217841</v>
+        <v>129217830</v>
       </c>
       <c r="B82" t="n">
-        <v>91557</v>
+        <v>78057</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8629,21 +8629,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1204</v>
+        <v>228579</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527375</v>
+        <v>526990</v>
       </c>
       <c r="R82" t="n">
-        <v>7087521</v>
+        <v>7087234</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217924</v>
+        <v>129217841</v>
       </c>
       <c r="B83" t="n">
-        <v>79043</v>
+        <v>91559</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>527289</v>
+        <v>527375</v>
       </c>
       <c r="R83" t="n">
-        <v>7087449</v>
+        <v>7087521</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8812,45 +8812,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217921</v>
+        <v>129217802</v>
       </c>
       <c r="B84" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526984</v>
+        <v>526934</v>
       </c>
       <c r="R84" t="n">
-        <v>7087226</v>
+        <v>7087213</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8914,32 +8914,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217914</v>
+        <v>129217929</v>
       </c>
       <c r="B85" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8949,10 +8949,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526928</v>
+        <v>527393</v>
       </c>
       <c r="R85" t="n">
-        <v>7087112</v>
+        <v>7087440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9016,10 +9016,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217851</v>
+        <v>129217783</v>
       </c>
       <c r="B86" t="n">
-        <v>79043</v>
+        <v>96958</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9027,21 +9027,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527094</v>
+        <v>527221</v>
       </c>
       <c r="R86" t="n">
-        <v>7087264</v>
+        <v>7087348</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9087,11 +9087,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9118,10 +9113,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217814</v>
+        <v>129217847</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>91565</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9129,23 +9124,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9153,10 +9144,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526905</v>
+        <v>527069</v>
       </c>
       <c r="R87" t="n">
-        <v>7087117</v>
+        <v>7087323</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9189,11 +9180,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9220,10 +9206,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217783</v>
+        <v>129217851</v>
       </c>
       <c r="B88" t="n">
-        <v>96956</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9231,21 +9217,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9255,10 +9241,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527221</v>
+        <v>527094</v>
       </c>
       <c r="R88" t="n">
-        <v>7087348</v>
+        <v>7087264</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9291,6 +9277,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9317,41 +9308,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217847</v>
+        <v>129217915</v>
       </c>
       <c r="B89" t="n">
-        <v>91563</v>
+        <v>98712</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527069</v>
+        <v>527145</v>
       </c>
       <c r="R89" t="n">
-        <v>7087323</v>
+        <v>7087306</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9384,6 +9379,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9410,45 +9410,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217915</v>
+        <v>129217814</v>
       </c>
       <c r="B90" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527145</v>
+        <v>526905</v>
       </c>
       <c r="R90" t="n">
-        <v>7087306</v>
+        <v>7087117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217831</v>
+        <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>80109</v>
+        <v>91549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527362</v>
+        <v>527219</v>
       </c>
       <c r="R6" t="n">
-        <v>7087507</v>
+        <v>7087542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R7" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R8" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,7 +1377,7 @@
         <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>92236</v>
+        <v>92240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129217782</v>
       </c>
       <c r="B10" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217795</v>
+        <v>129217928</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>82878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527123</v>
+        <v>527359</v>
       </c>
       <c r="R14" t="n">
-        <v>7087425</v>
+        <v>7087548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,6 +1948,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217855</v>
+        <v>129217842</v>
       </c>
       <c r="B15" t="n">
-        <v>82878</v>
+        <v>91563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1978,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527012</v>
+        <v>527385</v>
       </c>
       <c r="R15" t="n">
-        <v>7087233</v>
+        <v>7087528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217840</v>
+        <v>129217852</v>
       </c>
       <c r="B16" t="n">
-        <v>91559</v>
+        <v>82878</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527386</v>
+        <v>527265</v>
       </c>
       <c r="R16" t="n">
-        <v>7087517</v>
+        <v>7087520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217928</v>
+        <v>129217840</v>
       </c>
       <c r="B17" t="n">
-        <v>82878</v>
+        <v>91563</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,34 +2172,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527359</v>
+        <v>527386</v>
       </c>
       <c r="R17" t="n">
-        <v>7087548</v>
+        <v>7087517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2239,7 +2240,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217842</v>
+        <v>129217795</v>
       </c>
       <c r="B18" t="n">
-        <v>91559</v>
+        <v>91549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527385</v>
+        <v>527123</v>
       </c>
       <c r="R18" t="n">
-        <v>7087528</v>
+        <v>7087425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217852</v>
+        <v>129217855</v>
       </c>
       <c r="B19" t="n">
         <v>82878</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527265</v>
+        <v>527012</v>
       </c>
       <c r="R19" t="n">
-        <v>7087520</v>
+        <v>7087233</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217780</v>
+        <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>83012</v>
+        <v>92267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527179</v>
+        <v>527368</v>
       </c>
       <c r="R20" t="n">
-        <v>7087518</v>
+        <v>7087576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,45 +2549,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217925</v>
+        <v>129217785</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>91513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527089</v>
+        <v>527106</v>
       </c>
       <c r="R21" t="n">
-        <v>7087260</v>
+        <v>7087220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,45 +2646,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217917</v>
+        <v>129217780</v>
       </c>
       <c r="B22" t="n">
-        <v>98712</v>
+        <v>83012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527273</v>
+        <v>527179</v>
       </c>
       <c r="R22" t="n">
-        <v>7087581</v>
+        <v>7087518</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,11 +2717,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2748,45 +2743,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217797</v>
+        <v>129217925</v>
       </c>
       <c r="B23" t="n">
-        <v>92263</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527368</v>
+        <v>527089</v>
       </c>
       <c r="R23" t="n">
-        <v>7087576</v>
+        <v>7087260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2845,45 +2840,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217785</v>
+        <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>91509</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527106</v>
+        <v>527273</v>
       </c>
       <c r="R24" t="n">
-        <v>7087220</v>
+        <v>7087581</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2945,7 +2945,7 @@
         <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217926</v>
+        <v>129217789</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527029</v>
+        <v>527376</v>
       </c>
       <c r="R27" t="n">
-        <v>7087194</v>
+        <v>7087516</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217807</v>
+        <v>129217910</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,34 +3244,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>526921</v>
+        <v>527288</v>
       </c>
       <c r="R28" t="n">
-        <v>7087159</v>
+        <v>7087491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,11 +3304,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217789</v>
+        <v>129217926</v>
       </c>
       <c r="B29" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3346,34 +3341,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527376</v>
+        <v>527029</v>
       </c>
       <c r="R29" t="n">
-        <v>7087516</v>
+        <v>7087194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217910</v>
+        <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,34 +3438,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527288</v>
+        <v>526921</v>
       </c>
       <c r="R30" t="n">
-        <v>7087491</v>
+        <v>7087159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217820</v>
+        <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527034</v>
+        <v>527291</v>
       </c>
       <c r="R31" t="n">
-        <v>7087201</v>
+        <v>7087491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,11 +3600,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3631,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217787</v>
+        <v>129217820</v>
       </c>
       <c r="B32" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3642,21 +3637,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3666,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527291</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>7087491</v>
+        <v>7087201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3702,6 +3697,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3828,7 +3828,7 @@
         <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4117,10 +4117,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217803</v>
+        <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4128,23 +4128,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4152,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526923</v>
+        <v>527173</v>
       </c>
       <c r="R37" t="n">
-        <v>7087199</v>
+        <v>7087380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,11 +4184,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4219,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217821</v>
+        <v>129217833</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4254,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526924</v>
+        <v>527351</v>
       </c>
       <c r="R38" t="n">
-        <v>7087187</v>
+        <v>7087510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4294,7 +4285,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4321,30 +4312,34 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217845</v>
+        <v>129217835</v>
       </c>
       <c r="B39" t="n">
-        <v>91565</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4352,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527173</v>
+        <v>527103</v>
       </c>
       <c r="R39" t="n">
-        <v>7087380</v>
+        <v>7087341</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4414,32 +4409,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B40" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R40" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,7 +4484,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4516,32 +4511,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B41" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4551,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R41" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,6 +4582,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4616,7 +4616,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217790</v>
+        <v>129217923</v>
       </c>
       <c r="B47" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5109,34 +5109,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527357</v>
+        <v>527150</v>
       </c>
       <c r="R47" t="n">
-        <v>7087574</v>
+        <v>7087278</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5169,6 +5169,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5195,10 +5200,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5206,34 +5211,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R48" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5266,11 +5271,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5499,7 +5499,7 @@
         <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5598,65 +5598,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217819</v>
+        <v>129217837</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527070</v>
+        <v>526980</v>
       </c>
       <c r="R52" t="n">
-        <v>7087285</v>
+        <v>7087208</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5693,7 +5673,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5720,10 +5700,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217800</v>
+        <v>129217794</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5731,21 +5711,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5755,10 +5735,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527297</v>
+        <v>527134</v>
       </c>
       <c r="R53" t="n">
-        <v>7087514</v>
+        <v>7087464</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5791,11 +5771,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5822,7 +5797,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217801</v>
+        <v>129217819</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5850,17 +5825,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527106</v>
+        <v>527070</v>
       </c>
       <c r="R54" t="n">
-        <v>7087348</v>
+        <v>7087285</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5897,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5924,32 +5919,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217837</v>
+        <v>129217800</v>
       </c>
       <c r="B55" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5959,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>526980</v>
+        <v>527297</v>
       </c>
       <c r="R55" t="n">
-        <v>7087208</v>
+        <v>7087514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5999,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6026,10 +6021,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217794</v>
+        <v>129217801</v>
       </c>
       <c r="B56" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6037,21 +6032,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6061,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527134</v>
+        <v>527106</v>
       </c>
       <c r="R56" t="n">
-        <v>7087464</v>
+        <v>7087348</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6097,6 +6092,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6126,7 +6126,7 @@
         <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217832</v>
+        <v>129217848</v>
       </c>
       <c r="B58" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527149</v>
+        <v>527106</v>
       </c>
       <c r="R58" t="n">
-        <v>7087289</v>
+        <v>7087367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217919</v>
+        <v>129217832</v>
       </c>
       <c r="B59" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6353,14 +6353,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527135</v>
+        <v>527149</v>
       </c>
       <c r="R59" t="n">
-        <v>7087449</v>
+        <v>7087289</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217834</v>
+        <v>129217919</v>
       </c>
       <c r="B60" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6455,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527268</v>
+        <v>527135</v>
       </c>
       <c r="R60" t="n">
-        <v>7087590</v>
+        <v>7087449</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,32 +6526,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217848</v>
+        <v>129217834</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527106</v>
+        <v>527268</v>
       </c>
       <c r="R61" t="n">
-        <v>7087367</v>
+        <v>7087590</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217913</v>
+        <v>129217827</v>
       </c>
       <c r="B63" t="n">
-        <v>98712</v>
+        <v>92002</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,34 +6741,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>526924</v>
+        <v>527136</v>
       </c>
       <c r="R63" t="n">
-        <v>7087085</v>
+        <v>7087471</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6801,11 +6801,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6832,10 +6827,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217829</v>
+        <v>129217806</v>
       </c>
       <c r="B64" t="n">
-        <v>91843</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6843,21 +6838,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6867,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527138</v>
+        <v>526925</v>
       </c>
       <c r="R64" t="n">
-        <v>7087472</v>
+        <v>7087175</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6903,6 +6898,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6929,10 +6929,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217854</v>
+        <v>129217810</v>
       </c>
       <c r="B65" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527015</v>
+        <v>526914</v>
       </c>
       <c r="R65" t="n">
-        <v>7087228</v>
+        <v>7087139</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7000,6 +7000,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7026,32 +7031,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217827</v>
+        <v>129217818</v>
       </c>
       <c r="B66" t="n">
-        <v>91998</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7061,10 +7066,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527136</v>
+        <v>527359</v>
       </c>
       <c r="R66" t="n">
-        <v>7087471</v>
+        <v>7087452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7097,6 +7102,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7123,45 +7133,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217806</v>
+        <v>129217913</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526925</v>
+        <v>526924</v>
       </c>
       <c r="R67" t="n">
-        <v>7087175</v>
+        <v>7087085</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7198,7 +7208,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7225,10 +7235,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217810</v>
+        <v>129217829</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>91847</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,21 +7246,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7260,10 +7270,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>526914</v>
+        <v>527138</v>
       </c>
       <c r="R68" t="n">
-        <v>7087139</v>
+        <v>7087472</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7296,11 +7306,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7327,10 +7332,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217818</v>
+        <v>129217854</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7338,21 +7343,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7362,10 +7367,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527359</v>
+        <v>527015</v>
       </c>
       <c r="R69" t="n">
-        <v>7087452</v>
+        <v>7087228</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7398,11 +7403,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217786</v>
+        <v>129217804</v>
       </c>
       <c r="B70" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527238</v>
+        <v>526927</v>
       </c>
       <c r="R70" t="n">
-        <v>7087520</v>
+        <v>7087193</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7500,6 +7500,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7526,10 +7531,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217853</v>
+        <v>129217808</v>
       </c>
       <c r="B71" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7537,21 +7542,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7561,10 +7566,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527133</v>
+        <v>526917</v>
       </c>
       <c r="R71" t="n">
-        <v>7087390</v>
+        <v>7087144</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7597,6 +7602,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7623,10 +7633,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217911</v>
+        <v>129217786</v>
       </c>
       <c r="B72" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7654,14 +7664,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527164</v>
+        <v>527238</v>
       </c>
       <c r="R72" t="n">
-        <v>7087462</v>
+        <v>7087520</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7720,10 +7730,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217781</v>
+        <v>129217911</v>
       </c>
       <c r="B73" t="n">
-        <v>83012</v>
+        <v>91549</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7731,34 +7741,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527141</v>
+        <v>527164</v>
       </c>
       <c r="R73" t="n">
-        <v>7087466</v>
+        <v>7087462</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7817,10 +7827,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217804</v>
+        <v>129217853</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7828,21 +7838,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7852,10 +7862,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526927</v>
+        <v>527133</v>
       </c>
       <c r="R74" t="n">
-        <v>7087193</v>
+        <v>7087390</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7888,11 +7898,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7919,10 +7924,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217808</v>
+        <v>129217781</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7930,21 +7935,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7954,10 +7959,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526917</v>
+        <v>527141</v>
       </c>
       <c r="R75" t="n">
-        <v>7087144</v>
+        <v>7087466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7990,11 +7995,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8024,7 +8024,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8215,32 +8215,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217924</v>
+        <v>129217921</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527289</v>
+        <v>526984</v>
       </c>
       <c r="R78" t="n">
-        <v>7087449</v>
+        <v>7087226</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,6 +8286,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8312,32 +8317,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217912</v>
+        <v>129217914</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8347,10 +8352,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527089</v>
+        <v>526928</v>
       </c>
       <c r="R79" t="n">
-        <v>7087260</v>
+        <v>7087112</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8387,7 +8392,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8414,45 +8419,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217921</v>
+        <v>129217841</v>
       </c>
       <c r="B80" t="n">
-        <v>98712</v>
+        <v>91563</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526984</v>
+        <v>527375</v>
       </c>
       <c r="R80" t="n">
-        <v>7087226</v>
+        <v>7087521</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8485,11 +8490,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8516,32 +8516,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217914</v>
+        <v>129217912</v>
       </c>
       <c r="B81" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526928</v>
+        <v>527089</v>
       </c>
       <c r="R81" t="n">
-        <v>7087112</v>
+        <v>7087260</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8618,10 +8618,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217830</v>
+        <v>129217924</v>
       </c>
       <c r="B82" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8629,34 +8629,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526990</v>
+        <v>527289</v>
       </c>
       <c r="R82" t="n">
-        <v>7087234</v>
+        <v>7087449</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217841</v>
+        <v>129217802</v>
       </c>
       <c r="B83" t="n">
-        <v>91559</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>527375</v>
+        <v>526934</v>
       </c>
       <c r="R83" t="n">
-        <v>7087521</v>
+        <v>7087213</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8786,6 +8786,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8812,7 +8817,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217802</v>
+        <v>129217929</v>
       </c>
       <c r="B84" t="n">
         <v>57727</v>
@@ -8843,14 +8848,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526934</v>
+        <v>527393</v>
       </c>
       <c r="R84" t="n">
-        <v>7087213</v>
+        <v>7087440</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8914,10 +8919,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217929</v>
+        <v>129217830</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8925,34 +8930,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527393</v>
+        <v>526990</v>
       </c>
       <c r="R85" t="n">
-        <v>7087440</v>
+        <v>7087234</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8985,11 +8990,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9016,45 +9016,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217783</v>
+        <v>129217915</v>
       </c>
       <c r="B86" t="n">
-        <v>96958</v>
+        <v>98716</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527221</v>
+        <v>527145</v>
       </c>
       <c r="R86" t="n">
-        <v>7087348</v>
+        <v>7087306</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9087,6 +9087,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9113,10 +9118,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217847</v>
+        <v>129217783</v>
       </c>
       <c r="B87" t="n">
-        <v>91565</v>
+        <v>96962</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9124,19 +9129,23 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9144,10 +9153,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527069</v>
+        <v>527221</v>
       </c>
       <c r="R87" t="n">
-        <v>7087323</v>
+        <v>7087348</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9206,10 +9215,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217851</v>
+        <v>129217847</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>91569</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9217,23 +9226,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9241,10 +9246,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527094</v>
+        <v>527069</v>
       </c>
       <c r="R88" t="n">
-        <v>7087264</v>
+        <v>7087323</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9277,11 +9282,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9308,45 +9308,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217915</v>
+        <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527145</v>
+        <v>527094</v>
       </c>
       <c r="R89" t="n">
-        <v>7087306</v>
+        <v>7087264</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B6" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R6" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217831</v>
+        <v>129217791</v>
       </c>
       <c r="B8" t="n">
-        <v>80109</v>
+        <v>91550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527362</v>
+        <v>527219</v>
       </c>
       <c r="R8" t="n">
-        <v>7087507</v>
+        <v>7087542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217856</v>
+        <v>129217782</v>
       </c>
       <c r="B9" t="n">
-        <v>92240</v>
+        <v>96970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527386</v>
+        <v>527172</v>
       </c>
       <c r="R9" t="n">
-        <v>7087522</v>
+        <v>7087341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217782</v>
+        <v>129217856</v>
       </c>
       <c r="B10" t="n">
-        <v>96962</v>
+        <v>92241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527172</v>
+        <v>527386</v>
       </c>
       <c r="R10" t="n">
-        <v>7087341</v>
+        <v>7087522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1970,7 +1970,7 @@
         <v>129217842</v>
       </c>
       <c r="B15" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>129217840</v>
       </c>
       <c r="B17" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>129217795</v>
       </c>
       <c r="B18" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2549,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217785</v>
+        <v>129217780</v>
       </c>
       <c r="B21" t="n">
-        <v>91513</v>
+        <v>83012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527106</v>
+        <v>527179</v>
       </c>
       <c r="R21" t="n">
-        <v>7087220</v>
+        <v>7087518</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217780</v>
+        <v>129217925</v>
       </c>
       <c r="B22" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2657,34 +2657,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527179</v>
+        <v>527089</v>
       </c>
       <c r="R22" t="n">
-        <v>7087518</v>
+        <v>7087260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,32 +2743,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217925</v>
+        <v>129217917</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527089</v>
+        <v>527273</v>
       </c>
       <c r="R23" t="n">
-        <v>7087260</v>
+        <v>7087581</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,6 +2814,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2840,45 +2845,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217917</v>
+        <v>129217785</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>91514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527273</v>
+        <v>527106</v>
       </c>
       <c r="R24" t="n">
-        <v>7087581</v>
+        <v>7087220</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,11 +2916,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2945,7 +2945,7 @@
         <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>129217789</v>
       </c>
       <c r="B27" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>129217910</v>
       </c>
       <c r="B28" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217926</v>
+        <v>129217807</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,34 +3341,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527029</v>
+        <v>526921</v>
       </c>
       <c r="R29" t="n">
-        <v>7087194</v>
+        <v>7087159</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,6 +3401,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3427,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217807</v>
+        <v>129217926</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3438,34 +3443,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>526921</v>
+        <v>527029</v>
       </c>
       <c r="R30" t="n">
-        <v>7087159</v>
+        <v>7087194</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217787</v>
+        <v>129217922</v>
       </c>
       <c r="B31" t="n">
-        <v>91549</v>
+        <v>56908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,34 +3540,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527291</v>
+        <v>527122</v>
       </c>
       <c r="R31" t="n">
-        <v>7087491</v>
+        <v>7087232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217820</v>
+        <v>129217787</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,21 +3637,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527291</v>
       </c>
       <c r="R32" t="n">
-        <v>7087201</v>
+        <v>7087491</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,11 +3697,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3728,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217922</v>
+        <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3739,16 +3734,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3759,14 +3754,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527122</v>
+        <v>527034</v>
       </c>
       <c r="R33" t="n">
-        <v>7087232</v>
+        <v>7087201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3799,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3828,7 +3828,7 @@
         <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R38" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4312,32 +4312,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R39" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,6 +4383,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4409,32 +4414,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217803</v>
+        <v>129217833</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4444,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526923</v>
+        <v>527351</v>
       </c>
       <c r="R40" t="n">
-        <v>7087199</v>
+        <v>7087510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4484,7 +4489,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4511,32 +4516,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217821</v>
+        <v>129217835</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4551,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526924</v>
+        <v>527103</v>
       </c>
       <c r="R41" t="n">
-        <v>7087187</v>
+        <v>7087341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4582,11 +4587,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4616,7 +4616,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5109,34 +5109,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R47" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5169,11 +5169,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5200,10 +5195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217790</v>
+        <v>129217923</v>
       </c>
       <c r="B48" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5211,34 +5206,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527357</v>
+        <v>527150</v>
       </c>
       <c r="R48" t="n">
-        <v>7087574</v>
+        <v>7087278</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5271,6 +5266,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5297,45 +5297,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217844</v>
+        <v>129217920</v>
       </c>
       <c r="B49" t="n">
-        <v>57719</v>
+        <v>98724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527355</v>
+        <v>527064</v>
       </c>
       <c r="R49" t="n">
-        <v>7087521</v>
+        <v>7087252</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5368,6 +5368,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5394,32 +5399,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217805</v>
+        <v>129217844</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57719</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5429,10 +5434,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>526924</v>
+        <v>527355</v>
       </c>
       <c r="R50" t="n">
-        <v>7087183</v>
+        <v>7087521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5465,11 +5470,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5496,45 +5496,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217920</v>
+        <v>129217805</v>
       </c>
       <c r="B51" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527064</v>
+        <v>526924</v>
       </c>
       <c r="R51" t="n">
-        <v>7087252</v>
+        <v>7087183</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5598,32 +5598,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217837</v>
+        <v>129217794</v>
       </c>
       <c r="B52" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>526980</v>
+        <v>527134</v>
       </c>
       <c r="R52" t="n">
-        <v>7087208</v>
+        <v>7087464</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5669,11 +5669,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5700,10 +5695,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217794</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5711,34 +5706,54 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527134</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087464</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,6 +5786,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5797,7 +5817,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5825,37 +5845,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,7 +5919,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217801</v>
+        <v>129217837</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527106</v>
+        <v>526980</v>
       </c>
       <c r="R56" t="n">
-        <v>7087348</v>
+        <v>7087208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6126,7 +6126,7 @@
         <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217848</v>
+        <v>129217832</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527106</v>
+        <v>527149</v>
       </c>
       <c r="R58" t="n">
-        <v>7087367</v>
+        <v>7087289</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B59" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6353,14 +6353,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R59" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217919</v>
+        <v>129217834</v>
       </c>
       <c r="B60" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6455,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527135</v>
+        <v>527268</v>
       </c>
       <c r="R60" t="n">
-        <v>7087449</v>
+        <v>7087590</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,32 +6526,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217834</v>
+        <v>129217848</v>
       </c>
       <c r="B61" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527268</v>
+        <v>527106</v>
       </c>
       <c r="R61" t="n">
-        <v>7087590</v>
+        <v>7087367</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6730,32 +6730,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217827</v>
+        <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>92002</v>
+        <v>91848</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527136</v>
+        <v>527138</v>
       </c>
       <c r="R63" t="n">
-        <v>7087471</v>
+        <v>7087472</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6827,32 +6827,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217806</v>
+        <v>129217827</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>92003</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526925</v>
+        <v>527136</v>
       </c>
       <c r="R64" t="n">
-        <v>7087175</v>
+        <v>7087471</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6898,11 +6898,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6929,10 +6924,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217810</v>
+        <v>129217854</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6940,21 +6935,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6964,10 +6959,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526914</v>
+        <v>527015</v>
       </c>
       <c r="R65" t="n">
-        <v>7087139</v>
+        <v>7087228</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7000,11 +6995,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7031,7 +7021,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217818</v>
+        <v>129217806</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -7066,10 +7056,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527359</v>
+        <v>526925</v>
       </c>
       <c r="R66" t="n">
-        <v>7087452</v>
+        <v>7087175</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7133,45 +7123,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217913</v>
+        <v>129217810</v>
       </c>
       <c r="B67" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526924</v>
+        <v>526914</v>
       </c>
       <c r="R67" t="n">
-        <v>7087085</v>
+        <v>7087139</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7208,7 +7198,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7235,10 +7225,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217829</v>
+        <v>129217818</v>
       </c>
       <c r="B68" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7246,21 +7236,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7270,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527138</v>
+        <v>527359</v>
       </c>
       <c r="R68" t="n">
-        <v>7087472</v>
+        <v>7087452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7306,6 +7296,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7332,45 +7327,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217854</v>
+        <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>82878</v>
+        <v>98724</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527015</v>
+        <v>526924</v>
       </c>
       <c r="R69" t="n">
-        <v>7087228</v>
+        <v>7087085</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7403,6 +7398,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217804</v>
+        <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>526927</v>
+        <v>527238</v>
       </c>
       <c r="R70" t="n">
-        <v>7087193</v>
+        <v>7087520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7500,11 +7500,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7531,10 +7526,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217808</v>
+        <v>129217911</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7542,34 +7537,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526917</v>
+        <v>527164</v>
       </c>
       <c r="R71" t="n">
-        <v>7087144</v>
+        <v>7087462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7602,11 +7597,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7633,10 +7623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217786</v>
+        <v>129217853</v>
       </c>
       <c r="B72" t="n">
-        <v>91549</v>
+        <v>82878</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7644,21 +7634,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7668,10 +7658,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527238</v>
+        <v>527133</v>
       </c>
       <c r="R72" t="n">
-        <v>7087520</v>
+        <v>7087390</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7730,10 +7720,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217911</v>
+        <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>91549</v>
+        <v>83012</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7741,34 +7731,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527164</v>
+        <v>527141</v>
       </c>
       <c r="R73" t="n">
-        <v>7087462</v>
+        <v>7087466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7827,10 +7817,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217853</v>
+        <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7838,21 +7828,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7862,10 +7852,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527133</v>
+        <v>526927</v>
       </c>
       <c r="R74" t="n">
-        <v>7087390</v>
+        <v>7087193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7898,6 +7888,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7924,10 +7919,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217781</v>
+        <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7935,21 +7930,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7959,10 +7954,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527141</v>
+        <v>526917</v>
       </c>
       <c r="R75" t="n">
-        <v>7087466</v>
+        <v>7087144</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7995,6 +7990,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8024,7 +8024,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8215,45 +8215,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217921</v>
+        <v>129217841</v>
       </c>
       <c r="B78" t="n">
-        <v>98716</v>
+        <v>91564</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>526984</v>
+        <v>527375</v>
       </c>
       <c r="R78" t="n">
-        <v>7087226</v>
+        <v>7087521</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,11 +8286,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8317,45 +8312,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217914</v>
+        <v>129217802</v>
       </c>
       <c r="B79" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526928</v>
+        <v>526934</v>
       </c>
       <c r="R79" t="n">
-        <v>7087112</v>
+        <v>7087213</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8392,7 +8387,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8419,10 +8414,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217841</v>
+        <v>129217929</v>
       </c>
       <c r="B80" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8430,34 +8425,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527375</v>
+        <v>527393</v>
       </c>
       <c r="R80" t="n">
-        <v>7087521</v>
+        <v>7087440</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8490,6 +8485,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8516,32 +8516,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217912</v>
+        <v>129217921</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527089</v>
+        <v>526984</v>
       </c>
       <c r="R81" t="n">
-        <v>7087260</v>
+        <v>7087226</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8618,32 +8618,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217924</v>
+        <v>129217914</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527289</v>
+        <v>526928</v>
       </c>
       <c r="R82" t="n">
-        <v>7087449</v>
+        <v>7087112</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8689,6 +8689,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8715,10 +8720,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217802</v>
+        <v>129217830</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8726,21 +8731,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8750,10 +8755,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526934</v>
+        <v>526990</v>
       </c>
       <c r="R83" t="n">
-        <v>7087213</v>
+        <v>7087234</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8786,11 +8791,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8817,10 +8817,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217929</v>
+        <v>129217912</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8828,21 +8828,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8852,10 +8852,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527393</v>
+        <v>527089</v>
       </c>
       <c r="R84" t="n">
-        <v>7087440</v>
+        <v>7087260</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8919,10 +8919,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217830</v>
+        <v>129217924</v>
       </c>
       <c r="B85" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8930,34 +8930,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526990</v>
+        <v>527289</v>
       </c>
       <c r="R85" t="n">
-        <v>7087234</v>
+        <v>7087449</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9016,45 +9016,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217915</v>
+        <v>129217783</v>
       </c>
       <c r="B86" t="n">
-        <v>98716</v>
+        <v>96970</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527145</v>
+        <v>527221</v>
       </c>
       <c r="R86" t="n">
-        <v>7087306</v>
+        <v>7087348</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9087,11 +9087,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9118,10 +9113,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217783</v>
+        <v>129217851</v>
       </c>
       <c r="B87" t="n">
-        <v>96962</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9129,21 +9124,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9153,10 +9148,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527221</v>
+        <v>527094</v>
       </c>
       <c r="R87" t="n">
-        <v>7087348</v>
+        <v>7087264</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9189,6 +9184,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9218,7 +9218,7 @@
         <v>129217847</v>
       </c>
       <c r="B88" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9308,10 +9308,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217851</v>
+        <v>129217814</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9319,21 +9319,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9343,10 +9343,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527094</v>
+        <v>526905</v>
       </c>
       <c r="R89" t="n">
-        <v>7087264</v>
+        <v>7087117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9410,45 +9410,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217814</v>
+        <v>129217915</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>526905</v>
+        <v>527145</v>
       </c>
       <c r="R90" t="n">
-        <v>7087117</v>
+        <v>7087306</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217850</v>
+        <v>129217815</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527358</v>
+        <v>526883</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217815</v>
+        <v>129217850</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526883</v>
+        <v>527358</v>
       </c>
       <c r="R4" t="n">
-        <v>7087121</v>
+        <v>7087435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R6" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217831</v>
+        <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>80109</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527362</v>
+        <v>527399</v>
       </c>
       <c r="R7" t="n">
-        <v>7087507</v>
+        <v>7087454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217791</v>
+        <v>129217831</v>
       </c>
       <c r="B8" t="n">
-        <v>91550</v>
+        <v>80109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527219</v>
+        <v>527362</v>
       </c>
       <c r="R8" t="n">
-        <v>7087542</v>
+        <v>7087507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217928</v>
+        <v>129217925</v>
       </c>
       <c r="B14" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527359</v>
+        <v>527089</v>
       </c>
       <c r="R14" t="n">
-        <v>7087548</v>
+        <v>7087260</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1948,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,45 +1966,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217842</v>
+        <v>129217917</v>
       </c>
       <c r="B15" t="n">
-        <v>91564</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527385</v>
+        <v>527273</v>
       </c>
       <c r="R15" t="n">
-        <v>7087528</v>
+        <v>7087581</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,6 +2037,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2064,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217852</v>
+        <v>129217795</v>
       </c>
       <c r="B16" t="n">
-        <v>82878</v>
+        <v>91550</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2079,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527265</v>
+        <v>527123</v>
       </c>
       <c r="R16" t="n">
-        <v>7087520</v>
+        <v>7087425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217840</v>
+        <v>129217928</v>
       </c>
       <c r="B17" t="n">
-        <v>91564</v>
+        <v>82878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,34 +2176,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527386</v>
+        <v>527359</v>
       </c>
       <c r="R17" t="n">
-        <v>7087517</v>
+        <v>7087548</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,6 +2244,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2258,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217795</v>
+        <v>129217842</v>
       </c>
       <c r="B18" t="n">
-        <v>91550</v>
+        <v>91564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2274,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2298,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527123</v>
+        <v>527385</v>
       </c>
       <c r="R18" t="n">
-        <v>7087425</v>
+        <v>7087528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,7 +2360,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217855</v>
+        <v>129217852</v>
       </c>
       <c r="B19" t="n">
         <v>82878</v>
@@ -2390,10 +2395,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527012</v>
+        <v>527265</v>
       </c>
       <c r="R19" t="n">
-        <v>7087233</v>
+        <v>7087520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,32 +2457,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217797</v>
+        <v>129217840</v>
       </c>
       <c r="B20" t="n">
-        <v>92268</v>
+        <v>91564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527368</v>
+        <v>527386</v>
       </c>
       <c r="R20" t="n">
-        <v>7087576</v>
+        <v>7087517</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,10 +2554,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217780</v>
+        <v>129217855</v>
       </c>
       <c r="B21" t="n">
-        <v>83012</v>
+        <v>82878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2560,21 +2565,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527179</v>
+        <v>527012</v>
       </c>
       <c r="R21" t="n">
-        <v>7087518</v>
+        <v>7087233</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,45 +2651,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217925</v>
+        <v>129217797</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>92268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527089</v>
+        <v>527368</v>
       </c>
       <c r="R22" t="n">
-        <v>7087260</v>
+        <v>7087576</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,45 +2748,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217917</v>
+        <v>129217785</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>91514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527273</v>
+        <v>527106</v>
       </c>
       <c r="R23" t="n">
-        <v>7087581</v>
+        <v>7087220</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,11 +2819,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2845,32 +2845,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217785</v>
+        <v>129217780</v>
       </c>
       <c r="B24" t="n">
-        <v>91514</v>
+        <v>83012</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527106</v>
+        <v>527179</v>
       </c>
       <c r="R24" t="n">
-        <v>7087220</v>
+        <v>7087518</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217807</v>
+        <v>129217926</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,34 +3341,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>526921</v>
+        <v>527029</v>
       </c>
       <c r="R29" t="n">
-        <v>7087159</v>
+        <v>7087194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,11 +3401,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217926</v>
+        <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,34 +3438,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527029</v>
+        <v>526921</v>
       </c>
       <c r="R30" t="n">
-        <v>7087194</v>
+        <v>7087159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217922</v>
+        <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>56908</v>
+        <v>91550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,34 +3540,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527122</v>
+        <v>527291</v>
       </c>
       <c r="R31" t="n">
-        <v>7087232</v>
+        <v>7087491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217787</v>
+        <v>129217820</v>
       </c>
       <c r="B32" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,21 +3637,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527291</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>7087491</v>
+        <v>7087201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,6 +3697,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3723,10 +3728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,16 +3739,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3754,14 +3759,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R33" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3799,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4210,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217803</v>
+        <v>129217833</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526923</v>
+        <v>527351</v>
       </c>
       <c r="R38" t="n">
-        <v>7087199</v>
+        <v>7087510</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4312,32 +4312,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217821</v>
+        <v>129217835</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526924</v>
+        <v>527103</v>
       </c>
       <c r="R39" t="n">
-        <v>7087187</v>
+        <v>7087341</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,11 +4383,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4414,32 +4409,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R40" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,7 +4484,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4516,32 +4511,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4551,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R41" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4587,6 +4582,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5297,45 +5297,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217920</v>
+        <v>129217844</v>
       </c>
       <c r="B49" t="n">
-        <v>98724</v>
+        <v>57719</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527064</v>
+        <v>527355</v>
       </c>
       <c r="R49" t="n">
-        <v>7087252</v>
+        <v>7087521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5368,11 +5368,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5399,32 +5394,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217844</v>
+        <v>129217805</v>
       </c>
       <c r="B50" t="n">
-        <v>57719</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5434,10 +5429,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527355</v>
+        <v>526924</v>
       </c>
       <c r="R50" t="n">
-        <v>7087521</v>
+        <v>7087183</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,6 +5465,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5496,45 +5496,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217805</v>
+        <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>526924</v>
+        <v>527064</v>
       </c>
       <c r="R51" t="n">
-        <v>7087183</v>
+        <v>7087252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217784</v>
+        <v>129217823</v>
       </c>
       <c r="B57" t="n">
-        <v>96970</v>
+        <v>57887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527349</v>
+        <v>527374</v>
       </c>
       <c r="R57" t="n">
-        <v>7087510</v>
+        <v>7087508</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,6 +6194,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6220,32 +6225,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217832</v>
+        <v>129217784</v>
       </c>
       <c r="B58" t="n">
-        <v>98724</v>
+        <v>96970</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527149</v>
+        <v>527349</v>
       </c>
       <c r="R58" t="n">
-        <v>7087289</v>
+        <v>7087510</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6291,11 +6296,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,45 +6322,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217919</v>
+        <v>129217848</v>
       </c>
       <c r="B59" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527135</v>
+        <v>527106</v>
       </c>
       <c r="R59" t="n">
-        <v>7087449</v>
+        <v>7087367</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,7 +6424,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217834</v>
+        <v>129217832</v>
       </c>
       <c r="B60" t="n">
         <v>98724</v>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527268</v>
+        <v>527149</v>
       </c>
       <c r="R60" t="n">
-        <v>7087590</v>
+        <v>7087289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,45 +6526,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217848</v>
+        <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527106</v>
+        <v>527135</v>
       </c>
       <c r="R61" t="n">
-        <v>7087367</v>
+        <v>7087449</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6628,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217823</v>
+        <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527374</v>
+        <v>527268</v>
       </c>
       <c r="R62" t="n">
-        <v>7087508</v>
+        <v>7087590</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217829</v>
+        <v>129217806</v>
       </c>
       <c r="B63" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527138</v>
+        <v>526925</v>
       </c>
       <c r="R63" t="n">
-        <v>7087472</v>
+        <v>7087175</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6801,6 +6801,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6827,32 +6832,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217827</v>
+        <v>129217810</v>
       </c>
       <c r="B64" t="n">
-        <v>92003</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6862,10 +6867,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527136</v>
+        <v>526914</v>
       </c>
       <c r="R64" t="n">
-        <v>7087471</v>
+        <v>7087139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6898,6 +6903,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6924,10 +6934,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217854</v>
+        <v>129217818</v>
       </c>
       <c r="B65" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6935,21 +6945,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6959,10 +6969,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527015</v>
+        <v>527359</v>
       </c>
       <c r="R65" t="n">
-        <v>7087228</v>
+        <v>7087452</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6995,6 +7005,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7021,10 +7036,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217806</v>
+        <v>129217829</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7032,21 +7047,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7056,10 +7071,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526925</v>
+        <v>527138</v>
       </c>
       <c r="R66" t="n">
-        <v>7087175</v>
+        <v>7087472</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7092,11 +7107,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7123,32 +7133,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217810</v>
+        <v>129217827</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>92003</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7158,10 +7168,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526914</v>
+        <v>527136</v>
       </c>
       <c r="R67" t="n">
-        <v>7087139</v>
+        <v>7087471</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7194,11 +7204,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7225,10 +7230,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217818</v>
+        <v>129217854</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,21 +7241,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7260,10 +7265,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527359</v>
+        <v>527015</v>
       </c>
       <c r="R68" t="n">
-        <v>7087452</v>
+        <v>7087228</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7296,11 +7301,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8312,10 +8312,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217802</v>
+        <v>129217912</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8323,34 +8323,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526934</v>
+        <v>527089</v>
       </c>
       <c r="R79" t="n">
-        <v>7087213</v>
+        <v>7087260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8414,10 +8414,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217929</v>
+        <v>129217924</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8425,21 +8425,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527393</v>
+        <v>527289</v>
       </c>
       <c r="R80" t="n">
-        <v>7087440</v>
+        <v>7087449</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8485,11 +8485,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8817,10 +8812,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217912</v>
+        <v>129217802</v>
       </c>
       <c r="B84" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8828,34 +8823,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527089</v>
+        <v>526934</v>
       </c>
       <c r="R84" t="n">
-        <v>7087260</v>
+        <v>7087213</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8892,7 +8887,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8919,10 +8914,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217924</v>
+        <v>129217929</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8930,21 +8925,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8954,10 +8949,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527289</v>
+        <v>527393</v>
       </c>
       <c r="R85" t="n">
-        <v>7087449</v>
+        <v>7087440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8990,6 +8985,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9113,10 +9113,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217851</v>
+        <v>129217814</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9124,21 +9124,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527094</v>
+        <v>526905</v>
       </c>
       <c r="R87" t="n">
-        <v>7087264</v>
+        <v>7087117</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9215,41 +9215,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217847</v>
+        <v>129217915</v>
       </c>
       <c r="B88" t="n">
-        <v>91570</v>
+        <v>98724</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527069</v>
+        <v>527145</v>
       </c>
       <c r="R88" t="n">
-        <v>7087323</v>
+        <v>7087306</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9282,6 +9286,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9308,10 +9317,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217814</v>
+        <v>129217847</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9319,23 +9328,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9343,10 +9348,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526905</v>
+        <v>527069</v>
       </c>
       <c r="R89" t="n">
-        <v>7087117</v>
+        <v>7087323</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9379,11 +9384,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9410,45 +9410,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217915</v>
+        <v>129217851</v>
       </c>
       <c r="B90" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527145</v>
+        <v>527094</v>
       </c>
       <c r="R90" t="n">
-        <v>7087306</v>
+        <v>7087264</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B6" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R6" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>80109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217831</v>
+        <v>129217791</v>
       </c>
       <c r="B8" t="n">
-        <v>80109</v>
+        <v>91550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527362</v>
+        <v>527219</v>
       </c>
       <c r="R8" t="n">
-        <v>7087507</v>
+        <v>7087542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217925</v>
+        <v>129217795</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527089</v>
+        <v>527123</v>
       </c>
       <c r="R14" t="n">
-        <v>7087260</v>
+        <v>7087425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217917</v>
+        <v>129217928</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>82878</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527273</v>
+        <v>527359</v>
       </c>
       <c r="R15" t="n">
-        <v>7087581</v>
+        <v>7087548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2039,17 +2039,13 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2068,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217795</v>
+        <v>129217842</v>
       </c>
       <c r="B16" t="n">
-        <v>91550</v>
+        <v>91564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2103,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527123</v>
+        <v>527385</v>
       </c>
       <c r="R16" t="n">
-        <v>7087425</v>
+        <v>7087528</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,7 +2161,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217928</v>
+        <v>129217852</v>
       </c>
       <c r="B17" t="n">
         <v>82878</v>
@@ -2196,14 +2192,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527359</v>
+        <v>527265</v>
       </c>
       <c r="R17" t="n">
-        <v>7087548</v>
+        <v>7087520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2244,7 +2240,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2263,7 +2258,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217842</v>
+        <v>129217840</v>
       </c>
       <c r="B18" t="n">
         <v>91564</v>
@@ -2298,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527385</v>
+        <v>527386</v>
       </c>
       <c r="R18" t="n">
-        <v>7087528</v>
+        <v>7087517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,7 +2355,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217852</v>
+        <v>129217855</v>
       </c>
       <c r="B19" t="n">
         <v>82878</v>
@@ -2395,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527265</v>
+        <v>527012</v>
       </c>
       <c r="R19" t="n">
-        <v>7087520</v>
+        <v>7087233</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2457,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217840</v>
+        <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>91564</v>
+        <v>92268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2492,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527386</v>
+        <v>527368</v>
       </c>
       <c r="R20" t="n">
-        <v>7087517</v>
+        <v>7087576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2554,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217855</v>
+        <v>129217785</v>
       </c>
       <c r="B21" t="n">
-        <v>82878</v>
+        <v>91514</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527012</v>
+        <v>527106</v>
       </c>
       <c r="R21" t="n">
-        <v>7087233</v>
+        <v>7087220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2651,32 +2646,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217797</v>
+        <v>129217780</v>
       </c>
       <c r="B22" t="n">
-        <v>92268</v>
+        <v>83012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2686,10 +2681,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527368</v>
+        <v>527179</v>
       </c>
       <c r="R22" t="n">
-        <v>7087576</v>
+        <v>7087518</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2748,45 +2743,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217785</v>
+        <v>129217925</v>
       </c>
       <c r="B23" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527106</v>
+        <v>527089</v>
       </c>
       <c r="R23" t="n">
-        <v>7087220</v>
+        <v>7087260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2845,45 +2840,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217780</v>
+        <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>83012</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527179</v>
+        <v>527273</v>
       </c>
       <c r="R24" t="n">
-        <v>7087518</v>
+        <v>7087581</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2942,10 +2942,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129217793</v>
+        <v>129217779</v>
       </c>
       <c r="B25" t="n">
-        <v>91550</v>
+        <v>83012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527167</v>
+        <v>527248</v>
       </c>
       <c r="R25" t="n">
-        <v>7087461</v>
+        <v>7087513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129217779</v>
+        <v>129217793</v>
       </c>
       <c r="B26" t="n">
-        <v>83012</v>
+        <v>91550</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527248</v>
+        <v>527167</v>
       </c>
       <c r="R26" t="n">
-        <v>7087513</v>
+        <v>7087461</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129217846</v>
+        <v>129217812</v>
       </c>
       <c r="B35" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,19 +3933,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3953,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527139</v>
+        <v>526904</v>
       </c>
       <c r="R35" t="n">
-        <v>7087468</v>
+        <v>7087132</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3989,6 +3993,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4015,10 +4024,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129217812</v>
+        <v>129217846</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4026,23 +4035,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4050,10 +4055,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>526904</v>
+        <v>527139</v>
       </c>
       <c r="R36" t="n">
-        <v>7087132</v>
+        <v>7087468</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4086,11 +4091,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4117,10 +4117,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217845</v>
+        <v>129217821</v>
       </c>
       <c r="B37" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4128,19 +4128,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4148,10 +4152,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527173</v>
+        <v>526924</v>
       </c>
       <c r="R37" t="n">
-        <v>7087380</v>
+        <v>7087187</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,6 +4188,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4210,7 +4219,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217833</v>
+        <v>129217835</v>
       </c>
       <c r="B38" t="n">
         <v>98724</v>
@@ -4245,10 +4254,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527351</v>
+        <v>527103</v>
       </c>
       <c r="R38" t="n">
-        <v>7087510</v>
+        <v>7087341</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,11 +4290,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4312,32 +4316,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217835</v>
+        <v>129217803</v>
       </c>
       <c r="B39" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4347,10 +4351,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527103</v>
+        <v>526923</v>
       </c>
       <c r="R39" t="n">
-        <v>7087341</v>
+        <v>7087199</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,6 +4387,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4409,10 +4418,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217803</v>
+        <v>129217845</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4420,23 +4429,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4444,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526923</v>
+        <v>527173</v>
       </c>
       <c r="R40" t="n">
-        <v>7087199</v>
+        <v>7087380</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4480,11 +4485,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4511,32 +4511,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217821</v>
+        <v>129217833</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526924</v>
+        <v>527351</v>
       </c>
       <c r="R41" t="n">
-        <v>7087187</v>
+        <v>7087510</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5695,65 +5695,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217837</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>526980</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087208</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5790,7 +5770,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5817,7 +5797,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217819</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5845,17 +5825,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>527070</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087285</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,7 +5919,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217800</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>527297</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217837</v>
+        <v>129217801</v>
       </c>
       <c r="B56" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526980</v>
+        <v>527106</v>
       </c>
       <c r="R56" t="n">
-        <v>7087208</v>
+        <v>7087348</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217806</v>
+        <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>526925</v>
+        <v>527138</v>
       </c>
       <c r="R63" t="n">
-        <v>7087175</v>
+        <v>7087472</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6801,11 +6801,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6832,7 +6827,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217810</v>
+        <v>129217806</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -6867,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526914</v>
+        <v>526925</v>
       </c>
       <c r="R64" t="n">
-        <v>7087139</v>
+        <v>7087175</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6907,7 +6902,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6934,7 +6929,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217818</v>
+        <v>129217810</v>
       </c>
       <c r="B65" t="n">
         <v>57727</v>
@@ -6969,10 +6964,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527359</v>
+        <v>526914</v>
       </c>
       <c r="R65" t="n">
-        <v>7087452</v>
+        <v>7087139</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7009,7 +7004,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7036,10 +7031,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217829</v>
+        <v>129217818</v>
       </c>
       <c r="B66" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7047,21 +7042,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7071,10 +7066,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527138</v>
+        <v>527359</v>
       </c>
       <c r="R66" t="n">
-        <v>7087472</v>
+        <v>7087452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7107,6 +7102,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7133,10 +7133,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217827</v>
+        <v>129217913</v>
       </c>
       <c r="B67" t="n">
-        <v>92003</v>
+        <v>98724</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7144,34 +7144,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527136</v>
+        <v>526924</v>
       </c>
       <c r="R67" t="n">
-        <v>7087471</v>
+        <v>7087085</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,6 +7204,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7230,32 +7235,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217854</v>
+        <v>129217827</v>
       </c>
       <c r="B68" t="n">
-        <v>82878</v>
+        <v>92003</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7265,10 +7270,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527015</v>
+        <v>527136</v>
       </c>
       <c r="R68" t="n">
-        <v>7087228</v>
+        <v>7087471</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7327,45 +7332,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217913</v>
+        <v>129217854</v>
       </c>
       <c r="B69" t="n">
-        <v>98724</v>
+        <v>82878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526924</v>
+        <v>527015</v>
       </c>
       <c r="R69" t="n">
-        <v>7087085</v>
+        <v>7087228</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7398,11 +7403,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217841</v>
+        <v>129217802</v>
       </c>
       <c r="B78" t="n">
-        <v>91564</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,21 +8226,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527375</v>
+        <v>526934</v>
       </c>
       <c r="R78" t="n">
-        <v>7087521</v>
+        <v>7087213</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,6 +8286,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8312,10 +8317,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217912</v>
+        <v>129217929</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8323,21 +8328,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8347,10 +8352,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527089</v>
+        <v>527393</v>
       </c>
       <c r="R79" t="n">
-        <v>7087260</v>
+        <v>7087440</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8387,7 +8392,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8414,10 +8419,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217924</v>
+        <v>129217841</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>91564</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8425,34 +8430,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527289</v>
+        <v>527375</v>
       </c>
       <c r="R80" t="n">
-        <v>7087449</v>
+        <v>7087521</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8511,32 +8516,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217921</v>
+        <v>129217912</v>
       </c>
       <c r="B81" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8546,10 +8551,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526984</v>
+        <v>527089</v>
       </c>
       <c r="R81" t="n">
-        <v>7087226</v>
+        <v>7087260</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8586,7 +8591,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8613,32 +8618,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217914</v>
+        <v>129217924</v>
       </c>
       <c r="B82" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8648,10 +8653,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526928</v>
+        <v>527289</v>
       </c>
       <c r="R82" t="n">
-        <v>7087112</v>
+        <v>7087449</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8684,11 +8689,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8715,45 +8715,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217830</v>
+        <v>129217921</v>
       </c>
       <c r="B83" t="n">
-        <v>78057</v>
+        <v>98724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526990</v>
+        <v>526984</v>
       </c>
       <c r="R83" t="n">
-        <v>7087234</v>
+        <v>7087226</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8786,6 +8786,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8812,45 +8817,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217802</v>
+        <v>129217914</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526934</v>
+        <v>526928</v>
       </c>
       <c r="R84" t="n">
-        <v>7087213</v>
+        <v>7087112</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8887,7 +8892,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8914,10 +8919,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217929</v>
+        <v>129217830</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8925,34 +8930,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527393</v>
+        <v>526990</v>
       </c>
       <c r="R85" t="n">
-        <v>7087440</v>
+        <v>7087234</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8985,11 +8990,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9113,10 +9113,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217814</v>
+        <v>129217847</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9124,23 +9124,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9148,10 +9144,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526905</v>
+        <v>527069</v>
       </c>
       <c r="R87" t="n">
-        <v>7087117</v>
+        <v>7087323</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9184,11 +9180,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9215,45 +9206,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217915</v>
+        <v>129217814</v>
       </c>
       <c r="B88" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527145</v>
+        <v>526905</v>
       </c>
       <c r="R88" t="n">
-        <v>7087306</v>
+        <v>7087117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9290,7 +9281,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9317,10 +9308,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217847</v>
+        <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9328,19 +9319,23 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9348,10 +9343,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527069</v>
+        <v>527094</v>
       </c>
       <c r="R89" t="n">
-        <v>7087323</v>
+        <v>7087264</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9384,6 +9379,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9410,45 +9410,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217851</v>
+        <v>129217915</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527094</v>
+        <v>527145</v>
       </c>
       <c r="R90" t="n">
-        <v>7087264</v>
+        <v>7087306</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217815</v>
+        <v>129217850</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526883</v>
+        <v>527358</v>
       </c>
       <c r="R3" t="n">
-        <v>7087121</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217850</v>
+        <v>129217815</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527358</v>
+        <v>526883</v>
       </c>
       <c r="R4" t="n">
-        <v>7087435</v>
+        <v>7087121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,7 +979,7 @@
         <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>80109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R6" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217831</v>
+        <v>129217791</v>
       </c>
       <c r="B7" t="n">
-        <v>80109</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527362</v>
+        <v>527219</v>
       </c>
       <c r="R7" t="n">
-        <v>7087507</v>
+        <v>7087542</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B8" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R8" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217782</v>
+        <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>96970</v>
+        <v>92244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527172</v>
+        <v>527386</v>
       </c>
       <c r="R9" t="n">
-        <v>7087341</v>
+        <v>7087522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217856</v>
+        <v>129217782</v>
       </c>
       <c r="B10" t="n">
-        <v>92241</v>
+        <v>96973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527386</v>
+        <v>527172</v>
       </c>
       <c r="R10" t="n">
-        <v>7087522</v>
+        <v>7087341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217795</v>
+        <v>129217928</v>
       </c>
       <c r="B14" t="n">
-        <v>91550</v>
+        <v>82878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527123</v>
+        <v>527359</v>
       </c>
       <c r="R14" t="n">
-        <v>7087425</v>
+        <v>7087548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,6 +1948,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217928</v>
+        <v>129217842</v>
       </c>
       <c r="B15" t="n">
-        <v>82878</v>
+        <v>91567</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,34 +1978,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527359</v>
+        <v>527385</v>
       </c>
       <c r="R15" t="n">
-        <v>7087548</v>
+        <v>7087528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,7 +2046,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217842</v>
+        <v>129217852</v>
       </c>
       <c r="B16" t="n">
-        <v>91564</v>
+        <v>82878</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527385</v>
+        <v>527265</v>
       </c>
       <c r="R16" t="n">
-        <v>7087528</v>
+        <v>7087520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217852</v>
+        <v>129217840</v>
       </c>
       <c r="B17" t="n">
-        <v>82878</v>
+        <v>91567</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527265</v>
+        <v>527386</v>
       </c>
       <c r="R17" t="n">
-        <v>7087520</v>
+        <v>7087517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217840</v>
+        <v>129217795</v>
       </c>
       <c r="B18" t="n">
-        <v>91564</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527386</v>
+        <v>527123</v>
       </c>
       <c r="R18" t="n">
-        <v>7087517</v>
+        <v>7087425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217797</v>
+        <v>129217780</v>
       </c>
       <c r="B20" t="n">
-        <v>92268</v>
+        <v>83012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527368</v>
+        <v>527179</v>
       </c>
       <c r="R20" t="n">
-        <v>7087576</v>
+        <v>7087518</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,45 +2549,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217785</v>
+        <v>129217925</v>
       </c>
       <c r="B21" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527106</v>
+        <v>527089</v>
       </c>
       <c r="R21" t="n">
-        <v>7087220</v>
+        <v>7087260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,32 +2646,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217780</v>
+        <v>129217797</v>
       </c>
       <c r="B22" t="n">
-        <v>83012</v>
+        <v>92271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527179</v>
+        <v>527368</v>
       </c>
       <c r="R22" t="n">
-        <v>7087518</v>
+        <v>7087576</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,45 +2743,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217925</v>
+        <v>129217785</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527089</v>
+        <v>527106</v>
       </c>
       <c r="R23" t="n">
-        <v>7087260</v>
+        <v>7087220</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
         <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129217779</v>
+        <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>83012</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527248</v>
+        <v>527167</v>
       </c>
       <c r="R25" t="n">
-        <v>7087513</v>
+        <v>7087461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129217793</v>
+        <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>91550</v>
+        <v>83012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527167</v>
+        <v>527248</v>
       </c>
       <c r="R26" t="n">
-        <v>7087461</v>
+        <v>7087513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217789</v>
+        <v>129217807</v>
       </c>
       <c r="B27" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527376</v>
+        <v>526921</v>
       </c>
       <c r="R27" t="n">
-        <v>7087516</v>
+        <v>7087159</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,6 +3207,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3233,10 +3238,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217910</v>
+        <v>129217926</v>
       </c>
       <c r="B28" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3249,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3273,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527288</v>
+        <v>527029</v>
       </c>
       <c r="R28" t="n">
-        <v>7087491</v>
+        <v>7087194</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,10 +3335,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217926</v>
+        <v>129217789</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,34 +3346,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527029</v>
+        <v>527376</v>
       </c>
       <c r="R29" t="n">
-        <v>7087194</v>
+        <v>7087516</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217807</v>
+        <v>129217910</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3438,34 +3443,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>526921</v>
+        <v>527288</v>
       </c>
       <c r="R30" t="n">
-        <v>7087159</v>
+        <v>7087491</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217787</v>
+        <v>129217820</v>
       </c>
       <c r="B31" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527291</v>
+        <v>527034</v>
       </c>
       <c r="R31" t="n">
-        <v>7087491</v>
+        <v>7087201</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,6 +3600,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3626,32 +3631,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217820</v>
+        <v>129217836</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3666,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527091</v>
       </c>
       <c r="R32" t="n">
-        <v>7087201</v>
+        <v>7087273</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,11 +3702,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3728,10 +3728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217922</v>
+        <v>129217787</v>
       </c>
       <c r="B33" t="n">
-        <v>56908</v>
+        <v>91553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3739,34 +3739,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527122</v>
+        <v>527291</v>
       </c>
       <c r="R33" t="n">
-        <v>7087232</v>
+        <v>7087491</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>56908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R34" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129217812</v>
+        <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,23 +3933,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3957,10 +3953,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>526904</v>
+        <v>527139</v>
       </c>
       <c r="R35" t="n">
-        <v>7087132</v>
+        <v>7087468</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,11 +3989,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4024,10 +4015,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129217846</v>
+        <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4035,19 +4026,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4055,10 +4050,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527139</v>
+        <v>526904</v>
       </c>
       <c r="R36" t="n">
-        <v>7087468</v>
+        <v>7087132</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,6 +4086,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4117,10 +4117,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217821</v>
+        <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4128,23 +4128,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4152,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526924</v>
+        <v>527173</v>
       </c>
       <c r="R37" t="n">
-        <v>7087187</v>
+        <v>7087380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,11 +4184,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4219,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217835</v>
+        <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4254,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527103</v>
+        <v>526923</v>
       </c>
       <c r="R38" t="n">
-        <v>7087341</v>
+        <v>7087199</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,6 +4281,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4316,7 +4312,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217803</v>
+        <v>129217821</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4351,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526923</v>
+        <v>526924</v>
       </c>
       <c r="R39" t="n">
-        <v>7087199</v>
+        <v>7087187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,7 +4387,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4418,30 +4414,34 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217845</v>
+        <v>129217833</v>
       </c>
       <c r="B40" t="n">
-        <v>91570</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527173</v>
+        <v>527351</v>
       </c>
       <c r="R40" t="n">
-        <v>7087380</v>
+        <v>7087510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4485,6 +4485,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4511,10 +4516,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217833</v>
+        <v>129217835</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4546,10 +4551,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527351</v>
+        <v>527103</v>
       </c>
       <c r="R41" t="n">
-        <v>7087510</v>
+        <v>7087341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4582,11 +4587,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4616,7 +4616,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217790</v>
+        <v>129217923</v>
       </c>
       <c r="B47" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5109,34 +5109,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527357</v>
+        <v>527150</v>
       </c>
       <c r="R47" t="n">
-        <v>7087574</v>
+        <v>7087278</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5169,6 +5169,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5195,32 +5200,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217923</v>
+        <v>129217920</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5230,10 +5235,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527150</v>
+        <v>527064</v>
       </c>
       <c r="R48" t="n">
-        <v>7087278</v>
+        <v>7087252</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5270,7 +5275,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5297,32 +5302,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217844</v>
+        <v>129217790</v>
       </c>
       <c r="B49" t="n">
-        <v>57719</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100110</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5332,10 +5337,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527355</v>
+        <v>527357</v>
       </c>
       <c r="R49" t="n">
-        <v>7087521</v>
+        <v>7087574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5394,32 +5399,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217805</v>
+        <v>129217844</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57719</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5429,10 +5434,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>526924</v>
+        <v>527355</v>
       </c>
       <c r="R50" t="n">
-        <v>7087183</v>
+        <v>7087521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5465,11 +5470,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5496,45 +5496,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217920</v>
+        <v>129217805</v>
       </c>
       <c r="B51" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527064</v>
+        <v>526924</v>
       </c>
       <c r="R51" t="n">
-        <v>7087252</v>
+        <v>7087183</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5601,7 +5601,7 @@
         <v>129217794</v>
       </c>
       <c r="B52" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5695,45 +5695,65 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217837</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>526980</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087208</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5770,7 +5790,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5797,7 +5817,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5825,37 +5845,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,7 +5919,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217801</v>
+        <v>129217837</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527106</v>
+        <v>526980</v>
       </c>
       <c r="R56" t="n">
-        <v>7087348</v>
+        <v>7087208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217823</v>
+        <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>96973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527374</v>
+        <v>527349</v>
       </c>
       <c r="R57" t="n">
-        <v>7087508</v>
+        <v>7087510</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,11 +6194,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4st</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6225,10 +6220,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217784</v>
+        <v>129217848</v>
       </c>
       <c r="B58" t="n">
-        <v>96970</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6236,21 +6231,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6260,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527349</v>
+        <v>527106</v>
       </c>
       <c r="R58" t="n">
-        <v>7087510</v>
+        <v>7087367</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6296,6 +6291,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,32 +6322,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217848</v>
+        <v>129217832</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527106</v>
+        <v>527149</v>
       </c>
       <c r="R59" t="n">
-        <v>7087367</v>
+        <v>7087289</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,10 +6424,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B60" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6455,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R60" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,10 +6526,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217919</v>
+        <v>129217834</v>
       </c>
       <c r="B61" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6557,14 +6557,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527135</v>
+        <v>527268</v>
       </c>
       <c r="R61" t="n">
-        <v>7087449</v>
+        <v>7087590</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6628,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217834</v>
+        <v>129217823</v>
       </c>
       <c r="B62" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527268</v>
+        <v>527374</v>
       </c>
       <c r="R62" t="n">
-        <v>7087590</v>
+        <v>7087508</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217829</v>
+        <v>129217806</v>
       </c>
       <c r="B63" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527138</v>
+        <v>526925</v>
       </c>
       <c r="R63" t="n">
-        <v>7087472</v>
+        <v>7087175</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6801,6 +6801,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6827,7 +6832,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217806</v>
+        <v>129217810</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -6862,10 +6867,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526925</v>
+        <v>526914</v>
       </c>
       <c r="R64" t="n">
-        <v>7087175</v>
+        <v>7087139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6902,7 +6907,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6929,7 +6934,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217810</v>
+        <v>129217818</v>
       </c>
       <c r="B65" t="n">
         <v>57727</v>
@@ -6964,10 +6969,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526914</v>
+        <v>527359</v>
       </c>
       <c r="R65" t="n">
-        <v>7087139</v>
+        <v>7087452</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7004,7 +7009,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7031,10 +7036,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217818</v>
+        <v>129217829</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7042,21 +7047,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7066,10 +7071,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527359</v>
+        <v>527138</v>
       </c>
       <c r="R66" t="n">
-        <v>7087452</v>
+        <v>7087472</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7102,11 +7107,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7133,10 +7133,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217913</v>
+        <v>129217827</v>
       </c>
       <c r="B67" t="n">
-        <v>98724</v>
+        <v>92006</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7144,34 +7144,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526924</v>
+        <v>527136</v>
       </c>
       <c r="R67" t="n">
-        <v>7087085</v>
+        <v>7087471</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,11 +7204,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7235,32 +7230,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217827</v>
+        <v>129217854</v>
       </c>
       <c r="B68" t="n">
-        <v>92003</v>
+        <v>82878</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7270,10 +7265,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527136</v>
+        <v>527015</v>
       </c>
       <c r="R68" t="n">
-        <v>7087471</v>
+        <v>7087228</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7332,45 +7327,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217854</v>
+        <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>82878</v>
+        <v>98727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527015</v>
+        <v>526924</v>
       </c>
       <c r="R69" t="n">
-        <v>7087228</v>
+        <v>7087085</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7403,6 +7398,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217786</v>
+        <v>129217781</v>
       </c>
       <c r="B70" t="n">
-        <v>91550</v>
+        <v>83012</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527238</v>
+        <v>527141</v>
       </c>
       <c r="R70" t="n">
-        <v>7087520</v>
+        <v>7087466</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7526,10 +7526,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217911</v>
+        <v>129217786</v>
       </c>
       <c r="B71" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7557,14 +7557,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527164</v>
+        <v>527238</v>
       </c>
       <c r="R71" t="n">
-        <v>7087462</v>
+        <v>7087520</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7623,10 +7623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217853</v>
+        <v>129217911</v>
       </c>
       <c r="B72" t="n">
-        <v>82878</v>
+        <v>91553</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7634,34 +7634,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527133</v>
+        <v>527164</v>
       </c>
       <c r="R72" t="n">
-        <v>7087390</v>
+        <v>7087462</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7720,10 +7720,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217781</v>
+        <v>129217853</v>
       </c>
       <c r="B73" t="n">
-        <v>83012</v>
+        <v>82878</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7731,21 +7731,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527141</v>
+        <v>527133</v>
       </c>
       <c r="R73" t="n">
-        <v>7087466</v>
+        <v>7087390</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8024,7 +8024,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>129217841</v>
       </c>
       <c r="B80" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>129217921</v>
       </c>
       <c r="B83" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>129217914</v>
       </c>
       <c r="B84" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9016,10 +9016,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217783</v>
+        <v>129217814</v>
       </c>
       <c r="B86" t="n">
-        <v>96970</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9027,21 +9027,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527221</v>
+        <v>526905</v>
       </c>
       <c r="R86" t="n">
-        <v>7087348</v>
+        <v>7087117</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9087,6 +9087,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9113,41 +9118,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217847</v>
+        <v>129217915</v>
       </c>
       <c r="B87" t="n">
-        <v>91570</v>
+        <v>98727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527069</v>
+        <v>527145</v>
       </c>
       <c r="R87" t="n">
-        <v>7087323</v>
+        <v>7087306</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9180,6 +9189,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9206,10 +9220,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217814</v>
+        <v>129217783</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>96973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9217,21 +9231,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9241,10 +9255,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>526905</v>
+        <v>527221</v>
       </c>
       <c r="R88" t="n">
-        <v>7087117</v>
+        <v>7087348</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9277,11 +9291,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9308,10 +9317,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217851</v>
+        <v>129217847</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9319,23 +9328,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9343,10 +9348,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527094</v>
+        <v>527069</v>
       </c>
       <c r="R89" t="n">
-        <v>7087264</v>
+        <v>7087323</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9379,11 +9384,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9410,45 +9410,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217915</v>
+        <v>129217851</v>
       </c>
       <c r="B90" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527145</v>
+        <v>527094</v>
       </c>
       <c r="R90" t="n">
-        <v>7087306</v>
+        <v>7087264</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R7" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R8" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1869,32 +1869,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217928</v>
+        <v>129217917</v>
       </c>
       <c r="B14" t="n">
-        <v>82878</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527359</v>
+        <v>527273</v>
       </c>
       <c r="R14" t="n">
-        <v>7087548</v>
+        <v>7087581</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,13 +1942,17 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217842</v>
+        <v>129217797</v>
       </c>
       <c r="B15" t="n">
-        <v>91567</v>
+        <v>92271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2002,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527385</v>
+        <v>527368</v>
       </c>
       <c r="R15" t="n">
-        <v>7087528</v>
+        <v>7087576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217852</v>
+        <v>129217780</v>
       </c>
       <c r="B16" t="n">
-        <v>82878</v>
+        <v>83012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2079,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527265</v>
+        <v>527179</v>
       </c>
       <c r="R16" t="n">
-        <v>7087520</v>
+        <v>7087518</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217840</v>
+        <v>129217925</v>
       </c>
       <c r="B17" t="n">
-        <v>91567</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,34 +2176,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527386</v>
+        <v>527089</v>
       </c>
       <c r="R17" t="n">
-        <v>7087517</v>
+        <v>7087260</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2359,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217855</v>
+        <v>129217928</v>
       </c>
       <c r="B19" t="n">
         <v>82878</v>
@@ -2386,14 +2390,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527012</v>
+        <v>527359</v>
       </c>
       <c r="R19" t="n">
-        <v>7087233</v>
+        <v>7087548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,6 +2438,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2452,10 +2457,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217780</v>
+        <v>129217842</v>
       </c>
       <c r="B20" t="n">
-        <v>83012</v>
+        <v>91567</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2463,21 +2468,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527179</v>
+        <v>527385</v>
       </c>
       <c r="R20" t="n">
-        <v>7087518</v>
+        <v>7087528</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,10 +2554,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217925</v>
+        <v>129217852</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2560,34 +2565,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527089</v>
+        <v>527265</v>
       </c>
       <c r="R21" t="n">
-        <v>7087260</v>
+        <v>7087520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,32 +2651,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217797</v>
+        <v>129217840</v>
       </c>
       <c r="B22" t="n">
-        <v>92271</v>
+        <v>91567</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2681,10 +2686,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527368</v>
+        <v>527386</v>
       </c>
       <c r="R22" t="n">
-        <v>7087576</v>
+        <v>7087517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,32 +2748,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217785</v>
+        <v>129217855</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>82878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2778,10 +2783,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527106</v>
+        <v>527012</v>
       </c>
       <c r="R23" t="n">
-        <v>7087220</v>
+        <v>7087233</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2840,45 +2845,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217917</v>
+        <v>129217785</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527273</v>
+        <v>527106</v>
       </c>
       <c r="R24" t="n">
-        <v>7087581</v>
+        <v>7087220</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,11 +2916,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217807</v>
+        <v>129217926</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>526921</v>
+        <v>527029</v>
       </c>
       <c r="R27" t="n">
-        <v>7087159</v>
+        <v>7087194</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,11 +3207,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217926</v>
+        <v>129217807</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,34 +3244,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527029</v>
+        <v>526921</v>
       </c>
       <c r="R28" t="n">
-        <v>7087194</v>
+        <v>7087159</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3309,6 +3304,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3335,7 +3335,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217789</v>
+        <v>129217910</v>
       </c>
       <c r="B29" t="n">
         <v>91553</v>
@@ -3366,14 +3366,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527376</v>
+        <v>527288</v>
       </c>
       <c r="R29" t="n">
-        <v>7087516</v>
+        <v>7087491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217910</v>
+        <v>129217789</v>
       </c>
       <c r="B30" t="n">
         <v>91553</v>
@@ -3463,14 +3463,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527288</v>
+        <v>527376</v>
       </c>
       <c r="R30" t="n">
-        <v>7087491</v>
+        <v>7087516</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3631,45 +3631,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>56908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R32" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3728,32 +3728,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217787</v>
+        <v>129217836</v>
       </c>
       <c r="B33" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527291</v>
+        <v>527091</v>
       </c>
       <c r="R33" t="n">
-        <v>7087491</v>
+        <v>7087273</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217922</v>
+        <v>129217787</v>
       </c>
       <c r="B34" t="n">
-        <v>56908</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3836,34 +3836,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527122</v>
+        <v>527291</v>
       </c>
       <c r="R34" t="n">
-        <v>7087232</v>
+        <v>7087491</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4117,30 +4117,34 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217845</v>
+        <v>129217833</v>
       </c>
       <c r="B37" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4148,10 +4152,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527173</v>
+        <v>527351</v>
       </c>
       <c r="R37" t="n">
-        <v>7087380</v>
+        <v>7087510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,6 +4188,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4210,32 +4219,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217803</v>
+        <v>129217835</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4254,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526923</v>
+        <v>527103</v>
       </c>
       <c r="R38" t="n">
-        <v>7087199</v>
+        <v>7087341</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,11 +4290,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4312,7 +4316,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217821</v>
+        <v>129217803</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4347,10 +4351,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526924</v>
+        <v>526923</v>
       </c>
       <c r="R39" t="n">
-        <v>7087187</v>
+        <v>7087199</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4387,7 +4391,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4414,32 +4418,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217833</v>
+        <v>129217821</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4453,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527351</v>
+        <v>526924</v>
       </c>
       <c r="R40" t="n">
-        <v>7087510</v>
+        <v>7087187</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,7 +4493,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4516,34 +4520,30 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217835</v>
+        <v>129217845</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>91573</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527103</v>
+        <v>527173</v>
       </c>
       <c r="R41" t="n">
-        <v>7087341</v>
+        <v>7087380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129217792</v>
+        <v>129217843</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>91567</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527192</v>
+        <v>527378</v>
       </c>
       <c r="R42" t="n">
-        <v>7087529</v>
+        <v>7087514</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129217843</v>
+        <v>129217792</v>
       </c>
       <c r="B43" t="n">
-        <v>91567</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4721,21 +4721,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527378</v>
+        <v>527192</v>
       </c>
       <c r="R43" t="n">
-        <v>7087514</v>
+        <v>7087529</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5109,34 +5109,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R47" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5169,11 +5169,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5200,32 +5195,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217920</v>
+        <v>129217923</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5235,10 +5230,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527064</v>
+        <v>527150</v>
       </c>
       <c r="R48" t="n">
-        <v>7087252</v>
+        <v>7087278</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5275,7 +5270,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5302,45 +5297,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217790</v>
+        <v>129217920</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527357</v>
+        <v>527064</v>
       </c>
       <c r="R49" t="n">
-        <v>7087574</v>
+        <v>7087252</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5373,6 +5368,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5399,32 +5399,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217844</v>
+        <v>129217805</v>
       </c>
       <c r="B50" t="n">
-        <v>57719</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527355</v>
+        <v>526924</v>
       </c>
       <c r="R50" t="n">
-        <v>7087521</v>
+        <v>7087183</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,6 +5470,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5496,32 +5501,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217805</v>
+        <v>129217844</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>57719</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>100110</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>526924</v>
+        <v>527355</v>
       </c>
       <c r="R51" t="n">
-        <v>7087183</v>
+        <v>7087521</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5567,11 +5572,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5695,65 +5695,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217837</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>526980</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087208</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5790,7 +5770,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5817,7 +5797,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217819</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5845,17 +5825,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>527070</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087285</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,7 +5919,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217800</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>527297</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217837</v>
+        <v>129217801</v>
       </c>
       <c r="B56" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526980</v>
+        <v>527106</v>
       </c>
       <c r="R56" t="n">
-        <v>7087208</v>
+        <v>7087348</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6322,32 +6322,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217832</v>
+        <v>129217823</v>
       </c>
       <c r="B59" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527149</v>
+        <v>527374</v>
       </c>
       <c r="R59" t="n">
-        <v>7087289</v>
+        <v>7087508</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,7 +6424,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217919</v>
+        <v>129217832</v>
       </c>
       <c r="B60" t="n">
         <v>98727</v>
@@ -6455,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527135</v>
+        <v>527149</v>
       </c>
       <c r="R60" t="n">
-        <v>7087449</v>
+        <v>7087289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,7 +6526,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217834</v>
+        <v>129217919</v>
       </c>
       <c r="B61" t="n">
         <v>98727</v>
@@ -6557,14 +6557,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527268</v>
+        <v>527135</v>
       </c>
       <c r="R61" t="n">
-        <v>7087590</v>
+        <v>7087449</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6628,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217823</v>
+        <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527374</v>
+        <v>527268</v>
       </c>
       <c r="R62" t="n">
-        <v>7087508</v>
+        <v>7087590</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217806</v>
+        <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>526925</v>
+        <v>527138</v>
       </c>
       <c r="R63" t="n">
-        <v>7087175</v>
+        <v>7087472</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6801,11 +6801,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6832,32 +6827,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217810</v>
+        <v>129217827</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>92006</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6867,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526914</v>
+        <v>527136</v>
       </c>
       <c r="R64" t="n">
-        <v>7087139</v>
+        <v>7087471</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6903,11 +6898,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6934,10 +6924,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217818</v>
+        <v>129217854</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6945,21 +6935,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6969,10 +6959,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527359</v>
+        <v>527015</v>
       </c>
       <c r="R65" t="n">
-        <v>7087452</v>
+        <v>7087228</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7005,11 +6995,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7036,10 +7021,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217829</v>
+        <v>129217806</v>
       </c>
       <c r="B66" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7047,21 +7032,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7071,10 +7056,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527138</v>
+        <v>526925</v>
       </c>
       <c r="R66" t="n">
-        <v>7087472</v>
+        <v>7087175</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7107,6 +7092,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7133,32 +7123,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217827</v>
+        <v>129217810</v>
       </c>
       <c r="B67" t="n">
-        <v>92006</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7168,10 +7158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527136</v>
+        <v>526914</v>
       </c>
       <c r="R67" t="n">
-        <v>7087471</v>
+        <v>7087139</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,6 +7194,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7230,10 +7225,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217854</v>
+        <v>129217818</v>
       </c>
       <c r="B68" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7241,21 +7236,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7265,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527015</v>
+        <v>527359</v>
       </c>
       <c r="R68" t="n">
-        <v>7087228</v>
+        <v>7087452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7301,6 +7296,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217781</v>
+        <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>83012</v>
+        <v>91553</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527141</v>
+        <v>527238</v>
       </c>
       <c r="R70" t="n">
-        <v>7087466</v>
+        <v>7087520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7526,7 +7526,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217786</v>
+        <v>129217911</v>
       </c>
       <c r="B71" t="n">
         <v>91553</v>
@@ -7557,14 +7557,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527238</v>
+        <v>527164</v>
       </c>
       <c r="R71" t="n">
-        <v>7087520</v>
+        <v>7087462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7623,10 +7623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217911</v>
+        <v>129217853</v>
       </c>
       <c r="B72" t="n">
-        <v>91553</v>
+        <v>82878</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7634,34 +7634,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527164</v>
+        <v>527133</v>
       </c>
       <c r="R72" t="n">
-        <v>7087462</v>
+        <v>7087390</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7720,10 +7720,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217853</v>
+        <v>129217804</v>
       </c>
       <c r="B73" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7731,21 +7731,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527133</v>
+        <v>526927</v>
       </c>
       <c r="R73" t="n">
-        <v>7087390</v>
+        <v>7087193</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7791,6 +7791,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7817,7 +7822,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217804</v>
+        <v>129217808</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7852,10 +7857,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526927</v>
+        <v>526917</v>
       </c>
       <c r="R74" t="n">
-        <v>7087193</v>
+        <v>7087144</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7919,10 +7924,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217808</v>
+        <v>129217781</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7930,21 +7935,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7954,10 +7959,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526917</v>
+        <v>527141</v>
       </c>
       <c r="R75" t="n">
-        <v>7087144</v>
+        <v>7087466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7990,11 +7995,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217802</v>
+        <v>129217841</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,21 +8226,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>526934</v>
+        <v>527375</v>
       </c>
       <c r="R78" t="n">
-        <v>7087213</v>
+        <v>7087521</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,11 +8286,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8317,10 +8312,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217929</v>
+        <v>129217924</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8328,21 +8323,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8352,10 +8347,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527393</v>
+        <v>527289</v>
       </c>
       <c r="R79" t="n">
-        <v>7087440</v>
+        <v>7087449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8388,11 +8383,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8419,10 +8409,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217841</v>
+        <v>129217802</v>
       </c>
       <c r="B80" t="n">
-        <v>91567</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8430,21 +8420,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8454,10 +8444,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527375</v>
+        <v>526934</v>
       </c>
       <c r="R80" t="n">
-        <v>7087521</v>
+        <v>7087213</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8490,6 +8480,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8618,10 +8613,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217924</v>
+        <v>129217929</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8629,21 +8624,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8653,10 +8648,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527289</v>
+        <v>527393</v>
       </c>
       <c r="R82" t="n">
-        <v>7087449</v>
+        <v>7087440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8689,6 +8684,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9016,45 +9016,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217814</v>
+        <v>129217915</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>526905</v>
+        <v>527145</v>
       </c>
       <c r="R86" t="n">
-        <v>7087117</v>
+        <v>7087306</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9118,45 +9118,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217915</v>
+        <v>129217783</v>
       </c>
       <c r="B87" t="n">
-        <v>98727</v>
+        <v>96973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527145</v>
+        <v>527221</v>
       </c>
       <c r="R87" t="n">
-        <v>7087306</v>
+        <v>7087348</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9189,11 +9189,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9220,10 +9215,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217783</v>
+        <v>129217814</v>
       </c>
       <c r="B88" t="n">
-        <v>96973</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9231,21 +9226,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9255,10 +9250,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527221</v>
+        <v>526905</v>
       </c>
       <c r="R88" t="n">
-        <v>7087348</v>
+        <v>7087117</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9291,6 +9286,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9317,10 +9317,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217847</v>
+        <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9328,19 +9328,23 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9348,10 +9352,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527069</v>
+        <v>527094</v>
       </c>
       <c r="R89" t="n">
-        <v>7087323</v>
+        <v>7087264</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9384,6 +9388,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9410,10 +9419,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217851</v>
+        <v>129217847</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9421,23 +9430,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9445,10 +9450,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527094</v>
+        <v>527069</v>
       </c>
       <c r="R90" t="n">
-        <v>7087264</v>
+        <v>7087323</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9481,11 +9486,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R8" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1869,45 +1869,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217917</v>
+        <v>129217785</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527273</v>
+        <v>527106</v>
       </c>
       <c r="R14" t="n">
-        <v>7087581</v>
+        <v>7087220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,11 +1940,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,32 +1966,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217797</v>
+        <v>129217842</v>
       </c>
       <c r="B15" t="n">
-        <v>92271</v>
+        <v>91567</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527368</v>
+        <v>527385</v>
       </c>
       <c r="R15" t="n">
-        <v>7087576</v>
+        <v>7087528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217780</v>
+        <v>129217840</v>
       </c>
       <c r="B16" t="n">
-        <v>83012</v>
+        <v>91567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2103,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527179</v>
+        <v>527386</v>
       </c>
       <c r="R16" t="n">
-        <v>7087518</v>
+        <v>7087517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,10 +2160,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217925</v>
+        <v>129217795</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,34 +2171,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527089</v>
+        <v>527123</v>
       </c>
       <c r="R17" t="n">
-        <v>7087260</v>
+        <v>7087425</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,10 +2257,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217795</v>
+        <v>129217928</v>
       </c>
       <c r="B18" t="n">
-        <v>91553</v>
+        <v>82878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2273,34 +2268,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527123</v>
+        <v>527359</v>
       </c>
       <c r="R18" t="n">
-        <v>7087425</v>
+        <v>7087548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,6 +2336,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2359,7 +2355,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217928</v>
+        <v>129217852</v>
       </c>
       <c r="B19" t="n">
         <v>82878</v>
@@ -2390,14 +2386,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527359</v>
+        <v>527265</v>
       </c>
       <c r="R19" t="n">
-        <v>7087548</v>
+        <v>7087520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2438,7 +2434,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2457,10 +2452,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217842</v>
+        <v>129217855</v>
       </c>
       <c r="B20" t="n">
-        <v>91567</v>
+        <v>82878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2468,21 +2463,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2492,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527385</v>
+        <v>527012</v>
       </c>
       <c r="R20" t="n">
-        <v>7087528</v>
+        <v>7087233</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2554,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217852</v>
+        <v>129217797</v>
       </c>
       <c r="B21" t="n">
-        <v>82878</v>
+        <v>92271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2589,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527265</v>
+        <v>527368</v>
       </c>
       <c r="R21" t="n">
-        <v>7087520</v>
+        <v>7087576</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2651,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217840</v>
+        <v>129217780</v>
       </c>
       <c r="B22" t="n">
-        <v>91567</v>
+        <v>83012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2662,21 +2657,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2686,10 +2681,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527386</v>
+        <v>527179</v>
       </c>
       <c r="R22" t="n">
-        <v>7087517</v>
+        <v>7087518</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2748,10 +2743,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217855</v>
+        <v>129217925</v>
       </c>
       <c r="B23" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2759,34 +2754,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527012</v>
+        <v>527089</v>
       </c>
       <c r="R23" t="n">
-        <v>7087233</v>
+        <v>7087260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2845,45 +2840,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217785</v>
+        <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527106</v>
+        <v>527273</v>
       </c>
       <c r="R24" t="n">
-        <v>7087220</v>
+        <v>7087581</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217926</v>
+        <v>129217789</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527029</v>
+        <v>527376</v>
       </c>
       <c r="R27" t="n">
-        <v>7087194</v>
+        <v>7087516</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217807</v>
+        <v>129217910</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,34 +3244,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>526921</v>
+        <v>527288</v>
       </c>
       <c r="R28" t="n">
-        <v>7087159</v>
+        <v>7087491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,11 +3304,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217910</v>
+        <v>129217926</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3346,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527288</v>
+        <v>527029</v>
       </c>
       <c r="R29" t="n">
-        <v>7087491</v>
+        <v>7087194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217789</v>
+        <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3438,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527376</v>
+        <v>526921</v>
       </c>
       <c r="R30" t="n">
-        <v>7087516</v>
+        <v>7087159</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217922</v>
+        <v>129217787</v>
       </c>
       <c r="B32" t="n">
-        <v>56908</v>
+        <v>91553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3642,34 +3642,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527122</v>
+        <v>527291</v>
       </c>
       <c r="R32" t="n">
-        <v>7087232</v>
+        <v>7087491</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3728,45 +3728,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>56908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R33" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3825,32 +3825,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217787</v>
+        <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527291</v>
+        <v>527091</v>
       </c>
       <c r="R34" t="n">
-        <v>7087491</v>
+        <v>7087273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4117,34 +4117,30 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217833</v>
+        <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>91573</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4152,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527351</v>
+        <v>527173</v>
       </c>
       <c r="R37" t="n">
-        <v>7087510</v>
+        <v>7087380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,11 +4184,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4219,32 +4210,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217835</v>
+        <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4254,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527103</v>
+        <v>526923</v>
       </c>
       <c r="R38" t="n">
-        <v>7087341</v>
+        <v>7087199</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,6 +4281,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4316,7 +4312,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217803</v>
+        <v>129217821</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4351,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526923</v>
+        <v>526924</v>
       </c>
       <c r="R39" t="n">
-        <v>7087199</v>
+        <v>7087187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,7 +4387,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4418,32 +4414,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217821</v>
+        <v>129217833</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4453,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526924</v>
+        <v>527351</v>
       </c>
       <c r="R40" t="n">
-        <v>7087187</v>
+        <v>7087510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4493,7 +4489,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4520,30 +4516,34 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217845</v>
+        <v>129217835</v>
       </c>
       <c r="B41" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527173</v>
+        <v>527103</v>
       </c>
       <c r="R41" t="n">
-        <v>7087380</v>
+        <v>7087341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129217843</v>
+        <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91567</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527378</v>
+        <v>527192</v>
       </c>
       <c r="R42" t="n">
-        <v>7087514</v>
+        <v>7087529</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4710,32 +4710,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129217792</v>
+        <v>129217826</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>80053</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527192</v>
+        <v>527090</v>
       </c>
       <c r="R43" t="n">
-        <v>7087529</v>
+        <v>7087261</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217826</v>
+        <v>129217838</v>
       </c>
       <c r="B44" t="n">
-        <v>80053</v>
+        <v>56908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527090</v>
+        <v>527239</v>
       </c>
       <c r="R44" t="n">
-        <v>7087261</v>
+        <v>7087332</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217778</v>
+        <v>129217843</v>
       </c>
       <c r="B45" t="n">
-        <v>83012</v>
+        <v>91567</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>526957</v>
+        <v>527378</v>
       </c>
       <c r="R45" t="n">
-        <v>7087142</v>
+        <v>7087514</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217838</v>
+        <v>129217778</v>
       </c>
       <c r="B46" t="n">
-        <v>56908</v>
+        <v>83012</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5012,21 +5012,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527239</v>
+        <v>526957</v>
       </c>
       <c r="R46" t="n">
-        <v>7087332</v>
+        <v>7087142</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5297,45 +5297,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217920</v>
+        <v>129217844</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>57719</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527064</v>
+        <v>527355</v>
       </c>
       <c r="R49" t="n">
-        <v>7087252</v>
+        <v>7087521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5368,11 +5368,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5501,45 +5496,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217844</v>
+        <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>57719</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527355</v>
+        <v>527064</v>
       </c>
       <c r="R51" t="n">
-        <v>7087521</v>
+        <v>7087252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5572,6 +5567,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5695,45 +5695,65 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217837</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>526980</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087208</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5770,7 +5790,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5797,7 +5817,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5825,37 +5845,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,7 +5919,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5954,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217801</v>
+        <v>129217837</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527106</v>
+        <v>526980</v>
       </c>
       <c r="R56" t="n">
-        <v>7087348</v>
+        <v>7087208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217784</v>
+        <v>129217823</v>
       </c>
       <c r="B57" t="n">
-        <v>96973</v>
+        <v>57887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527349</v>
+        <v>527374</v>
       </c>
       <c r="R57" t="n">
-        <v>7087510</v>
+        <v>7087508</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,6 +6194,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6220,10 +6225,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217848</v>
+        <v>129217784</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>96973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6231,21 +6236,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527106</v>
+        <v>527349</v>
       </c>
       <c r="R58" t="n">
-        <v>7087367</v>
+        <v>7087510</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6291,11 +6296,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217823</v>
+        <v>129217848</v>
       </c>
       <c r="B59" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527374</v>
+        <v>527106</v>
       </c>
       <c r="R59" t="n">
-        <v>7087508</v>
+        <v>7087367</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,7 +6424,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B60" t="n">
         <v>98727</v>
@@ -6455,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R60" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,7 +6526,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217919</v>
+        <v>129217832</v>
       </c>
       <c r="B61" t="n">
         <v>98727</v>
@@ -6557,14 +6557,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527135</v>
+        <v>527149</v>
       </c>
       <c r="R61" t="n">
-        <v>7087449</v>
+        <v>7087289</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6730,32 +6730,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217829</v>
+        <v>129217827</v>
       </c>
       <c r="B63" t="n">
-        <v>91851</v>
+        <v>92006</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527138</v>
+        <v>527136</v>
       </c>
       <c r="R63" t="n">
-        <v>7087472</v>
+        <v>7087471</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6827,32 +6827,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217827</v>
+        <v>129217854</v>
       </c>
       <c r="B64" t="n">
-        <v>92006</v>
+        <v>82878</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527136</v>
+        <v>527015</v>
       </c>
       <c r="R64" t="n">
-        <v>7087471</v>
+        <v>7087228</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6924,10 +6924,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217854</v>
+        <v>129217829</v>
       </c>
       <c r="B65" t="n">
-        <v>82878</v>
+        <v>91851</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6935,21 +6935,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6959,10 +6959,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527015</v>
+        <v>527138</v>
       </c>
       <c r="R65" t="n">
-        <v>7087228</v>
+        <v>7087472</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7429,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217786</v>
+        <v>129217853</v>
       </c>
       <c r="B70" t="n">
-        <v>91553</v>
+        <v>82878</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527238</v>
+        <v>527133</v>
       </c>
       <c r="R70" t="n">
-        <v>7087520</v>
+        <v>7087390</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7526,7 +7526,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217911</v>
+        <v>129217786</v>
       </c>
       <c r="B71" t="n">
         <v>91553</v>
@@ -7557,14 +7557,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527164</v>
+        <v>527238</v>
       </c>
       <c r="R71" t="n">
-        <v>7087462</v>
+        <v>7087520</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7623,10 +7623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217853</v>
+        <v>129217911</v>
       </c>
       <c r="B72" t="n">
-        <v>82878</v>
+        <v>91553</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7634,34 +7634,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527133</v>
+        <v>527164</v>
       </c>
       <c r="R72" t="n">
-        <v>7087390</v>
+        <v>7087462</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7720,10 +7720,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217804</v>
+        <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7731,21 +7731,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>526927</v>
+        <v>527141</v>
       </c>
       <c r="R73" t="n">
-        <v>7087193</v>
+        <v>7087466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7791,11 +7791,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7822,7 +7817,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217808</v>
+        <v>129217804</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7857,10 +7852,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526917</v>
+        <v>526927</v>
       </c>
       <c r="R74" t="n">
-        <v>7087144</v>
+        <v>7087193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7924,10 +7919,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217781</v>
+        <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>83012</v>
+        <v>57727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7935,21 +7930,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7959,10 +7954,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527141</v>
+        <v>526917</v>
       </c>
       <c r="R75" t="n">
-        <v>7087466</v>
+        <v>7087144</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7995,6 +7990,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217841</v>
+        <v>129217830</v>
       </c>
       <c r="B78" t="n">
-        <v>91567</v>
+        <v>78057</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,21 +8226,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8250,10 +8250,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527375</v>
+        <v>526990</v>
       </c>
       <c r="R78" t="n">
-        <v>7087521</v>
+        <v>7087234</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8312,32 +8312,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217924</v>
+        <v>129217921</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527289</v>
+        <v>526984</v>
       </c>
       <c r="R79" t="n">
-        <v>7087449</v>
+        <v>7087226</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8383,6 +8383,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8409,45 +8414,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217802</v>
+        <v>129217914</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526934</v>
+        <v>526928</v>
       </c>
       <c r="R80" t="n">
-        <v>7087213</v>
+        <v>7087112</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8484,7 +8489,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8613,10 +8618,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217929</v>
+        <v>129217924</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8624,21 +8629,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8648,10 +8653,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527393</v>
+        <v>527289</v>
       </c>
       <c r="R82" t="n">
-        <v>7087440</v>
+        <v>7087449</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8684,11 +8689,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8715,45 +8715,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217921</v>
+        <v>129217841</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>91567</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526984</v>
+        <v>527375</v>
       </c>
       <c r="R83" t="n">
-        <v>7087226</v>
+        <v>7087521</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8786,11 +8786,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8817,45 +8812,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217914</v>
+        <v>129217802</v>
       </c>
       <c r="B84" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526928</v>
+        <v>526934</v>
       </c>
       <c r="R84" t="n">
-        <v>7087112</v>
+        <v>7087213</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8892,7 +8887,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8919,10 +8914,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217830</v>
+        <v>129217929</v>
       </c>
       <c r="B85" t="n">
-        <v>78057</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8930,34 +8925,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526990</v>
+        <v>527393</v>
       </c>
       <c r="R85" t="n">
-        <v>7087234</v>
+        <v>7087440</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8990,6 +8985,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9016,45 +9016,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217915</v>
+        <v>129217851</v>
       </c>
       <c r="B86" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527145</v>
+        <v>527094</v>
       </c>
       <c r="R86" t="n">
-        <v>7087306</v>
+        <v>7087264</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9215,10 +9215,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217814</v>
+        <v>129217847</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9226,23 +9226,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9250,10 +9246,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>526905</v>
+        <v>527069</v>
       </c>
       <c r="R88" t="n">
-        <v>7087117</v>
+        <v>7087323</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9286,11 +9282,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9317,10 +9308,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217851</v>
+        <v>129217814</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9328,21 +9319,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9352,10 +9343,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527094</v>
+        <v>526905</v>
       </c>
       <c r="R89" t="n">
-        <v>7087264</v>
+        <v>7087117</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9392,7 +9383,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9419,41 +9410,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217847</v>
+        <v>129217915</v>
       </c>
       <c r="B90" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527069</v>
+        <v>527145</v>
       </c>
       <c r="R90" t="n">
-        <v>7087323</v>
+        <v>7087306</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9486,6 +9481,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217849</v>
+        <v>129217918</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526979</v>
+        <v>527262</v>
       </c>
       <c r="R2" t="n">
-        <v>7087143</v>
+        <v>7087588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217850</v>
+        <v>129217849</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527358</v>
+        <v>526979</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217815</v>
+        <v>129217850</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526883</v>
+        <v>527358</v>
       </c>
       <c r="R4" t="n">
-        <v>7087121</v>
+        <v>7087435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217918</v>
+        <v>129217815</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527262</v>
+        <v>526883</v>
       </c>
       <c r="R5" t="n">
-        <v>7087588</v>
+        <v>7087121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217831</v>
+        <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>80109</v>
+        <v>91553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527362</v>
+        <v>527219</v>
       </c>
       <c r="R6" t="n">
-        <v>7087507</v>
+        <v>7087542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R7" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217799</v>
+        <v>129217831</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527399</v>
+        <v>527362</v>
       </c>
       <c r="R8" t="n">
-        <v>7087454</v>
+        <v>7087507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,11 +1348,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217856</v>
+        <v>129217782</v>
       </c>
       <c r="B9" t="n">
-        <v>92244</v>
+        <v>96973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527386</v>
+        <v>527172</v>
       </c>
       <c r="R9" t="n">
-        <v>7087522</v>
+        <v>7087341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217782</v>
+        <v>129217813</v>
       </c>
       <c r="B10" t="n">
-        <v>96973</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527172</v>
+        <v>526901</v>
       </c>
       <c r="R10" t="n">
-        <v>7087341</v>
+        <v>7087135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,7 +1573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217813</v>
+        <v>129217798</v>
       </c>
       <c r="B11" t="n">
         <v>57727</v>
@@ -1603,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526901</v>
+        <v>527408</v>
       </c>
       <c r="R11" t="n">
-        <v>7087135</v>
+        <v>7087464</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1648,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,32 +1675,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217798</v>
+        <v>129217856</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527408</v>
+        <v>527386</v>
       </c>
       <c r="R12" t="n">
-        <v>7087464</v>
+        <v>7087522</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,45 +1869,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217785</v>
+        <v>129217928</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>82878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527106</v>
+        <v>527359</v>
       </c>
       <c r="R14" t="n">
-        <v>7087220</v>
+        <v>7087548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,6 +1948,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2063,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217840</v>
+        <v>129217852</v>
       </c>
       <c r="B16" t="n">
-        <v>91567</v>
+        <v>82878</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2098,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527386</v>
+        <v>527265</v>
       </c>
       <c r="R16" t="n">
-        <v>7087517</v>
+        <v>7087520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217795</v>
+        <v>129217840</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>91567</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2195,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527123</v>
+        <v>527386</v>
       </c>
       <c r="R17" t="n">
-        <v>7087425</v>
+        <v>7087517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217928</v>
+        <v>129217795</v>
       </c>
       <c r="B18" t="n">
-        <v>82878</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,34 +2269,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527359</v>
+        <v>527123</v>
       </c>
       <c r="R18" t="n">
-        <v>7087548</v>
+        <v>7087425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2336,7 +2337,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217852</v>
+        <v>129217855</v>
       </c>
       <c r="B19" t="n">
         <v>82878</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527265</v>
+        <v>527012</v>
       </c>
       <c r="R19" t="n">
-        <v>7087520</v>
+        <v>7087233</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217855</v>
+        <v>129217797</v>
       </c>
       <c r="B20" t="n">
-        <v>82878</v>
+        <v>92271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527012</v>
+        <v>527368</v>
       </c>
       <c r="R20" t="n">
-        <v>7087233</v>
+        <v>7087576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217797</v>
+        <v>129217780</v>
       </c>
       <c r="B21" t="n">
-        <v>92271</v>
+        <v>83012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527368</v>
+        <v>527179</v>
       </c>
       <c r="R21" t="n">
-        <v>7087576</v>
+        <v>7087518</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217780</v>
+        <v>129217925</v>
       </c>
       <c r="B22" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2657,34 +2657,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527179</v>
+        <v>527089</v>
       </c>
       <c r="R22" t="n">
-        <v>7087518</v>
+        <v>7087260</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,45 +2743,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217925</v>
+        <v>129217785</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527089</v>
+        <v>527106</v>
       </c>
       <c r="R23" t="n">
-        <v>7087260</v>
+        <v>7087220</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217789</v>
+        <v>129217926</v>
       </c>
       <c r="B27" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527376</v>
+        <v>527029</v>
       </c>
       <c r="R27" t="n">
-        <v>7087516</v>
+        <v>7087194</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217910</v>
+        <v>129217789</v>
       </c>
       <c r="B28" t="n">
         <v>91553</v>
@@ -3264,14 +3264,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527288</v>
+        <v>527376</v>
       </c>
       <c r="R28" t="n">
-        <v>7087491</v>
+        <v>7087516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217926</v>
+        <v>129217910</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527029</v>
+        <v>527288</v>
       </c>
       <c r="R29" t="n">
-        <v>7087194</v>
+        <v>7087491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217820</v>
+        <v>129217787</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527034</v>
+        <v>527291</v>
       </c>
       <c r="R31" t="n">
-        <v>7087201</v>
+        <v>7087491</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3600,11 +3600,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3631,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217787</v>
+        <v>129217836</v>
       </c>
       <c r="B32" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3666,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527291</v>
+        <v>527091</v>
       </c>
       <c r="R32" t="n">
-        <v>7087491</v>
+        <v>7087273</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3728,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217922</v>
+        <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3739,16 +3734,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3759,14 +3754,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527122</v>
+        <v>527034</v>
       </c>
       <c r="R33" t="n">
-        <v>7087232</v>
+        <v>7087201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3799,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217836</v>
+        <v>129217922</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>56908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527091</v>
+        <v>527122</v>
       </c>
       <c r="R34" t="n">
-        <v>7087273</v>
+        <v>7087232</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4117,30 +4117,34 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217845</v>
+        <v>129217833</v>
       </c>
       <c r="B37" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4148,10 +4152,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527173</v>
+        <v>527351</v>
       </c>
       <c r="R37" t="n">
-        <v>7087380</v>
+        <v>7087510</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,6 +4188,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4210,32 +4219,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217803</v>
+        <v>129217835</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4245,10 +4254,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526923</v>
+        <v>527103</v>
       </c>
       <c r="R38" t="n">
-        <v>7087199</v>
+        <v>7087341</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,11 +4290,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4414,32 +4418,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4453,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R40" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,7 +4493,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4516,34 +4520,30 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217835</v>
+        <v>129217845</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>91573</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527103</v>
+        <v>527173</v>
       </c>
       <c r="R41" t="n">
-        <v>7087341</v>
+        <v>7087380</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4710,32 +4710,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129217826</v>
+        <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>80053</v>
+        <v>91567</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527090</v>
+        <v>527378</v>
       </c>
       <c r="R43" t="n">
-        <v>7087261</v>
+        <v>7087514</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4904,32 +4904,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217843</v>
+        <v>129217826</v>
       </c>
       <c r="B45" t="n">
-        <v>91567</v>
+        <v>80053</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527378</v>
+        <v>527090</v>
       </c>
       <c r="R45" t="n">
-        <v>7087514</v>
+        <v>7087261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,32 +5098,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217790</v>
+        <v>129217844</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>57719</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527357</v>
+        <v>527355</v>
       </c>
       <c r="R47" t="n">
-        <v>7087574</v>
+        <v>7087521</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217923</v>
+        <v>129217805</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5206,34 +5206,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527150</v>
+        <v>526924</v>
       </c>
       <c r="R48" t="n">
-        <v>7087278</v>
+        <v>7087183</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5297,45 +5297,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217844</v>
+        <v>129217920</v>
       </c>
       <c r="B49" t="n">
-        <v>57719</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527355</v>
+        <v>527064</v>
       </c>
       <c r="R49" t="n">
-        <v>7087521</v>
+        <v>7087252</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5368,6 +5368,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5394,10 +5399,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217805</v>
+        <v>129217923</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5405,34 +5410,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>526924</v>
+        <v>527150</v>
       </c>
       <c r="R50" t="n">
-        <v>7087183</v>
+        <v>7087278</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5469,7 +5474,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5496,45 +5501,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217920</v>
+        <v>129217790</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527064</v>
+        <v>527357</v>
       </c>
       <c r="R51" t="n">
-        <v>7087252</v>
+        <v>7087574</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5567,11 +5572,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5598,10 +5598,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217794</v>
+        <v>129217800</v>
       </c>
       <c r="B52" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5609,21 +5609,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527134</v>
+        <v>527297</v>
       </c>
       <c r="R52" t="n">
-        <v>7087464</v>
+        <v>7087514</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5669,6 +5669,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5695,7 +5700,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217801</v>
       </c>
       <c r="B53" t="n">
         <v>57727</v>
@@ -5723,37 +5728,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>527106</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087348</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5790,7 +5775,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5817,7 +5802,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217819</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5845,17 +5830,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>527070</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087285</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5897,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,10 +5924,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217794</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5930,21 +5935,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5954,10 +5959,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>527134</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087464</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5990,11 +5995,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217823</v>
+        <v>129217848</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527374</v>
+        <v>527106</v>
       </c>
       <c r="R57" t="n">
-        <v>7087508</v>
+        <v>7087367</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6322,10 +6322,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217848</v>
+        <v>129217823</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527106</v>
+        <v>527374</v>
       </c>
       <c r="R59" t="n">
-        <v>7087367</v>
+        <v>7087508</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,7 +6424,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217919</v>
+        <v>129217832</v>
       </c>
       <c r="B60" t="n">
         <v>98727</v>
@@ -6455,14 +6455,14 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527135</v>
+        <v>527149</v>
       </c>
       <c r="R60" t="n">
-        <v>7087449</v>
+        <v>7087289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,7 +6526,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217832</v>
+        <v>129217919</v>
       </c>
       <c r="B61" t="n">
         <v>98727</v>
@@ -6557,14 +6557,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527149</v>
+        <v>527135</v>
       </c>
       <c r="R61" t="n">
-        <v>7087289</v>
+        <v>7087449</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6730,32 +6730,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217827</v>
+        <v>129217818</v>
       </c>
       <c r="B63" t="n">
-        <v>92006</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527136</v>
+        <v>527359</v>
       </c>
       <c r="R63" t="n">
-        <v>7087471</v>
+        <v>7087452</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6801,6 +6801,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6827,10 +6832,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217854</v>
+        <v>129217810</v>
       </c>
       <c r="B64" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6838,21 +6843,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6862,10 +6867,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527015</v>
+        <v>526914</v>
       </c>
       <c r="R64" t="n">
-        <v>7087228</v>
+        <v>7087139</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6898,6 +6903,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6924,10 +6934,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217829</v>
+        <v>129217806</v>
       </c>
       <c r="B65" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6935,21 +6945,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6959,10 +6969,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527138</v>
+        <v>526925</v>
       </c>
       <c r="R65" t="n">
-        <v>7087472</v>
+        <v>7087175</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6995,6 +7005,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7021,10 +7036,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217806</v>
+        <v>129217829</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7032,21 +7047,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7056,10 +7071,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526925</v>
+        <v>527138</v>
       </c>
       <c r="R66" t="n">
-        <v>7087175</v>
+        <v>7087472</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7092,11 +7107,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7123,32 +7133,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217810</v>
+        <v>129217827</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>92006</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7158,10 +7168,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526914</v>
+        <v>527136</v>
       </c>
       <c r="R67" t="n">
-        <v>7087139</v>
+        <v>7087471</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7194,11 +7204,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7225,10 +7230,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217818</v>
+        <v>129217854</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7236,21 +7241,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7260,10 +7265,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527359</v>
+        <v>527015</v>
       </c>
       <c r="R68" t="n">
-        <v>7087452</v>
+        <v>7087228</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7296,11 +7301,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217853</v>
+        <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>82878</v>
+        <v>91553</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527133</v>
+        <v>527238</v>
       </c>
       <c r="R70" t="n">
-        <v>7087390</v>
+        <v>7087520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7526,7 +7526,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217786</v>
+        <v>129217911</v>
       </c>
       <c r="B71" t="n">
         <v>91553</v>
@@ -7557,14 +7557,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527238</v>
+        <v>527164</v>
       </c>
       <c r="R71" t="n">
-        <v>7087520</v>
+        <v>7087462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7623,10 +7623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217911</v>
+        <v>129217853</v>
       </c>
       <c r="B72" t="n">
-        <v>91553</v>
+        <v>82878</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7634,34 +7634,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527164</v>
+        <v>527133</v>
       </c>
       <c r="R72" t="n">
-        <v>7087462</v>
+        <v>7087390</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7817,7 +7817,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217804</v>
+        <v>129217808</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7852,10 +7852,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526927</v>
+        <v>526917</v>
       </c>
       <c r="R74" t="n">
-        <v>7087193</v>
+        <v>7087144</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217808</v>
+        <v>129217804</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526917</v>
+        <v>526927</v>
       </c>
       <c r="R75" t="n">
-        <v>7087144</v>
+        <v>7087193</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217830</v>
+        <v>129217912</v>
       </c>
       <c r="B78" t="n">
-        <v>78057</v>
+        <v>80149</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,34 +8226,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>526990</v>
+        <v>527089</v>
       </c>
       <c r="R78" t="n">
-        <v>7087234</v>
+        <v>7087260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,6 +8286,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8312,32 +8317,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217921</v>
+        <v>129217924</v>
       </c>
       <c r="B79" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8347,10 +8352,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526984</v>
+        <v>527289</v>
       </c>
       <c r="R79" t="n">
-        <v>7087226</v>
+        <v>7087449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8383,11 +8388,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8414,7 +8414,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217914</v>
+        <v>129217921</v>
       </c>
       <c r="B80" t="n">
         <v>98727</v>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526928</v>
+        <v>526984</v>
       </c>
       <c r="R80" t="n">
-        <v>7087112</v>
+        <v>7087226</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8516,32 +8516,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217912</v>
+        <v>129217914</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527089</v>
+        <v>526928</v>
       </c>
       <c r="R81" t="n">
-        <v>7087260</v>
+        <v>7087112</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8618,10 +8618,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217924</v>
+        <v>129217830</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8629,34 +8629,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527289</v>
+        <v>526990</v>
       </c>
       <c r="R82" t="n">
-        <v>7087449</v>
+        <v>7087234</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9016,45 +9016,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217851</v>
+        <v>129217915</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527094</v>
+        <v>527145</v>
       </c>
       <c r="R86" t="n">
-        <v>7087264</v>
+        <v>7087306</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9118,10 +9118,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217783</v>
+        <v>129217851</v>
       </c>
       <c r="B87" t="n">
-        <v>96973</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9129,21 +9129,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527221</v>
+        <v>527094</v>
       </c>
       <c r="R87" t="n">
-        <v>7087348</v>
+        <v>7087264</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9189,6 +9189,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9215,10 +9220,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217847</v>
+        <v>129217783</v>
       </c>
       <c r="B88" t="n">
-        <v>91573</v>
+        <v>96973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9226,19 +9231,23 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9246,10 +9255,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527069</v>
+        <v>527221</v>
       </c>
       <c r="R88" t="n">
-        <v>7087323</v>
+        <v>7087348</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9308,10 +9317,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217814</v>
+        <v>129217847</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9319,23 +9328,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9343,10 +9348,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526905</v>
+        <v>527069</v>
       </c>
       <c r="R89" t="n">
-        <v>7087117</v>
+        <v>7087323</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9379,11 +9384,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9410,45 +9410,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129217915</v>
+        <v>129217814</v>
       </c>
       <c r="B90" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527145</v>
+        <v>526905</v>
       </c>
       <c r="R90" t="n">
-        <v>7087306</v>
+        <v>7087117</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Många rosetter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217918</v>
+        <v>129217849</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527262</v>
+        <v>526979</v>
       </c>
       <c r="R2" t="n">
-        <v>7087588</v>
+        <v>7087143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217849</v>
+        <v>129217815</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526979</v>
+        <v>526883</v>
       </c>
       <c r="R3" t="n">
-        <v>7087143</v>
+        <v>7087121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217815</v>
+        <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526883</v>
+        <v>527262</v>
       </c>
       <c r="R5" t="n">
-        <v>7087121</v>
+        <v>7087588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217782</v>
+        <v>129217813</v>
       </c>
       <c r="B9" t="n">
-        <v>96973</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527172</v>
+        <v>526901</v>
       </c>
       <c r="R9" t="n">
-        <v>7087341</v>
+        <v>7087135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1445,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,7 +1476,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217813</v>
+        <v>129217798</v>
       </c>
       <c r="B10" t="n">
         <v>57727</v>
@@ -1506,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526901</v>
+        <v>527408</v>
       </c>
       <c r="R10" t="n">
-        <v>7087135</v>
+        <v>7087464</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217798</v>
+        <v>129217782</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>96973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527408</v>
+        <v>527172</v>
       </c>
       <c r="R11" t="n">
-        <v>7087464</v>
+        <v>7087341</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,45 +1869,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217928</v>
+        <v>129217797</v>
       </c>
       <c r="B14" t="n">
-        <v>82878</v>
+        <v>92271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527359</v>
+        <v>527368</v>
       </c>
       <c r="R14" t="n">
-        <v>7087548</v>
+        <v>7087576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1948,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217842</v>
+        <v>129217928</v>
       </c>
       <c r="B15" t="n">
-        <v>91567</v>
+        <v>82878</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1978,34 +1977,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527385</v>
+        <v>527359</v>
       </c>
       <c r="R15" t="n">
-        <v>7087528</v>
+        <v>7087548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2046,6 +2045,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217852</v>
+        <v>129217842</v>
       </c>
       <c r="B16" t="n">
-        <v>82878</v>
+        <v>91567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527265</v>
+        <v>527385</v>
       </c>
       <c r="R16" t="n">
-        <v>7087520</v>
+        <v>7087528</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217840</v>
+        <v>129217852</v>
       </c>
       <c r="B17" t="n">
-        <v>91567</v>
+        <v>82878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527386</v>
+        <v>527265</v>
       </c>
       <c r="R17" t="n">
-        <v>7087517</v>
+        <v>7087520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217795</v>
+        <v>129217840</v>
       </c>
       <c r="B18" t="n">
-        <v>91553</v>
+        <v>91567</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527123</v>
+        <v>527386</v>
       </c>
       <c r="R18" t="n">
-        <v>7087425</v>
+        <v>7087517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217855</v>
+        <v>129217795</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>91553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527012</v>
+        <v>527123</v>
       </c>
       <c r="R19" t="n">
-        <v>7087233</v>
+        <v>7087425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217797</v>
+        <v>129217855</v>
       </c>
       <c r="B20" t="n">
-        <v>92271</v>
+        <v>82878</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527368</v>
+        <v>527012</v>
       </c>
       <c r="R20" t="n">
-        <v>7087576</v>
+        <v>7087233</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217926</v>
+        <v>129217910</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527029</v>
+        <v>527288</v>
       </c>
       <c r="R27" t="n">
-        <v>7087194</v>
+        <v>7087491</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217910</v>
+        <v>129217926</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527288</v>
+        <v>527029</v>
       </c>
       <c r="R29" t="n">
-        <v>7087491</v>
+        <v>7087194</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217836</v>
+        <v>129217820</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527091</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>7087273</v>
+        <v>7087201</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,6 +3697,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3723,10 +3728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,16 +3739,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3754,14 +3759,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R33" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3799,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,45 +3825,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217922</v>
+        <v>129217836</v>
       </c>
       <c r="B34" t="n">
-        <v>56908</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527122</v>
+        <v>527091</v>
       </c>
       <c r="R34" t="n">
-        <v>7087232</v>
+        <v>7087273</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4316,7 +4316,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217821</v>
+        <v>129217803</v>
       </c>
       <c r="B39" t="n">
         <v>57727</v>
@@ -4351,10 +4351,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526924</v>
+        <v>526923</v>
       </c>
       <c r="R39" t="n">
-        <v>7087187</v>
+        <v>7087199</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4418,7 +4418,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217803</v>
+        <v>129217821</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526923</v>
+        <v>526924</v>
       </c>
       <c r="R40" t="n">
-        <v>7087199</v>
+        <v>7087187</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4807,10 +4807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217838</v>
+        <v>129217778</v>
       </c>
       <c r="B44" t="n">
-        <v>56908</v>
+        <v>83012</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4818,21 +4818,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527239</v>
+        <v>526957</v>
       </c>
       <c r="R44" t="n">
-        <v>7087332</v>
+        <v>7087142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217778</v>
+        <v>129217838</v>
       </c>
       <c r="B46" t="n">
-        <v>83012</v>
+        <v>56908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5012,21 +5012,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>526957</v>
+        <v>527239</v>
       </c>
       <c r="R46" t="n">
-        <v>7087142</v>
+        <v>7087332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5098,32 +5098,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217844</v>
+        <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>57719</v>
+        <v>91553</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100110</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527355</v>
+        <v>527357</v>
       </c>
       <c r="R47" t="n">
-        <v>7087521</v>
+        <v>7087574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5297,32 +5297,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217920</v>
+        <v>129217923</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527064</v>
+        <v>527150</v>
       </c>
       <c r="R49" t="n">
-        <v>7087252</v>
+        <v>7087278</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5399,45 +5399,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217923</v>
+        <v>129217844</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>57719</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100110</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527150</v>
+        <v>527355</v>
       </c>
       <c r="R50" t="n">
-        <v>7087278</v>
+        <v>7087521</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,11 +5470,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5501,45 +5496,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217790</v>
+        <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527357</v>
+        <v>527064</v>
       </c>
       <c r="R51" t="n">
-        <v>7087574</v>
+        <v>7087252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5572,6 +5567,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5598,32 +5598,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217800</v>
+        <v>129217837</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527297</v>
+        <v>526980</v>
       </c>
       <c r="R52" t="n">
-        <v>7087514</v>
+        <v>7087208</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5700,10 +5700,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217801</v>
+        <v>129217794</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5711,21 +5711,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527106</v>
+        <v>527134</v>
       </c>
       <c r="R53" t="n">
-        <v>7087348</v>
+        <v>7087464</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,11 +5771,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5924,10 +5919,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217794</v>
+        <v>129217800</v>
       </c>
       <c r="B55" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5935,21 +5930,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5959,10 +5954,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527134</v>
+        <v>527297</v>
       </c>
       <c r="R55" t="n">
-        <v>7087464</v>
+        <v>7087514</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5995,6 +5990,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217837</v>
+        <v>129217801</v>
       </c>
       <c r="B56" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526980</v>
+        <v>527106</v>
       </c>
       <c r="R56" t="n">
-        <v>7087208</v>
+        <v>7087348</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217848</v>
+        <v>129217784</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>96973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527106</v>
+        <v>527349</v>
       </c>
       <c r="R57" t="n">
-        <v>7087367</v>
+        <v>7087510</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,11 +6194,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6225,32 +6220,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217784</v>
+        <v>129217832</v>
       </c>
       <c r="B58" t="n">
-        <v>96973</v>
+        <v>98727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6260,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527349</v>
+        <v>527149</v>
       </c>
       <c r="R58" t="n">
-        <v>7087510</v>
+        <v>7087289</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6296,6 +6291,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,45 +6322,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217823</v>
+        <v>129217919</v>
       </c>
       <c r="B59" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527374</v>
+        <v>527135</v>
       </c>
       <c r="R59" t="n">
-        <v>7087508</v>
+        <v>7087449</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,7 +6424,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217832</v>
+        <v>129217834</v>
       </c>
       <c r="B60" t="n">
         <v>98727</v>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527149</v>
+        <v>527268</v>
       </c>
       <c r="R60" t="n">
-        <v>7087289</v>
+        <v>7087590</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,45 +6526,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217919</v>
+        <v>129217823</v>
       </c>
       <c r="B61" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527135</v>
+        <v>527374</v>
       </c>
       <c r="R61" t="n">
-        <v>7087449</v>
+        <v>7087508</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6628,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217834</v>
+        <v>129217848</v>
       </c>
       <c r="B62" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527268</v>
+        <v>527106</v>
       </c>
       <c r="R62" t="n">
-        <v>7087590</v>
+        <v>7087367</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217818</v>
+        <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6741,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6765,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527359</v>
+        <v>527138</v>
       </c>
       <c r="R63" t="n">
-        <v>7087452</v>
+        <v>7087472</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6801,11 +6801,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6832,32 +6827,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217810</v>
+        <v>129217827</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>92006</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6867,10 +6862,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526914</v>
+        <v>527136</v>
       </c>
       <c r="R64" t="n">
-        <v>7087139</v>
+        <v>7087471</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6903,11 +6898,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6934,10 +6924,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217806</v>
+        <v>129217854</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6945,21 +6935,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6969,10 +6959,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526925</v>
+        <v>527015</v>
       </c>
       <c r="R65" t="n">
-        <v>7087175</v>
+        <v>7087228</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7005,11 +6995,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7036,45 +7021,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217829</v>
+        <v>129217913</v>
       </c>
       <c r="B66" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527138</v>
+        <v>526924</v>
       </c>
       <c r="R66" t="n">
-        <v>7087472</v>
+        <v>7087085</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7107,6 +7092,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7133,32 +7123,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217827</v>
+        <v>129217806</v>
       </c>
       <c r="B67" t="n">
-        <v>92006</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7168,10 +7158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527136</v>
+        <v>526925</v>
       </c>
       <c r="R67" t="n">
-        <v>7087471</v>
+        <v>7087175</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7204,6 +7194,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7230,10 +7225,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217854</v>
+        <v>129217810</v>
       </c>
       <c r="B68" t="n">
-        <v>82878</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7241,21 +7236,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7265,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527015</v>
+        <v>526914</v>
       </c>
       <c r="R68" t="n">
-        <v>7087228</v>
+        <v>7087139</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7301,6 +7296,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7327,45 +7327,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217913</v>
+        <v>129217818</v>
       </c>
       <c r="B69" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526924</v>
+        <v>527359</v>
       </c>
       <c r="R69" t="n">
-        <v>7087085</v>
+        <v>7087452</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7817,7 +7817,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217808</v>
+        <v>129217804</v>
       </c>
       <c r="B74" t="n">
         <v>57727</v>
@@ -7852,10 +7852,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526917</v>
+        <v>526927</v>
       </c>
       <c r="R74" t="n">
-        <v>7087144</v>
+        <v>7087193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217804</v>
+        <v>129217808</v>
       </c>
       <c r="B75" t="n">
         <v>57727</v>
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526927</v>
+        <v>526917</v>
       </c>
       <c r="R75" t="n">
-        <v>7087193</v>
+        <v>7087144</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217912</v>
+        <v>129217841</v>
       </c>
       <c r="B78" t="n">
-        <v>80149</v>
+        <v>91567</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,34 +8226,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527089</v>
+        <v>527375</v>
       </c>
       <c r="R78" t="n">
-        <v>7087260</v>
+        <v>7087521</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,11 +8286,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8317,10 +8312,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217924</v>
+        <v>129217912</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8328,21 +8323,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8352,10 +8347,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527289</v>
+        <v>527089</v>
       </c>
       <c r="R79" t="n">
-        <v>7087449</v>
+        <v>7087260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8388,6 +8383,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8414,32 +8414,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217921</v>
+        <v>129217929</v>
       </c>
       <c r="B80" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526984</v>
+        <v>527393</v>
       </c>
       <c r="R80" t="n">
-        <v>7087226</v>
+        <v>7087440</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8516,7 +8516,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217914</v>
+        <v>129217921</v>
       </c>
       <c r="B81" t="n">
         <v>98727</v>
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526928</v>
+        <v>526984</v>
       </c>
       <c r="R81" t="n">
-        <v>7087112</v>
+        <v>7087226</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8618,45 +8618,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217830</v>
+        <v>129217914</v>
       </c>
       <c r="B82" t="n">
-        <v>78057</v>
+        <v>98727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526990</v>
+        <v>526928</v>
       </c>
       <c r="R82" t="n">
-        <v>7087234</v>
+        <v>7087112</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8689,6 +8689,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8715,10 +8720,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217841</v>
+        <v>129217924</v>
       </c>
       <c r="B83" t="n">
-        <v>91567</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8726,34 +8731,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>527375</v>
+        <v>527289</v>
       </c>
       <c r="R83" t="n">
-        <v>7087521</v>
+        <v>7087449</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8914,10 +8919,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217929</v>
+        <v>129217830</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>78057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8925,34 +8930,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527393</v>
+        <v>526990</v>
       </c>
       <c r="R85" t="n">
-        <v>7087440</v>
+        <v>7087234</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8985,11 +8990,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9016,45 +9016,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217915</v>
+        <v>129217783</v>
       </c>
       <c r="B86" t="n">
-        <v>98727</v>
+        <v>96973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527145</v>
+        <v>527221</v>
       </c>
       <c r="R86" t="n">
-        <v>7087306</v>
+        <v>7087348</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9087,11 +9087,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9220,45 +9215,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217783</v>
+        <v>129217915</v>
       </c>
       <c r="B88" t="n">
-        <v>96973</v>
+        <v>98727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527221</v>
+        <v>527145</v>
       </c>
       <c r="R88" t="n">
-        <v>7087348</v>
+        <v>7087306</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9291,6 +9286,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217815</v>
+        <v>129217850</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526883</v>
+        <v>527358</v>
       </c>
       <c r="R3" t="n">
-        <v>7087121</v>
+        <v>7087435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217850</v>
+        <v>129217815</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527358</v>
+        <v>526883</v>
       </c>
       <c r="R4" t="n">
-        <v>7087435</v>
+        <v>7087121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B6" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R6" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217813</v>
+        <v>129217782</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>96973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526901</v>
+        <v>527172</v>
       </c>
       <c r="R9" t="n">
-        <v>7087135</v>
+        <v>7087341</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217798</v>
+        <v>129217856</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>92244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527408</v>
+        <v>527386</v>
       </c>
       <c r="R10" t="n">
-        <v>7087464</v>
+        <v>7087522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1542,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217782</v>
+        <v>129217813</v>
       </c>
       <c r="B11" t="n">
-        <v>96973</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527172</v>
+        <v>526901</v>
       </c>
       <c r="R11" t="n">
-        <v>7087341</v>
+        <v>7087135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1639,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,32 +1670,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217856</v>
+        <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>92244</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527386</v>
+        <v>527408</v>
       </c>
       <c r="R12" t="n">
-        <v>7087522</v>
+        <v>7087464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,45 +1869,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217797</v>
+        <v>129217928</v>
       </c>
       <c r="B14" t="n">
-        <v>92271</v>
+        <v>82878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527368</v>
+        <v>527359</v>
       </c>
       <c r="R14" t="n">
-        <v>7087576</v>
+        <v>7087548</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,6 +1948,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217928</v>
+        <v>129217842</v>
       </c>
       <c r="B15" t="n">
-        <v>82878</v>
+        <v>91567</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,34 +1978,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527359</v>
+        <v>527385</v>
       </c>
       <c r="R15" t="n">
-        <v>7087548</v>
+        <v>7087528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,7 +2046,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217842</v>
+        <v>129217852</v>
       </c>
       <c r="B16" t="n">
-        <v>91567</v>
+        <v>82878</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527385</v>
+        <v>527265</v>
       </c>
       <c r="R16" t="n">
-        <v>7087528</v>
+        <v>7087520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217852</v>
+        <v>129217840</v>
       </c>
       <c r="B17" t="n">
-        <v>82878</v>
+        <v>91567</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527265</v>
+        <v>527386</v>
       </c>
       <c r="R17" t="n">
-        <v>7087520</v>
+        <v>7087517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217840</v>
+        <v>129217795</v>
       </c>
       <c r="B18" t="n">
-        <v>91567</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2269,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527386</v>
+        <v>527123</v>
       </c>
       <c r="R18" t="n">
-        <v>7087517</v>
+        <v>7087425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217795</v>
+        <v>129217855</v>
       </c>
       <c r="B19" t="n">
-        <v>91553</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527123</v>
+        <v>527012</v>
       </c>
       <c r="R19" t="n">
-        <v>7087425</v>
+        <v>7087233</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217855</v>
+        <v>129217785</v>
       </c>
       <c r="B20" t="n">
-        <v>82878</v>
+        <v>91517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527012</v>
+        <v>527106</v>
       </c>
       <c r="R20" t="n">
-        <v>7087233</v>
+        <v>7087220</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217780</v>
+        <v>129217797</v>
       </c>
       <c r="B21" t="n">
-        <v>83012</v>
+        <v>92271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527179</v>
+        <v>527368</v>
       </c>
       <c r="R21" t="n">
-        <v>7087518</v>
+        <v>7087576</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217925</v>
+        <v>129217780</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2657,34 +2657,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527089</v>
+        <v>527179</v>
       </c>
       <c r="R22" t="n">
-        <v>7087260</v>
+        <v>7087518</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2743,45 +2743,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217785</v>
+        <v>129217925</v>
       </c>
       <c r="B23" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527106</v>
+        <v>527089</v>
       </c>
       <c r="R23" t="n">
-        <v>7087220</v>
+        <v>7087260</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217910</v>
+        <v>129217789</v>
       </c>
       <c r="B27" t="n">
         <v>91553</v>
@@ -3167,14 +3167,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527288</v>
+        <v>527376</v>
       </c>
       <c r="R27" t="n">
-        <v>7087491</v>
+        <v>7087516</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217789</v>
+        <v>129217910</v>
       </c>
       <c r="B28" t="n">
         <v>91553</v>
@@ -3264,14 +3264,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527376</v>
+        <v>527288</v>
       </c>
       <c r="R28" t="n">
-        <v>7087516</v>
+        <v>7087491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3657,14 +3657,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R32" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,11 +3697,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3728,45 +3723,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217922</v>
+        <v>129217836</v>
       </c>
       <c r="B33" t="n">
-        <v>56908</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527122</v>
+        <v>527091</v>
       </c>
       <c r="R33" t="n">
-        <v>7087232</v>
+        <v>7087273</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3825,32 +3820,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217836</v>
+        <v>129217820</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3860,10 +3855,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527091</v>
+        <v>527034</v>
       </c>
       <c r="R34" t="n">
-        <v>7087273</v>
+        <v>7087201</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,6 +3891,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4117,32 +4117,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217833</v>
+        <v>129217803</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527351</v>
+        <v>526923</v>
       </c>
       <c r="R37" t="n">
-        <v>7087510</v>
+        <v>7087199</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4219,32 +4219,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217835</v>
+        <v>129217821</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527103</v>
+        <v>526924</v>
       </c>
       <c r="R38" t="n">
-        <v>7087341</v>
+        <v>7087187</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4290,6 +4290,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4316,32 +4321,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217803</v>
+        <v>129217833</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4351,10 +4356,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526923</v>
+        <v>527351</v>
       </c>
       <c r="R39" t="n">
-        <v>7087199</v>
+        <v>7087510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4391,7 +4396,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4418,32 +4423,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217821</v>
+        <v>129217835</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4453,10 +4458,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>526924</v>
+        <v>527103</v>
       </c>
       <c r="R40" t="n">
-        <v>7087187</v>
+        <v>7087341</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4489,11 +4494,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4807,32 +4807,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217778</v>
+        <v>129217826</v>
       </c>
       <c r="B44" t="n">
-        <v>83012</v>
+        <v>80053</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>526957</v>
+        <v>527090</v>
       </c>
       <c r="R44" t="n">
-        <v>7087142</v>
+        <v>7087261</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,32 +4904,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217826</v>
+        <v>129217778</v>
       </c>
       <c r="B45" t="n">
-        <v>80053</v>
+        <v>83012</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527090</v>
+        <v>526957</v>
       </c>
       <c r="R45" t="n">
-        <v>7087261</v>
+        <v>7087142</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217790</v>
+        <v>129217923</v>
       </c>
       <c r="B47" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5109,34 +5109,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527357</v>
+        <v>527150</v>
       </c>
       <c r="R47" t="n">
-        <v>7087574</v>
+        <v>7087278</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5169,6 +5169,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5195,45 +5200,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217805</v>
+        <v>129217920</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>526924</v>
+        <v>527064</v>
       </c>
       <c r="R48" t="n">
-        <v>7087183</v>
+        <v>7087252</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5270,7 +5275,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5297,10 +5302,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5308,34 +5313,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R49" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5368,11 +5373,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5496,45 +5496,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217920</v>
+        <v>129217805</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527064</v>
+        <v>526924</v>
       </c>
       <c r="R51" t="n">
-        <v>7087252</v>
+        <v>7087183</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5700,10 +5700,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217794</v>
+        <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5711,34 +5711,54 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527134</v>
+        <v>527070</v>
       </c>
       <c r="R53" t="n">
-        <v>7087464</v>
+        <v>7087285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5771,6 +5791,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5797,7 +5822,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217819</v>
+        <v>129217800</v>
       </c>
       <c r="B54" t="n">
         <v>57727</v>
@@ -5825,37 +5850,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527070</v>
+        <v>527297</v>
       </c>
       <c r="R54" t="n">
-        <v>7087285</v>
+        <v>7087514</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5897,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,7 +5924,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217800</v>
+        <v>129217801</v>
       </c>
       <c r="B55" t="n">
         <v>57727</v>
@@ -5954,10 +5959,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527297</v>
+        <v>527106</v>
       </c>
       <c r="R55" t="n">
-        <v>7087514</v>
+        <v>7087348</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5994,7 +5999,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6021,10 +6026,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217801</v>
+        <v>129217794</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6032,21 +6037,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6061,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527106</v>
+        <v>527134</v>
       </c>
       <c r="R56" t="n">
-        <v>7087348</v>
+        <v>7087464</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6092,11 +6097,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217784</v>
+        <v>129217848</v>
       </c>
       <c r="B57" t="n">
-        <v>96973</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527349</v>
+        <v>527106</v>
       </c>
       <c r="R57" t="n">
-        <v>7087510</v>
+        <v>7087367</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6194,6 +6194,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6220,32 +6225,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217832</v>
+        <v>129217823</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527149</v>
+        <v>527374</v>
       </c>
       <c r="R58" t="n">
-        <v>7087289</v>
+        <v>7087508</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6295,7 +6300,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6322,45 +6327,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217919</v>
+        <v>129217784</v>
       </c>
       <c r="B59" t="n">
-        <v>98727</v>
+        <v>96973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527135</v>
+        <v>527349</v>
       </c>
       <c r="R59" t="n">
-        <v>7087449</v>
+        <v>7087510</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6393,11 +6398,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,7 +6424,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217834</v>
+        <v>129217832</v>
       </c>
       <c r="B60" t="n">
         <v>98727</v>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527268</v>
+        <v>527149</v>
       </c>
       <c r="R60" t="n">
-        <v>7087590</v>
+        <v>7087289</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,45 +6526,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217823</v>
+        <v>129217919</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527374</v>
+        <v>527135</v>
       </c>
       <c r="R61" t="n">
-        <v>7087508</v>
+        <v>7087449</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6628,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217848</v>
+        <v>129217834</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527106</v>
+        <v>527268</v>
       </c>
       <c r="R62" t="n">
-        <v>7087367</v>
+        <v>7087590</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217786</v>
+        <v>129217804</v>
       </c>
       <c r="B70" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527238</v>
+        <v>526927</v>
       </c>
       <c r="R70" t="n">
-        <v>7087520</v>
+        <v>7087193</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7500,6 +7500,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7526,10 +7531,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217911</v>
+        <v>129217808</v>
       </c>
       <c r="B71" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7537,34 +7542,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527164</v>
+        <v>526917</v>
       </c>
       <c r="R71" t="n">
-        <v>7087462</v>
+        <v>7087144</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7597,6 +7602,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7623,10 +7633,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217853</v>
+        <v>129217786</v>
       </c>
       <c r="B72" t="n">
-        <v>82878</v>
+        <v>91553</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7634,21 +7644,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7658,10 +7668,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527133</v>
+        <v>527238</v>
       </c>
       <c r="R72" t="n">
-        <v>7087390</v>
+        <v>7087520</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7720,10 +7730,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217781</v>
+        <v>129217911</v>
       </c>
       <c r="B73" t="n">
-        <v>83012</v>
+        <v>91553</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7731,34 +7741,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527141</v>
+        <v>527164</v>
       </c>
       <c r="R73" t="n">
-        <v>7087466</v>
+        <v>7087462</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7817,10 +7827,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217804</v>
+        <v>129217853</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>82878</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7828,21 +7838,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7852,10 +7862,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526927</v>
+        <v>527133</v>
       </c>
       <c r="R74" t="n">
-        <v>7087193</v>
+        <v>7087390</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7888,11 +7898,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7919,10 +7924,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217808</v>
+        <v>129217781</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>83012</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7930,21 +7935,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7954,10 +7959,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526917</v>
+        <v>527141</v>
       </c>
       <c r="R75" t="n">
-        <v>7087144</v>
+        <v>7087466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7990,11 +7995,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8414,10 +8414,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217929</v>
+        <v>129217924</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8425,21 +8425,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527393</v>
+        <v>527289</v>
       </c>
       <c r="R80" t="n">
-        <v>7087440</v>
+        <v>7087449</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8485,11 +8485,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8516,45 +8511,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217921</v>
+        <v>129217802</v>
       </c>
       <c r="B81" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526984</v>
+        <v>526934</v>
       </c>
       <c r="R81" t="n">
-        <v>7087226</v>
+        <v>7087213</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8591,7 +8586,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8618,32 +8613,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217914</v>
+        <v>129217929</v>
       </c>
       <c r="B82" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8653,10 +8648,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526928</v>
+        <v>527393</v>
       </c>
       <c r="R82" t="n">
-        <v>7087112</v>
+        <v>7087440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8693,7 +8688,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8720,32 +8715,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217924</v>
+        <v>129217921</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8755,10 +8750,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>527289</v>
+        <v>526984</v>
       </c>
       <c r="R83" t="n">
-        <v>7087449</v>
+        <v>7087226</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8791,6 +8786,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8817,45 +8817,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217802</v>
+        <v>129217914</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526934</v>
+        <v>526928</v>
       </c>
       <c r="R84" t="n">
-        <v>7087213</v>
+        <v>7087112</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9016,10 +9016,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217783</v>
+        <v>129217847</v>
       </c>
       <c r="B86" t="n">
-        <v>96973</v>
+        <v>91573</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9027,23 +9027,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9051,10 +9047,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527221</v>
+        <v>527069</v>
       </c>
       <c r="R86" t="n">
-        <v>7087348</v>
+        <v>7087323</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9113,45 +9109,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217851</v>
+        <v>129217915</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527094</v>
+        <v>527145</v>
       </c>
       <c r="R87" t="n">
-        <v>7087264</v>
+        <v>7087306</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9188,7 +9184,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9215,45 +9211,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129217915</v>
+        <v>129217783</v>
       </c>
       <c r="B88" t="n">
-        <v>98727</v>
+        <v>96973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527145</v>
+        <v>527221</v>
       </c>
       <c r="R88" t="n">
-        <v>7087306</v>
+        <v>7087348</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9286,11 +9282,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9317,10 +9308,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129217847</v>
+        <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9328,19 +9319,23 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9348,10 +9343,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527069</v>
+        <v>527094</v>
       </c>
       <c r="R89" t="n">
-        <v>7087323</v>
+        <v>7087264</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9384,6 +9379,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129217849</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129217850</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129217815</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129217918</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217799</v>
+        <v>129217791</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>91581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527399</v>
+        <v>527219</v>
       </c>
       <c r="R6" t="n">
-        <v>7087454</v>
+        <v>7087542</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217791</v>
+        <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527219</v>
+        <v>527399</v>
       </c>
       <c r="R7" t="n">
-        <v>7087542</v>
+        <v>7087454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,7 +1280,7 @@
         <v>129217831</v>
       </c>
       <c r="B8" t="n">
-        <v>80109</v>
+        <v>80135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129217782</v>
       </c>
       <c r="B9" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,32 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217856</v>
+        <v>129217813</v>
       </c>
       <c r="B10" t="n">
-        <v>92244</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527386</v>
+        <v>526901</v>
       </c>
       <c r="R10" t="n">
-        <v>7087522</v>
+        <v>7087135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,6 +1542,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217813</v>
+        <v>129217798</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526901</v>
+        <v>527408</v>
       </c>
       <c r="R11" t="n">
-        <v>7087135</v>
+        <v>7087464</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,7 +1648,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1670,32 +1675,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217798</v>
+        <v>129217856</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92272</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527408</v>
+        <v>527386</v>
       </c>
       <c r="R12" t="n">
-        <v>7087464</v>
+        <v>7087522</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1746,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,7 +1775,7 @@
         <v>129217927</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217928</v>
+        <v>129217842</v>
       </c>
       <c r="B14" t="n">
-        <v>82878</v>
+        <v>91595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527359</v>
+        <v>527385</v>
       </c>
       <c r="R14" t="n">
-        <v>7087548</v>
+        <v>7087528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1948,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1967,10 +1966,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217842</v>
+        <v>129217840</v>
       </c>
       <c r="B15" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2002,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527385</v>
+        <v>527386</v>
       </c>
       <c r="R15" t="n">
-        <v>7087528</v>
+        <v>7087517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,10 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129217852</v>
+        <v>129217795</v>
       </c>
       <c r="B16" t="n">
-        <v>82878</v>
+        <v>91581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527265</v>
+        <v>527123</v>
       </c>
       <c r="R16" t="n">
-        <v>7087520</v>
+        <v>7087425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,32 +2160,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217840</v>
+        <v>129217797</v>
       </c>
       <c r="B17" t="n">
-        <v>91567</v>
+        <v>92299</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527386</v>
+        <v>527368</v>
       </c>
       <c r="R17" t="n">
-        <v>7087517</v>
+        <v>7087576</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,32 +2257,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217795</v>
+        <v>129217785</v>
       </c>
       <c r="B18" t="n">
-        <v>91553</v>
+        <v>91545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527123</v>
+        <v>527106</v>
       </c>
       <c r="R18" t="n">
-        <v>7087425</v>
+        <v>7087220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,10 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217855</v>
+        <v>129217928</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,14 +2385,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527012</v>
+        <v>527359</v>
       </c>
       <c r="R19" t="n">
-        <v>7087233</v>
+        <v>7087548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,6 +2433,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217785</v>
+        <v>129217852</v>
       </c>
       <c r="B20" t="n">
-        <v>91517</v>
+        <v>82905</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527106</v>
+        <v>527265</v>
       </c>
       <c r="R20" t="n">
-        <v>7087220</v>
+        <v>7087520</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,32 +2549,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217797</v>
+        <v>129217855</v>
       </c>
       <c r="B21" t="n">
-        <v>92271</v>
+        <v>82905</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527368</v>
+        <v>527012</v>
       </c>
       <c r="R21" t="n">
-        <v>7087576</v>
+        <v>7087233</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,7 +2649,7 @@
         <v>129217780</v>
       </c>
       <c r="B22" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>129217925</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>129217917</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>129217793</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>129217779</v>
       </c>
       <c r="B26" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217789</v>
+        <v>129217926</v>
       </c>
       <c r="B27" t="n">
-        <v>91553</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3147,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527376</v>
+        <v>527029</v>
       </c>
       <c r="R27" t="n">
-        <v>7087516</v>
+        <v>7087194</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217910</v>
+        <v>129217789</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3264,14 +3264,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527288</v>
+        <v>527376</v>
       </c>
       <c r="R28" t="n">
-        <v>7087491</v>
+        <v>7087516</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217926</v>
+        <v>129217910</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527029</v>
+        <v>527288</v>
       </c>
       <c r="R29" t="n">
-        <v>7087194</v>
+        <v>7087491</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,32 +3529,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217787</v>
+        <v>129217836</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527291</v>
+        <v>527091</v>
       </c>
       <c r="R31" t="n">
-        <v>7087491</v>
+        <v>7087273</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,10 +3626,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217922</v>
+        <v>129217787</v>
       </c>
       <c r="B32" t="n">
-        <v>56908</v>
+        <v>91581</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3637,34 +3637,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527122</v>
+        <v>527291</v>
       </c>
       <c r="R32" t="n">
-        <v>7087232</v>
+        <v>7087491</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3723,32 +3723,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217836</v>
+        <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527091</v>
+        <v>527034</v>
       </c>
       <c r="R33" t="n">
-        <v>7087273</v>
+        <v>7087201</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3820,10 +3825,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217820</v>
+        <v>129217922</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>56911</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3831,16 +3836,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3851,14 +3856,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527034</v>
+        <v>527122</v>
       </c>
       <c r="R34" t="n">
-        <v>7087201</v>
+        <v>7087232</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,11 +3896,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3925,7 +3925,7 @@
         <v>129217846</v>
       </c>
       <c r="B35" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,10 +4117,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217803</v>
+        <v>129217845</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4128,23 +4128,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4152,10 +4148,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526923</v>
+        <v>527173</v>
       </c>
       <c r="R37" t="n">
-        <v>7087199</v>
+        <v>7087380</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4188,11 +4184,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4219,10 +4210,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217821</v>
+        <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4254,10 +4245,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526924</v>
+        <v>526923</v>
       </c>
       <c r="R38" t="n">
-        <v>7087187</v>
+        <v>7087199</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4294,7 +4285,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4321,32 +4312,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217833</v>
+        <v>129217821</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4356,10 +4347,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527351</v>
+        <v>526924</v>
       </c>
       <c r="R39" t="n">
-        <v>7087510</v>
+        <v>7087187</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4396,7 +4387,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>47 plantor</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4423,10 +4414,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217835</v>
+        <v>129217833</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4458,10 +4449,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527103</v>
+        <v>527351</v>
       </c>
       <c r="R40" t="n">
-        <v>7087341</v>
+        <v>7087510</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4494,6 +4485,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>47 plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4520,30 +4516,34 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217845</v>
+        <v>129217835</v>
       </c>
       <c r="B41" t="n">
-        <v>91573</v>
+        <v>98756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527173</v>
+        <v>527103</v>
       </c>
       <c r="R41" t="n">
-        <v>7087380</v>
+        <v>7087341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4616,7 +4616,7 @@
         <v>129217792</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>129217843</v>
       </c>
       <c r="B43" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,32 +4807,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217826</v>
+        <v>129217778</v>
       </c>
       <c r="B44" t="n">
-        <v>80053</v>
+        <v>83039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527090</v>
+        <v>526957</v>
       </c>
       <c r="R44" t="n">
-        <v>7087261</v>
+        <v>7087142</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217778</v>
+        <v>129217838</v>
       </c>
       <c r="B45" t="n">
-        <v>83012</v>
+        <v>56911</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4915,21 +4915,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>526957</v>
+        <v>527239</v>
       </c>
       <c r="R45" t="n">
-        <v>7087142</v>
+        <v>7087332</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5001,32 +5001,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217838</v>
+        <v>129217826</v>
       </c>
       <c r="B46" t="n">
-        <v>56908</v>
+        <v>80079</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527239</v>
+        <v>527090</v>
       </c>
       <c r="R46" t="n">
-        <v>7087332</v>
+        <v>7087261</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5101,7 +5101,7 @@
         <v>129217923</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5200,45 +5200,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217920</v>
+        <v>129217790</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527064</v>
+        <v>527357</v>
       </c>
       <c r="R48" t="n">
-        <v>7087252</v>
+        <v>7087574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5271,11 +5271,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5302,32 +5297,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217790</v>
+        <v>129217844</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>57722</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5337,10 +5332,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527357</v>
+        <v>527355</v>
       </c>
       <c r="R49" t="n">
-        <v>7087574</v>
+        <v>7087521</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5399,32 +5394,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217844</v>
+        <v>129217805</v>
       </c>
       <c r="B50" t="n">
-        <v>57719</v>
+        <v>57730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5434,10 +5429,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527355</v>
+        <v>526924</v>
       </c>
       <c r="R50" t="n">
-        <v>7087521</v>
+        <v>7087183</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5470,6 +5465,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5496,45 +5496,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217805</v>
+        <v>129217920</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>526924</v>
+        <v>527064</v>
       </c>
       <c r="R51" t="n">
-        <v>7087183</v>
+        <v>7087252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5598,32 +5598,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217837</v>
+        <v>129217794</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>526980</v>
+        <v>527134</v>
       </c>
       <c r="R52" t="n">
-        <v>7087208</v>
+        <v>7087464</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5669,11 +5669,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5703,7 +5698,7 @@
         <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5825,7 +5820,7 @@
         <v>129217800</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5927,7 +5922,7 @@
         <v>129217801</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6026,32 +6021,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217794</v>
+        <v>129217837</v>
       </c>
       <c r="B56" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6061,10 +6056,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527134</v>
+        <v>526980</v>
       </c>
       <c r="R56" t="n">
-        <v>7087464</v>
+        <v>7087208</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6097,6 +6092,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>60 plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217848</v>
+        <v>129217823</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>57890</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527106</v>
+        <v>527374</v>
       </c>
       <c r="R57" t="n">
-        <v>7087367</v>
+        <v>7087508</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6225,32 +6225,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217823</v>
+        <v>129217832</v>
       </c>
       <c r="B58" t="n">
-        <v>57887</v>
+        <v>98756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527374</v>
+        <v>527149</v>
       </c>
       <c r="R58" t="n">
-        <v>7087508</v>
+        <v>7087289</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6327,45 +6327,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217784</v>
+        <v>129217919</v>
       </c>
       <c r="B59" t="n">
-        <v>96973</v>
+        <v>98756</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527349</v>
+        <v>527135</v>
       </c>
       <c r="R59" t="n">
-        <v>7087510</v>
+        <v>7087449</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6398,6 +6398,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6424,10 +6429,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217832</v>
+        <v>129217834</v>
       </c>
       <c r="B60" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6459,10 +6464,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527149</v>
+        <v>527268</v>
       </c>
       <c r="R60" t="n">
-        <v>7087289</v>
+        <v>7087590</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6499,7 +6504,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Flera 100 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6526,45 +6531,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217919</v>
+        <v>129217784</v>
       </c>
       <c r="B61" t="n">
-        <v>98727</v>
+        <v>97002</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527135</v>
+        <v>527349</v>
       </c>
       <c r="R61" t="n">
-        <v>7087449</v>
+        <v>7087510</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6597,11 +6602,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Väldigt många exemplar. 50 plus</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6628,32 +6628,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217834</v>
+        <v>129217848</v>
       </c>
       <c r="B62" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527268</v>
+        <v>527106</v>
       </c>
       <c r="R62" t="n">
-        <v>7087590</v>
+        <v>7087367</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6733,7 +6733,7 @@
         <v>129217829</v>
       </c>
       <c r="B63" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>129217827</v>
       </c>
       <c r="B64" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>129217854</v>
       </c>
       <c r="B65" t="n">
-        <v>82878</v>
+        <v>82905</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7021,45 +7021,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217913</v>
+        <v>129217806</v>
       </c>
       <c r="B66" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526924</v>
+        <v>526925</v>
       </c>
       <c r="R66" t="n">
-        <v>7087085</v>
+        <v>7087175</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7123,10 +7123,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217806</v>
+        <v>129217810</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526925</v>
+        <v>526914</v>
       </c>
       <c r="R67" t="n">
-        <v>7087175</v>
+        <v>7087139</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7225,10 +7225,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217810</v>
+        <v>129217818</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>526914</v>
+        <v>527359</v>
       </c>
       <c r="R68" t="n">
-        <v>7087139</v>
+        <v>7087452</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7327,45 +7327,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217818</v>
+        <v>129217913</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527359</v>
+        <v>526924</v>
       </c>
       <c r="R69" t="n">
-        <v>7087452</v>
+        <v>7087085</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Väldigt många exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7429,10 +7429,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217804</v>
+        <v>129217786</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>91581</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>526927</v>
+        <v>527238</v>
       </c>
       <c r="R70" t="n">
-        <v>7087193</v>
+        <v>7087520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7500,11 +7500,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7531,10 +7526,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217808</v>
+        <v>129217911</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>91581</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7542,34 +7537,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526917</v>
+        <v>527164</v>
       </c>
       <c r="R71" t="n">
-        <v>7087144</v>
+        <v>7087462</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7602,11 +7597,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7633,10 +7623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217786</v>
+        <v>129217853</v>
       </c>
       <c r="B72" t="n">
-        <v>91553</v>
+        <v>82905</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7644,21 +7634,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7668,10 +7658,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527238</v>
+        <v>527133</v>
       </c>
       <c r="R72" t="n">
-        <v>7087520</v>
+        <v>7087390</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7730,10 +7720,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217911</v>
+        <v>129217781</v>
       </c>
       <c r="B73" t="n">
-        <v>91553</v>
+        <v>83039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7741,34 +7731,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527164</v>
+        <v>527141</v>
       </c>
       <c r="R73" t="n">
-        <v>7087462</v>
+        <v>7087466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7827,10 +7817,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129217853</v>
+        <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>82878</v>
+        <v>57730</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7838,21 +7828,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7862,10 +7852,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527133</v>
+        <v>526927</v>
       </c>
       <c r="R74" t="n">
-        <v>7087390</v>
+        <v>7087193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7898,6 +7888,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7924,10 +7919,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129217781</v>
+        <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>83012</v>
+        <v>57730</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7935,21 +7930,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7959,10 +7954,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527141</v>
+        <v>526917</v>
       </c>
       <c r="R75" t="n">
-        <v>7087466</v>
+        <v>7087144</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7995,6 +7990,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8024,7 +8024,7 @@
         <v>129217839</v>
       </c>
       <c r="B76" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>129217825</v>
       </c>
       <c r="B77" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217841</v>
+        <v>129217912</v>
       </c>
       <c r="B78" t="n">
-        <v>91567</v>
+        <v>80175</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,34 +8226,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527375</v>
+        <v>527089</v>
       </c>
       <c r="R78" t="n">
-        <v>7087521</v>
+        <v>7087260</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8286,6 +8286,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8312,10 +8317,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217912</v>
+        <v>129217924</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>79070</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8323,21 +8328,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8347,10 +8352,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527089</v>
+        <v>527289</v>
       </c>
       <c r="R79" t="n">
-        <v>7087260</v>
+        <v>7087449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8383,11 +8388,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8414,10 +8414,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217924</v>
+        <v>129217802</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8425,34 +8425,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527289</v>
+        <v>526934</v>
       </c>
       <c r="R80" t="n">
-        <v>7087449</v>
+        <v>7087213</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8485,6 +8485,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8511,10 +8516,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129217802</v>
+        <v>129217929</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8542,14 +8547,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526934</v>
+        <v>527393</v>
       </c>
       <c r="R81" t="n">
-        <v>7087213</v>
+        <v>7087440</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8613,32 +8618,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129217929</v>
+        <v>129217921</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8648,10 +8653,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527393</v>
+        <v>526984</v>
       </c>
       <c r="R82" t="n">
-        <v>7087440</v>
+        <v>7087226</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8688,7 +8693,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många plantor, 50 +</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8715,10 +8720,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129217921</v>
+        <v>129217914</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8750,10 +8755,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526984</v>
+        <v>526928</v>
       </c>
       <c r="R83" t="n">
-        <v>7087226</v>
+        <v>7087112</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8790,7 +8795,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Väldigt många plantor, 50 +</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8817,45 +8822,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129217914</v>
+        <v>129217830</v>
       </c>
       <c r="B84" t="n">
-        <v>98727</v>
+        <v>78083</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526928</v>
+        <v>526990</v>
       </c>
       <c r="R84" t="n">
-        <v>7087112</v>
+        <v>7087234</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8888,11 +8893,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8919,10 +8919,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129217830</v>
+        <v>129217841</v>
       </c>
       <c r="B85" t="n">
-        <v>78057</v>
+        <v>91595</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>1204</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526990</v>
+        <v>527375</v>
       </c>
       <c r="R85" t="n">
-        <v>7087234</v>
+        <v>7087521</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9016,41 +9016,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129217847</v>
+        <v>129217915</v>
       </c>
       <c r="B86" t="n">
-        <v>91573</v>
+        <v>98756</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527069</v>
+        <v>527145</v>
       </c>
       <c r="R86" t="n">
-        <v>7087323</v>
+        <v>7087306</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9083,6 +9087,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9109,45 +9118,41 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129217915</v>
+        <v>129217847</v>
       </c>
       <c r="B87" t="n">
-        <v>98727</v>
+        <v>91601</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527145</v>
+        <v>527069</v>
       </c>
       <c r="R87" t="n">
-        <v>7087306</v>
+        <v>7087323</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9180,11 +9185,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Många rosetter</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9214,7 +9214,7 @@
         <v>129217783</v>
       </c>
       <c r="B88" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>129217851</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>129217814</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217849</v>
+        <v>129217815</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526979</v>
+        <v>526883</v>
       </c>
       <c r="R2" t="n">
-        <v>7087143</v>
+        <v>7087121</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,45 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217850</v>
+        <v>129217918</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527358</v>
+        <v>527262</v>
       </c>
       <c r="R3" t="n">
-        <v>7087435</v>
+        <v>7087588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt, över 200 bålar</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217815</v>
+        <v>129217849</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526883</v>
+        <v>526979</v>
       </c>
       <c r="R4" t="n">
-        <v>7087121</v>
+        <v>7087143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217918</v>
+        <v>129217850</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527262</v>
+        <v>527358</v>
       </c>
       <c r="R5" t="n">
-        <v>7087588</v>
+        <v>7087435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1374,32 +1374,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217782</v>
+        <v>129217856</v>
       </c>
       <c r="B9" t="n">
-        <v>97002</v>
+        <v>92272</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527172</v>
+        <v>527386</v>
       </c>
       <c r="R9" t="n">
-        <v>7087341</v>
+        <v>7087522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,10 +1573,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217798</v>
+        <v>129217782</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>97002</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1584,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527408</v>
+        <v>527172</v>
       </c>
       <c r="R11" t="n">
-        <v>7087464</v>
+        <v>7087341</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,11 +1644,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,32 +1670,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217856</v>
+        <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>92272</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527386</v>
+        <v>527408</v>
       </c>
       <c r="R12" t="n">
-        <v>7087522</v>
+        <v>7087464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -5098,10 +5098,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217923</v>
+        <v>129217790</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>91581</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5109,34 +5109,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527150</v>
+        <v>527357</v>
       </c>
       <c r="R47" t="n">
-        <v>7087278</v>
+        <v>7087574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5169,11 +5169,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5200,32 +5195,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217790</v>
+        <v>129217844</v>
       </c>
       <c r="B48" t="n">
-        <v>91581</v>
+        <v>57722</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5235,10 +5230,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527357</v>
+        <v>527355</v>
       </c>
       <c r="R48" t="n">
-        <v>7087574</v>
+        <v>7087521</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5297,32 +5292,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217844</v>
+        <v>129217805</v>
       </c>
       <c r="B49" t="n">
-        <v>57722</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5332,10 +5327,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527355</v>
+        <v>526924</v>
       </c>
       <c r="R49" t="n">
-        <v>7087521</v>
+        <v>7087183</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5368,6 +5363,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5394,45 +5394,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217805</v>
+        <v>129217920</v>
       </c>
       <c r="B50" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>526924</v>
+        <v>527064</v>
       </c>
       <c r="R50" t="n">
-        <v>7087183</v>
+        <v>7087252</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5469,7 +5469,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Väldigt många rosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5496,32 +5496,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217920</v>
+        <v>129217923</v>
       </c>
       <c r="B51" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5531,10 +5531,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527064</v>
+        <v>527150</v>
       </c>
       <c r="R51" t="n">
-        <v>7087252</v>
+        <v>7087278</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -8215,10 +8215,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129217912</v>
+        <v>129217802</v>
       </c>
       <c r="B78" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8226,34 +8226,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527089</v>
+        <v>526934</v>
       </c>
       <c r="R78" t="n">
-        <v>7087260</v>
+        <v>7087213</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Äldre exemplar på högstubbe av asp</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8317,10 +8317,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129217924</v>
+        <v>129217912</v>
       </c>
       <c r="B79" t="n">
-        <v>79070</v>
+        <v>80175</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8328,21 +8328,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527289</v>
+        <v>527089</v>
       </c>
       <c r="R79" t="n">
-        <v>7087449</v>
+        <v>7087260</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8388,6 +8388,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8414,10 +8419,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129217802</v>
+        <v>129217924</v>
       </c>
       <c r="B80" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8425,34 +8430,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>526934</v>
+        <v>527289</v>
       </c>
       <c r="R80" t="n">
-        <v>7087213</v>
+        <v>7087449</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8485,11 +8490,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129217815</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
         <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,12 +1265,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1474,7 +1474,7 @@
         <v>129217813</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,12 +1561,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1673,7 +1673,7 @@
         <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,12 +1760,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
         <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3517,12 +3517,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3726,7 +3726,7 @@
         <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3813,12 +3813,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
         <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4105,12 +4105,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
         <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4300,12 +4300,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4315,7 +4315,7 @@
         <v>129217821</v>
       </c>
       <c r="B39" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4402,12 +4402,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5295,7 +5295,7 @@
         <v>129217805</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5382,12 +5382,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5698,7 +5698,7 @@
         <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5805,12 +5805,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5820,7 +5820,7 @@
         <v>129217800</v>
       </c>
       <c r="B54" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5907,12 +5907,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5922,7 +5922,7 @@
         <v>129217801</v>
       </c>
       <c r="B55" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6009,12 +6009,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7024,7 +7024,7 @@
         <v>129217806</v>
       </c>
       <c r="B66" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7111,12 +7111,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7126,7 +7126,7 @@
         <v>129217810</v>
       </c>
       <c r="B67" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7213,12 +7213,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
         <v>129217818</v>
       </c>
       <c r="B68" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7315,12 +7315,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7820,7 +7820,7 @@
         <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7907,12 +7907,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7922,7 +7922,7 @@
         <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8009,12 +8009,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8218,7 +8218,7 @@
         <v>129217802</v>
       </c>
       <c r="B78" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8305,12 +8305,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8519,7 +8519,7 @@
         <v>129217929</v>
       </c>
       <c r="B81" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8606,12 +8606,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
         <v>129217814</v>
       </c>
       <c r="B90" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9500,12 +9500,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129217815</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129217813</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>129217821</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>129217805</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>129217800</v>
       </c>
       <c r="B54" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>129217801</v>
       </c>
       <c r="B55" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>129217806</v>
       </c>
       <c r="B66" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>129217810</v>
       </c>
       <c r="B67" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>129217818</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>129217802</v>
       </c>
       <c r="B78" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>129217929</v>
       </c>
       <c r="B81" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>129217814</v>
       </c>
       <c r="B90" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129217815</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129217813</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>129217821</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>129217805</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>129217800</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>129217801</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>129217806</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>129217810</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>129217818</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>129217802</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>129217929</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>129217814</v>
       </c>
       <c r="B90" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129217815</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129217799</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129217813</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129217798</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>129217807</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129217820</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129217812</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>129217803</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>129217821</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>129217805</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>129217819</v>
       </c>
       <c r="B53" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>129217800</v>
       </c>
       <c r="B54" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>129217801</v>
       </c>
       <c r="B55" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>129217806</v>
       </c>
       <c r="B66" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>129217810</v>
       </c>
       <c r="B67" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>129217818</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>129217804</v>
       </c>
       <c r="B74" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129217808</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>129217802</v>
       </c>
       <c r="B78" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>129217929</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>129217814</v>
       </c>
       <c r="B90" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 43555-2025 artfynd.xlsx
+++ b/artfynd/A 43555-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129217815</v>
+        <v>129217782</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526883</v>
+        <v>527172</v>
       </c>
       <c r="R2" t="n">
-        <v>7087121</v>
+        <v>7087341</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129217918</v>
+        <v>129217783</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527262</v>
+        <v>527221</v>
       </c>
       <c r="R3" t="n">
-        <v>7087588</v>
+        <v>7087348</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +845,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129217849</v>
+        <v>129217784</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526979</v>
+        <v>527349</v>
       </c>
       <c r="R4" t="n">
-        <v>7087143</v>
+        <v>7087510</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129217850</v>
+        <v>129217829</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527358</v>
+        <v>527138</v>
       </c>
       <c r="R5" t="n">
-        <v>7087435</v>
+        <v>7087472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,11 +1039,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt, över 200 bålar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1066,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129217791</v>
+        <v>129217856</v>
       </c>
       <c r="B6" t="n">
-        <v>91581</v>
+        <v>92605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527219</v>
+        <v>527386</v>
       </c>
       <c r="R6" t="n">
-        <v>7087542</v>
+        <v>7087522</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129217799</v>
+        <v>129217839</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527399</v>
+        <v>527283</v>
       </c>
       <c r="R7" t="n">
-        <v>7087454</v>
+        <v>7087446</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129217831</v>
+        <v>129217786</v>
       </c>
       <c r="B8" t="n">
-        <v>80135</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527362</v>
+        <v>527238</v>
       </c>
       <c r="R8" t="n">
-        <v>7087507</v>
+        <v>7087520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129217856</v>
+        <v>129217787</v>
       </c>
       <c r="B9" t="n">
-        <v>92272</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527386</v>
+        <v>527291</v>
       </c>
       <c r="R9" t="n">
-        <v>7087522</v>
+        <v>7087491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129217813</v>
+        <v>129217789</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526901</v>
+        <v>527376</v>
       </c>
       <c r="R10" t="n">
-        <v>7087135</v>
+        <v>7087516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129217782</v>
+        <v>129217790</v>
       </c>
       <c r="B11" t="n">
-        <v>97002</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1584,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527172</v>
+        <v>527357</v>
       </c>
       <c r="R11" t="n">
-        <v>7087341</v>
+        <v>7087574</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129217798</v>
+        <v>129217791</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1681,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527408</v>
+        <v>527219</v>
       </c>
       <c r="R12" t="n">
-        <v>7087464</v>
+        <v>7087542</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1741,11 +1716,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129217927</v>
+        <v>129217792</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526992</v>
+        <v>527192</v>
       </c>
       <c r="R13" t="n">
-        <v>7087193</v>
+        <v>7087529</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129217842</v>
+        <v>129217793</v>
       </c>
       <c r="B14" t="n">
-        <v>91595</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1904,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527385</v>
+        <v>527167</v>
       </c>
       <c r="R14" t="n">
-        <v>7087528</v>
+        <v>7087461</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,22 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129217840</v>
+        <v>129217794</v>
       </c>
       <c r="B15" t="n">
-        <v>91595</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527386</v>
+        <v>527134</v>
       </c>
       <c r="R15" t="n">
-        <v>7087517</v>
+        <v>7087464</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,12 +2021,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2066,7 +2036,7 @@
         <v>129217795</v>
       </c>
       <c r="B16" t="n">
-        <v>91581</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,57 +2118,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129217797</v>
+        <v>129217910</v>
       </c>
       <c r="B17" t="n">
-        <v>92299</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527368</v>
+        <v>527288</v>
       </c>
       <c r="R17" t="n">
-        <v>7087576</v>
+        <v>7087491</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,57 +2215,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129217785</v>
+        <v>129217911</v>
       </c>
       <c r="B18" t="n">
-        <v>91545</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527106</v>
+        <v>527164</v>
       </c>
       <c r="R18" t="n">
-        <v>7087220</v>
+        <v>7087462</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2342,57 +2312,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129217928</v>
+        <v>129217840</v>
       </c>
       <c r="B19" t="n">
-        <v>82905</v>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527359</v>
+        <v>527386</v>
       </c>
       <c r="R19" t="n">
-        <v>7087548</v>
+        <v>7087517</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2433,51 +2403,50 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129217852</v>
+        <v>129217841</v>
       </c>
       <c r="B20" t="n">
-        <v>82905</v>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2487,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527265</v>
+        <v>527375</v>
       </c>
       <c r="R20" t="n">
-        <v>7087520</v>
+        <v>7087521</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2537,44 +2506,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129217855</v>
+        <v>129217842</v>
       </c>
       <c r="B21" t="n">
-        <v>82905</v>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2584,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527012</v>
+        <v>527385</v>
       </c>
       <c r="R21" t="n">
-        <v>7087233</v>
+        <v>7087528</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2634,44 +2603,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129217780</v>
+        <v>129217843</v>
       </c>
       <c r="B22" t="n">
-        <v>83039</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2681,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527179</v>
+        <v>527378</v>
       </c>
       <c r="R22" t="n">
-        <v>7087518</v>
+        <v>7087514</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,22 +2700,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129217925</v>
+        <v>129217827</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>92369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2754,34 +2723,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527089</v>
+        <v>527136</v>
       </c>
       <c r="R23" t="n">
-        <v>7087260</v>
+        <v>7087471</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,57 +2797,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129217917</v>
+        <v>129217852</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527273</v>
+        <v>527265</v>
       </c>
       <c r="R24" t="n">
-        <v>7087581</v>
+        <v>7087520</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2913,11 +2882,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Väldigt många rosetter</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -2930,22 +2894,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129217793</v>
+        <v>129217853</v>
       </c>
       <c r="B25" t="n">
-        <v>91581</v>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2953,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527167</v>
+        <v>527133</v>
       </c>
       <c r="R25" t="n">
-        <v>7087461</v>
+        <v>7087390</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3027,22 +2991,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129217779</v>
+        <v>129217854</v>
       </c>
       <c r="B26" t="n">
-        <v>83039</v>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527248</v>
+        <v>527015</v>
       </c>
       <c r="R26" t="n">
-        <v>7087513</v>
+        <v>7087228</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3124,22 +3088,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129217926</v>
+        <v>129217855</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,34 +3111,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527029</v>
+        <v>527012</v>
       </c>
       <c r="R27" t="n">
-        <v>7087194</v>
+        <v>7087233</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,22 +3185,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129217789</v>
+        <v>129217928</v>
       </c>
       <c r="B28" t="n">
-        <v>91581</v>
+        <v>83173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,34 +3208,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527376</v>
+        <v>527359</v>
       </c>
       <c r="R28" t="n">
-        <v>7087516</v>
+        <v>7087548</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3312,63 +3276,64 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129217910</v>
+        <v>129217797</v>
       </c>
       <c r="B29" t="n">
-        <v>91581</v>
+        <v>92632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527288</v>
+        <v>527368</v>
       </c>
       <c r="R29" t="n">
-        <v>7087491</v>
+        <v>7087576</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3415,44 +3380,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129217807</v>
+        <v>129217785</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3462,10 +3427,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>526921</v>
+        <v>527106</v>
       </c>
       <c r="R30" t="n">
-        <v>7087159</v>
+        <v>7087220</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3463,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,10 +3489,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129217836</v>
+        <v>129217848</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3540,21 +3500,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527091</v>
+        <v>527106</v>
       </c>
       <c r="R31" t="n">
-        <v>7087273</v>
+        <v>7087367</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,6 +3562,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3614,44 +3579,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129217787</v>
+        <v>129217849</v>
       </c>
       <c r="B32" t="n">
-        <v>91581</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527291</v>
+        <v>526979</v>
       </c>
       <c r="R32" t="n">
-        <v>7087491</v>
+        <v>7087143</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,44 +3676,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129217820</v>
+        <v>129217850</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527034</v>
+        <v>527358</v>
       </c>
       <c r="R33" t="n">
-        <v>7087201</v>
+        <v>7087435</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3798,7 +3763,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt, över 200 bålar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,45 +3790,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129217922</v>
+        <v>129217851</v>
       </c>
       <c r="B34" t="n">
-        <v>56911</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527122</v>
+        <v>527094</v>
       </c>
       <c r="R34" t="n">
-        <v>7087232</v>
+        <v>7087264</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3898,6 +3863,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -3910,53 +3880,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129217846</v>
+        <v>129217923</v>
       </c>
       <c r="B35" t="n">
-        <v>91601</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527139</v>
+        <v>527150</v>
       </c>
       <c r="R35" t="n">
-        <v>7087468</v>
+        <v>7087278</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3991,6 +3965,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt. Över 100 bålar på flera granar</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4003,57 +3982,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129217812</v>
+        <v>129217924</v>
       </c>
       <c r="B36" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>526904</v>
+        <v>527289</v>
       </c>
       <c r="R36" t="n">
-        <v>7087132</v>
+        <v>7087449</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4086,11 +4065,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4117,41 +4091,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129217845</v>
+        <v>129217925</v>
       </c>
       <c r="B37" t="n">
-        <v>91601</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527173</v>
+        <v>527089</v>
       </c>
       <c r="R37" t="n">
-        <v>7087380</v>
+        <v>7087260</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4198,57 +4176,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129217803</v>
+        <v>129217926</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526923</v>
+        <v>527029</v>
       </c>
       <c r="R38" t="n">
-        <v>7087199</v>
+        <v>7087194</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,11 +4259,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4312,45 +4285,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129217821</v>
+        <v>129217927</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526924</v>
+        <v>526992</v>
       </c>
       <c r="R39" t="n">
-        <v>7087187</v>
+        <v>7087193</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4383,11 +4356,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4414,32 +4382,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129217833</v>
+        <v>129217778</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>83307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4449,10 +4417,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527351</v>
+        <v>526957</v>
       </c>
       <c r="R40" t="n">
-        <v>7087510</v>
+        <v>7087142</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4487,11 +4455,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>47 plantor</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4504,44 +4467,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129217835</v>
+        <v>129217779</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4551,10 +4514,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527103</v>
+        <v>527248</v>
       </c>
       <c r="R41" t="n">
-        <v>7087341</v>
+        <v>7087513</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4601,22 +4564,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129217792</v>
+        <v>129217780</v>
       </c>
       <c r="B42" t="n">
-        <v>91581</v>
+        <v>83307</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4624,21 +4587,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4648,10 +4611,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527192</v>
+        <v>527179</v>
       </c>
       <c r="R42" t="n">
-        <v>7087529</v>
+        <v>7087518</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4698,22 +4661,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129217843</v>
+        <v>129217781</v>
       </c>
       <c r="B43" t="n">
-        <v>91595</v>
+        <v>83307</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4721,21 +4684,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4745,10 +4708,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527378</v>
+        <v>527141</v>
       </c>
       <c r="R43" t="n">
-        <v>7087514</v>
+        <v>7087466</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4795,44 +4758,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129217778</v>
+        <v>129217825</v>
       </c>
       <c r="B44" t="n">
-        <v>83039</v>
+        <v>80336</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4842,10 +4805,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>526957</v>
+        <v>527297</v>
       </c>
       <c r="R44" t="n">
-        <v>7087142</v>
+        <v>7087643</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4892,44 +4855,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129217838</v>
+        <v>129217826</v>
       </c>
       <c r="B45" t="n">
-        <v>56911</v>
+        <v>80336</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4939,10 +4902,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527239</v>
+        <v>527090</v>
       </c>
       <c r="R45" t="n">
-        <v>7087332</v>
+        <v>7087261</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4989,57 +4952,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129217826</v>
+        <v>129217912</v>
       </c>
       <c r="B46" t="n">
-        <v>80079</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527090</v>
+        <v>527089</v>
       </c>
       <c r="R46" t="n">
-        <v>7087261</v>
+        <v>7087260</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5074,6 +5037,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre exemplar på högstubbe av asp</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5086,44 +5054,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129217790</v>
+        <v>129217824</v>
       </c>
       <c r="B47" t="n">
-        <v>91581</v>
+        <v>80461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5133,10 +5101,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527357</v>
+        <v>526972</v>
       </c>
       <c r="R47" t="n">
-        <v>7087574</v>
+        <v>7087130</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5183,44 +5151,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129217844</v>
+        <v>129217798</v>
       </c>
       <c r="B48" t="n">
-        <v>57722</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5230,10 +5198,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527355</v>
+        <v>527408</v>
       </c>
       <c r="R48" t="n">
-        <v>7087521</v>
+        <v>7087464</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5268,6 +5236,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5280,22 +5253,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129217805</v>
+        <v>129217799</v>
       </c>
       <c r="B49" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5327,10 +5300,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>526924</v>
+        <v>527399</v>
       </c>
       <c r="R49" t="n">
-        <v>7087183</v>
+        <v>7087454</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5367,7 +5340,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5394,45 +5367,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129217920</v>
+        <v>129217800</v>
       </c>
       <c r="B50" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527064</v>
+        <v>527297</v>
       </c>
       <c r="R50" t="n">
-        <v>7087252</v>
+        <v>7087514</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5469,7 +5442,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Väldigt många rosetter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5484,22 +5457,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129217923</v>
+        <v>129217801</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5507,34 +5480,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527150</v>
+        <v>527106</v>
       </c>
       <c r="R51" t="n">
-        <v>7087278</v>
+        <v>7087348</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5571,7 +5544,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt. Över 100 bålar på flera granar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5586,22 +5559,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129217794</v>
+        <v>129217802</v>
       </c>
       <c r="B52" t="n">
-        <v>91581</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5609,21 +5582,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5633,10 +5606,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527134</v>
+        <v>526934</v>
       </c>
       <c r="R52" t="n">
-        <v>7087464</v>
+        <v>7087213</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5671,6 +5644,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5683,22 +5661,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129217819</v>
+        <v>129217803</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5723,37 +5701,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527070</v>
+        <v>526923</v>
       </c>
       <c r="R53" t="n">
-        <v>7087285</v>
+        <v>7087199</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5790,7 +5748,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Födosökande hona</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5817,10 +5775,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129217800</v>
+        <v>129217804</v>
       </c>
       <c r="B54" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,10 +5810,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527297</v>
+        <v>526927</v>
       </c>
       <c r="R54" t="n">
-        <v>7087514</v>
+        <v>7087193</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5892,7 +5850,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5919,10 +5877,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129217801</v>
+        <v>129217805</v>
       </c>
       <c r="B55" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5954,10 +5912,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527106</v>
+        <v>526924</v>
       </c>
       <c r="R55" t="n">
-        <v>7087348</v>
+        <v>7087183</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6021,32 +5979,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129217837</v>
+        <v>129217806</v>
       </c>
       <c r="B56" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6056,10 +6014,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526980</v>
+        <v>526925</v>
       </c>
       <c r="R56" t="n">
-        <v>7087208</v>
+        <v>7087175</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6096,7 +6054,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>60 plantor</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6111,22 +6069,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129217823</v>
+        <v>129217807</v>
       </c>
       <c r="B57" t="n">
-        <v>57890</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6092,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6116,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527374</v>
+        <v>526921</v>
       </c>
       <c r="R57" t="n">
-        <v>7087508</v>
+        <v>7087159</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6198,7 +6156,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6213,44 +6171,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129217832</v>
+        <v>129217808</v>
       </c>
       <c r="B58" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6260,10 +6218,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527149</v>
+        <v>526917</v>
       </c>
       <c r="R58" t="n">
-        <v>7087289</v>
+        <v>7087144</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6300,7 +6258,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>30 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6315,57 +6273,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129217919</v>
+        <v>129217809</v>
       </c>
       <c r="B59" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527135</v>
+        <v>526909</v>
       </c>
       <c r="R59" t="n">
-        <v>7087449</v>
+        <v>7087153</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6402,7 +6360,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar. 50 plus</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6417,44 +6375,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129217834</v>
+        <v>129217810</v>
       </c>
       <c r="B60" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6464,10 +6422,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527268</v>
+        <v>526914</v>
       </c>
       <c r="R60" t="n">
-        <v>7087590</v>
+        <v>7087139</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6504,7 +6462,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Flera 100 plantor</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6519,22 +6477,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129217784</v>
+        <v>129217812</v>
       </c>
       <c r="B61" t="n">
-        <v>97002</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6542,21 +6500,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6566,10 +6524,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527349</v>
+        <v>526904</v>
       </c>
       <c r="R61" t="n">
-        <v>7087510</v>
+        <v>7087132</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6604,6 +6562,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6616,22 +6579,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129217848</v>
+        <v>129217813</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6639,21 +6602,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6663,10 +6626,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527106</v>
+        <v>526901</v>
       </c>
       <c r="R62" t="n">
-        <v>7087367</v>
+        <v>7087135</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6703,7 +6666,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6718,22 +6681,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129217829</v>
+        <v>129217814</v>
       </c>
       <c r="B63" t="n">
-        <v>91879</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6741,21 +6704,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6765,10 +6728,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527138</v>
+        <v>526905</v>
       </c>
       <c r="R63" t="n">
-        <v>7087472</v>
+        <v>7087117</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6803,6 +6766,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -6815,44 +6783,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129217827</v>
+        <v>129217815</v>
       </c>
       <c r="B64" t="n">
-        <v>92034</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6862,10 +6830,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527136</v>
+        <v>526883</v>
       </c>
       <c r="R64" t="n">
-        <v>7087471</v>
+        <v>7087121</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6900,6 +6868,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -6912,22 +6885,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129217854</v>
+        <v>129217816</v>
       </c>
       <c r="B65" t="n">
-        <v>82905</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6935,21 +6908,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6959,10 +6932,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527015</v>
+        <v>526870</v>
       </c>
       <c r="R65" t="n">
-        <v>7087228</v>
+        <v>7087117</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6997,6 +6970,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7009,22 +6987,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129217806</v>
+        <v>129217818</v>
       </c>
       <c r="B66" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7056,10 +7034,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526925</v>
+        <v>527359</v>
       </c>
       <c r="R66" t="n">
-        <v>7087175</v>
+        <v>7087452</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7123,10 +7101,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129217810</v>
+        <v>129217819</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7151,17 +7129,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526914</v>
+        <v>527070</v>
       </c>
       <c r="R67" t="n">
-        <v>7087139</v>
+        <v>7087285</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7198,7 +7196,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Födosökande hona</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7225,10 +7223,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129217818</v>
+        <v>129217820</v>
       </c>
       <c r="B68" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7260,10 +7258,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527359</v>
+        <v>527034</v>
       </c>
       <c r="R68" t="n">
-        <v>7087452</v>
+        <v>7087201</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7327,45 +7325,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129217913</v>
+        <v>129217821</v>
       </c>
       <c r="B69" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
         <v>526924</v>
       </c>
       <c r="R69" t="n">
-        <v>7087085</v>
+        <v>7087187</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7402,7 +7400,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Väldigt många exemplar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7417,22 +7415,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129217786</v>
+        <v>129217929</v>
       </c>
       <c r="B70" t="n">
-        <v>91581</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7440,34 +7438,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527238</v>
+        <v>527393</v>
       </c>
       <c r="R70" t="n">
-        <v>7087520</v>
+        <v>7087440</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7502,6 +7500,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7514,57 +7517,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129217911</v>
+        <v>129217844</v>
       </c>
       <c r="B71" t="n">
-        <v>91581</v>
+        <v>57945</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lager 2, Jmt</t>
+          <t>Illdrolet, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527164</v>
+        <v>527355</v>
       </c>
       <c r="R71" t="n">
-        <v>7087462</v>
+        <v>7087521</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7611,44 +7614,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129217853</v>
+        <v>129217838</v>
       </c>
       <c r="B72" t="n">
-        <v>82905</v>
+        <v>57132</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7658,10 +7661,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527133</v>
+        <v>527239</v>
       </c>
       <c r="R72" t="n">
-        <v>7087390</v>
+        <v>7087332</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7708,57 +7711,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129217781</v>
+        <v>129217922</v>
       </c>
       <c r="B73" t="n">
-        <v>83039</v>
+        <v>57132</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Illdrolet, Jmt</t>
+          <t>Lager 2, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527141</v>
+        <v>527122</v>
       </c>
       <c r="R73" t="n">
-        <v>7087466</v>
+        <v>7087232</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7805,22 +7808,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mariel